--- a/participants/Mari BH.xlsx
+++ b/participants/Mari BH.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uio.sharepoint.com/sites/VM-tippekonk/Delte dokumenter/General/Innsendte skjema/Kampresultat/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uio-my.sharepoint.com/personal/mbergset_uio_no/Documents/privat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AE113A2-668B-4DC6-9CD4-D9EE75BE6CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{2E4C6686-4D4E-4593-9826-8946E4147F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF36653-14C0-4F97-9CFB-BAC71DD21AD3}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="26280" windowHeight="17775" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="28770" windowHeight="16890" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T" sheetId="1" state="hidden" r:id="rId1"/>
@@ -40564,7 +40564,7 @@
       </c>
       <c r="AM8" s="123">
         <f>AL8-AL12</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN8" s="123">
         <f>AF8*3+AG8</f>
@@ -40576,7 +40576,7 @@
       </c>
       <c r="AP8" s="123">
         <f>AO8*10000000+BI8*100+AM8/AM12*10+AI8/AI12*1++IF(AQ8=0,ROW(),AQ8)/2000000</f>
-        <v>90000009.191316694</v>
+        <v>90000009.429411933</v>
       </c>
       <c r="AQ8" s="126">
         <f>VLOOKUP(AE8,db_fifarank,2,FALSE)</f>
@@ -40588,7 +40588,7 @@
       </c>
       <c r="AS8" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J9,"1A")</f>
-        <v>1A</v>
+        <v>Mexico</v>
       </c>
       <c r="AT8" s="126" cm="1">
         <f t="array" ref="AT8">SUMPRODUCT(($S$7:$S$78=AE8&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE8&amp;"_win")*($U$7:$U$78))</f>
@@ -40795,7 +40795,7 @@
       </c>
       <c r="AH9" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE9 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE9,$G$7:$G$78)</f>
@@ -40803,11 +40803,11 @@
       </c>
       <c r="AJ9" s="123">
         <f>SUMIF($E$7:$E$78,$AE9,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE9,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL9" s="123">
         <f>AI9-AJ9</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM9" s="123">
         <f>AL9-AL12</f>
@@ -40831,11 +40831,11 @@
       </c>
       <c r="AR9" s="125">
         <f>AP9/AP12</f>
-        <v>1.595244351105583E-9</v>
+        <v>1.5952443468853603E-9</v>
       </c>
       <c r="AS9" s="125" t="str">
         <f>IF(SUM(AF8:AH11)=12,J10,"2A")</f>
-        <v>2A</v>
+        <v>Czech Republic</v>
       </c>
       <c r="AT9" s="126" cm="1">
         <f t="array" ref="AT9">SUMPRODUCT(($S$7:$S$78=AE9&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE9&amp;"_win")*($U$7:$U$78))</f>
@@ -41052,7 +41052,7 @@
       </c>
       <c r="AF10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE10 &amp; "_draw")</f>
@@ -41064,7 +41064,7 @@
       </c>
       <c r="AI10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE10,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ10" s="123">
         <f>SUMIF($E$7:$E$78,$AE10,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE10,$F$7:$F$78)</f>
@@ -41072,23 +41072,23 @@
       </c>
       <c r="AL10" s="123">
         <f>AI10-AJ10</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM10" s="123">
         <f>AL10-AL12</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN10" s="123">
         <f>AF10*3+AG10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10" s="123">
         <f>AN10/AN12*10+BA10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP10" s="123">
         <f>AO10*10000000+BI10*100+AM10/AM12*10+AI10/AI12*1++IF(AQ10=0,ROW(),AQ10)/2000000</f>
-        <v>0.42936575857142856</v>
+        <v>30000003.429365758</v>
       </c>
       <c r="AQ10" s="126">
         <f>VLOOKUP(AE10,db_fifarank,2,FALSE)</f>
@@ -41096,7 +41096,7 @@
       </c>
       <c r="AR10" s="125">
         <f>AP10/AP12</f>
-        <v>4.7707301105711905E-9</v>
+        <v>0.33333333280994576</v>
       </c>
       <c r="AT10" s="126" cm="1">
         <f t="array" ref="AT10">SUMPRODUCT(($S$7:$S$78=AE10&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE10&amp;"_win")*($U$7:$U$78))</f>
@@ -41167,14 +41167,16 @@
       </c>
       <c r="BL10" s="24" t="str">
         <f>AS32</f>
-        <v>1E</v>
-      </c>
-      <c r="BM10" s="61"/>
+        <v>Germany</v>
+      </c>
+      <c r="BM10" s="61">
+        <v>2</v>
+      </c>
       <c r="BN10" s="63"/>
       <c r="BO10" s="25"/>
-      <c r="BP10" s="112" t="str">
+      <c r="BP10" s="112">
         <f>IF(OR(BM10="",BM11="",AND(BN10="",BN11&lt;&gt;""),AND(BN11="",BN10&lt;&gt;""),AND(BO10="",BO11&lt;&gt;""),AND(BO11="",BO10&lt;&gt;"")),"",BM10*1000+BN10*10+BO10)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ10" s="112"/>
       <c r="BR10" s="21"/>
@@ -41239,11 +41241,11 @@
       </c>
       <c r="K11" s="23">
         <f>L11+M11+N11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="23">
         <f>VLOOKUP(3,AD8:AN11,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="23">
         <f>VLOOKUP(3,AD8:AN11,4,FALSE)</f>
@@ -41255,11 +41257,11 @@
       </c>
       <c r="O11" s="23" t="str">
         <f>VLOOKUP(3,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD8:AN11,7,FALSE)</f>
-        <v>3 - 5</v>
+        <v>4 - 5</v>
       </c>
       <c r="P11" s="34">
         <f>L11*3+M11</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" s="123">
         <f>DATE(2026,6,13)+TIME(14,0,0)+gmt_delta</f>
@@ -41339,7 +41341,7 @@
       </c>
       <c r="AM11" s="123">
         <f>AL11-AL12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="123">
         <f>AF11*3+AG11</f>
@@ -41351,7 +41353,7 @@
       </c>
       <c r="AP11" s="123">
         <f>AO11*10000000+BI11*100+AM11/AM12*10+AI11/AI12*1++IF(AQ11=0,ROW(),AQ11)/2000000</f>
-        <v>60000005.715036407</v>
+        <v>60000006.429322124</v>
       </c>
       <c r="AQ11" s="126">
         <f>VLOOKUP(AE11,db_fifarank,2,FALSE)</f>
@@ -41359,7 +41361,7 @@
       </c>
       <c r="AR11" s="125">
         <f>AP11/AP12</f>
-        <v>0.66666665467583774</v>
+        <v>0.66666666084867665</v>
       </c>
       <c r="AT11" s="126" cm="1">
         <f t="array" ref="AT11">SUMPRODUCT(($S$7:$S$78=AE11&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE11&amp;"_win")*($U$7:$U$78))</f>
@@ -41428,14 +41430,16 @@
       <c r="BK11" s="142"/>
       <c r="BL11" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!G3,AK80:AS91,9,FALSE),"3rd Group A/B/C/D/F")</f>
-        <v>3rd Group A/B/C/D/F</v>
-      </c>
-      <c r="BM11" s="62"/>
+        <v>Scotland</v>
+      </c>
+      <c r="BM11" s="62">
+        <v>1</v>
+      </c>
       <c r="BN11" s="64"/>
       <c r="BO11" s="27"/>
-      <c r="BP11" s="113" t="str">
+      <c r="BP11" s="113">
         <f>IF(BP10="","",BM11*1000+BN11*10+BO11)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ11" s="112"/>
       <c r="BR11" s="21" t="str" cm="1">
@@ -41506,7 +41510,7 @@
       </c>
       <c r="K12" s="36">
         <f>L12+M12+N12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="36">
         <f>VLOOKUP(4,AD8:AN11,3,FALSE)</f>
@@ -41518,11 +41522,11 @@
       </c>
       <c r="N12" s="36">
         <f>VLOOKUP(4,AD8:AN11,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" s="36" t="str">
         <f>VLOOKUP(4,AD8:AN11,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD8:AN11,7,FALSE)</f>
-        <v>1 - 3</v>
+        <v>1 - 4</v>
       </c>
       <c r="P12" s="37">
         <f>L12*3+M12</f>
@@ -41582,7 +41586,7 @@
       </c>
       <c r="AH12" s="123">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI12" s="123">
         <f>MAX(AI8:AI11)+1</f>
@@ -41590,11 +41594,11 @@
       </c>
       <c r="AL12" s="123">
         <f>MIN(AL8:AL11)</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AM12" s="123">
         <f>MAX(AM8:AM11)+1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN12" s="123">
         <f>MAX(AN8:AN11)+1</f>
@@ -41606,7 +41610,7 @@
       </c>
       <c r="AP12" s="123">
         <f>MAX(AP8:AP11)+1</f>
-        <v>90000010.191316694</v>
+        <v>90000010.429411933</v>
       </c>
       <c r="AT12" s="126">
         <f>MAX(AT8:AT11)-MIN(AT8:AT11)+1</f>
@@ -41668,14 +41672,16 @@
       </c>
       <c r="BS12" s="24" t="str">
         <f>IF(BP10&gt;BP11,BL10,IF(BP10&lt;BP11,BL11,""))</f>
-        <v/>
-      </c>
-      <c r="BT12" s="61"/>
+        <v>Germany</v>
+      </c>
+      <c r="BT12" s="61">
+        <v>1</v>
+      </c>
       <c r="BU12" s="63"/>
       <c r="BV12" s="25"/>
-      <c r="BW12" s="112" t="str">
+      <c r="BW12" s="112">
         <f>IF(OR(BT12="",BT13="",AND(BU12="",BU13&lt;&gt;""),AND(BU13="",BU12&lt;&gt;""),AND(BV12="",BV13&lt;&gt;""),AND(BV13="",BV12&lt;&gt;"")),"",BT12*1000+BU12*10+BV12)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BX12" s="112"/>
       <c r="BY12" s="21"/>
@@ -41787,14 +41793,16 @@
       <c r="BR13" s="142"/>
       <c r="BS13" s="26" t="str">
         <f>IF(BP14&gt;BP15,BL14,IF(BP14&lt;BP15,BL15,""))</f>
-        <v/>
-      </c>
-      <c r="BT13" s="62"/>
+        <v>France</v>
+      </c>
+      <c r="BT13" s="62">
+        <v>2</v>
+      </c>
       <c r="BU13" s="64"/>
       <c r="BV13" s="27"/>
-      <c r="BW13" s="113" t="str">
+      <c r="BW13" s="113">
         <f>IF(BW12="","",BT13*1000+BU13*10+BV13)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BX13" s="112"/>
       <c r="BY13" s="21"/>
@@ -42047,14 +42055,16 @@
       </c>
       <c r="BL14" s="24" t="str">
         <f>AS56</f>
-        <v>1I</v>
-      </c>
-      <c r="BM14" s="61"/>
+        <v>France</v>
+      </c>
+      <c r="BM14" s="61">
+        <v>3</v>
+      </c>
       <c r="BN14" s="63"/>
       <c r="BO14" s="25"/>
-      <c r="BP14" s="116" t="str">
+      <c r="BP14" s="116">
         <f>IF(OR(BM14="",BM15="",AND(BN14="",BN15&lt;&gt;""),AND(BN15="",BN14&lt;&gt;""),AND(BO14="",BO15&lt;&gt;""),AND(BO15="",BO14&lt;&gt;"")),"",BM14*1000+BN14*10+BO14)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ14" s="112"/>
       <c r="BR14" s="21"/>
@@ -42312,14 +42322,16 @@
       <c r="BK15" s="142"/>
       <c r="BL15" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!I3,AK80:AS91,9,FALSE),"3rd Group C/D/F/G/H")</f>
-        <v>3rd Group C/D/F/G/H</v>
-      </c>
-      <c r="BM15" s="62"/>
+        <v>Australia</v>
+      </c>
+      <c r="BM15" s="62">
+        <v>1</v>
+      </c>
       <c r="BN15" s="64"/>
       <c r="BO15" s="27"/>
-      <c r="BP15" s="112" t="str">
+      <c r="BP15" s="112">
         <f>IF(BP14="","",BM15*1000+BN15*10+BO15)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ15" s="112"/>
       <c r="BR15" s="21"/>
@@ -42588,14 +42600,16 @@
       </c>
       <c r="BZ16" s="24" t="str">
         <f>IF(BW12&gt;BW13,BS12,IF(BW12&lt;BW13,BS13,""))</f>
-        <v/>
-      </c>
-      <c r="CA16" s="61"/>
+        <v>France</v>
+      </c>
+      <c r="CA16" s="61">
+        <v>1</v>
+      </c>
       <c r="CB16" s="63"/>
       <c r="CC16" s="25"/>
-      <c r="CD16" s="112" t="str">
+      <c r="CD16" s="112">
         <f>IF(OR(CA16="",CA17="",AND(CB16="",CB17&lt;&gt;""),AND(CB17="",CB16&lt;&gt;""),AND(CC16="",CC17&lt;&gt;""),AND(CC17="",CC16&lt;&gt;"")),"",CA16*1000+CB16*10+CC16)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="CE16" s="112"/>
       <c r="CF16" s="21"/>
@@ -42848,14 +42862,16 @@
       <c r="BY17" s="142"/>
       <c r="BZ17" s="26" t="str">
         <f>IF(BW20&gt;BW21,BS20,IF(BW20&lt;BW21,BS21,""))</f>
-        <v/>
-      </c>
-      <c r="CA17" s="62"/>
+        <v>Canada</v>
+      </c>
+      <c r="CA17" s="62">
+        <v>0</v>
+      </c>
       <c r="CB17" s="64"/>
       <c r="CC17" s="27"/>
-      <c r="CD17" s="113" t="str">
+      <c r="CD17" s="113">
         <f>IF(CD16="","",CA17*1000+CB17*10+CC17)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE17" s="117"/>
       <c r="CF17" s="21"/>
@@ -43054,14 +43070,18 @@
       </c>
       <c r="BL18" s="24" t="str">
         <f>AS9</f>
-        <v>2A</v>
-      </c>
-      <c r="BM18" s="61"/>
-      <c r="BN18" s="63"/>
+        <v>Czech Republic</v>
+      </c>
+      <c r="BM18" s="61">
+        <v>1</v>
+      </c>
+      <c r="BN18" s="63">
+        <v>1</v>
+      </c>
       <c r="BO18" s="25"/>
-      <c r="BP18" s="112" t="str">
+      <c r="BP18" s="112">
         <f>IF(OR(BM18="",BM19="",AND(BN18="",BN19&lt;&gt;""),AND(BN19="",BN18&lt;&gt;""),AND(BO18="",BO19&lt;&gt;""),AND(BO19="",BO18&lt;&gt;"")),"",BM18*1000+BN18*10+BO18)</f>
-        <v/>
+        <v>1010</v>
       </c>
       <c r="BQ18" s="112"/>
       <c r="BR18" s="21"/>
@@ -43162,12 +43182,16 @@
         <f>AS15</f>
         <v>Canada</v>
       </c>
-      <c r="BM19" s="62"/>
-      <c r="BN19" s="64"/>
+      <c r="BM19" s="62">
+        <v>1</v>
+      </c>
+      <c r="BN19" s="64">
+        <v>2</v>
+      </c>
       <c r="BO19" s="27"/>
-      <c r="BP19" s="113" t="str">
+      <c r="BP19" s="113">
         <f>IF(BP18="","",BM19*1000+BN19*10+BO19)</f>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="BQ19" s="112"/>
       <c r="BR19" s="21" t="str" cm="1">
@@ -43440,14 +43464,18 @@
       </c>
       <c r="BS20" s="24" t="str">
         <f>IF(BP18&gt;BP19,BL18,IF(BP18&lt;BP19,BL19,""))</f>
-        <v/>
-      </c>
-      <c r="BT20" s="61"/>
-      <c r="BU20" s="63"/>
+        <v>Canada</v>
+      </c>
+      <c r="BT20" s="61">
+        <v>2</v>
+      </c>
+      <c r="BU20" s="63">
+        <v>3</v>
+      </c>
       <c r="BV20" s="25"/>
-      <c r="BW20" s="116" t="str">
+      <c r="BW20" s="116">
         <f>IF(OR(BT20="",BT21="",AND(BU20="",BU21&lt;&gt;""),AND(BU21="",BU20&lt;&gt;""),AND(BV20="",BV21&lt;&gt;""),AND(BV21="",BV20&lt;&gt;"")),"",BT20*1000+BU20*10+BV20)</f>
-        <v/>
+        <v>2030</v>
       </c>
       <c r="BX20" s="112"/>
       <c r="BY20" s="21"/>
@@ -43541,7 +43569,7 @@
       </c>
       <c r="U21" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="123">
         <f t="shared" si="3"/>
@@ -43553,7 +43581,7 @@
       </c>
       <c r="X21" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="123">
         <f t="shared" si="10"/>
@@ -43711,14 +43739,18 @@
       <c r="BR21" s="142"/>
       <c r="BS21" s="26" t="str">
         <f>IF(BP22&gt;BP23,BL22,IF(BP22&lt;BP23,BL23,""))</f>
-        <v/>
-      </c>
-      <c r="BT21" s="62"/>
-      <c r="BU21" s="64"/>
+        <v>Netherlands</v>
+      </c>
+      <c r="BT21" s="62">
+        <v>2</v>
+      </c>
+      <c r="BU21" s="64">
+        <v>2</v>
+      </c>
       <c r="BV21" s="27"/>
-      <c r="BW21" s="112" t="str">
+      <c r="BW21" s="112">
         <f>IF(BW20="","",BT21*1000+BU21*10+BV21)</f>
-        <v/>
+        <v>2020</v>
       </c>
       <c r="BX21" s="112"/>
       <c r="BY21" s="21"/>
@@ -43967,14 +43999,20 @@
       </c>
       <c r="BL22" s="24" t="str">
         <f>AS38</f>
-        <v>1F</v>
-      </c>
-      <c r="BM22" s="61"/>
-      <c r="BN22" s="63"/>
-      <c r="BO22" s="25"/>
-      <c r="BP22" s="116" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="BM22" s="61">
+        <v>2</v>
+      </c>
+      <c r="BN22" s="63">
+        <v>2</v>
+      </c>
+      <c r="BO22" s="25">
+        <v>5</v>
+      </c>
+      <c r="BP22" s="116">
         <f>IF(OR(BM22="",BM23="",AND(BN22="",BN23&lt;&gt;""),AND(BN23="",BN22&lt;&gt;""),AND(BO22="",BO23&lt;&gt;""),AND(BO23="",BO22&lt;&gt;"")),"",BM22*1000+BN22*10+BO22)</f>
-        <v/>
+        <v>2025</v>
       </c>
       <c r="BQ22" s="112"/>
       <c r="BR22" s="21"/>
@@ -44231,12 +44269,18 @@
         <f>AS21</f>
         <v>Morocco</v>
       </c>
-      <c r="BM23" s="62"/>
-      <c r="BN23" s="64"/>
-      <c r="BO23" s="27"/>
-      <c r="BP23" s="112" t="str">
+      <c r="BM23" s="62">
+        <v>2</v>
+      </c>
+      <c r="BN23" s="64">
+        <v>2</v>
+      </c>
+      <c r="BO23" s="27">
+        <v>3</v>
+      </c>
+      <c r="BP23" s="112">
         <f>IF(BP22="","",BM23*1000+BN23*10+BO23)</f>
-        <v/>
+        <v>2023</v>
       </c>
       <c r="BQ23" s="112"/>
       <c r="BR23" s="21"/>
@@ -44258,14 +44302,16 @@
       </c>
       <c r="CG23" s="24" t="str">
         <f>IF(CD16&gt;CD17,BZ16,IF(CD16&lt;CD17,BZ17,""))</f>
-        <v/>
-      </c>
-      <c r="CH23" s="61"/>
+        <v>France</v>
+      </c>
+      <c r="CH23" s="61">
+        <v>2</v>
+      </c>
       <c r="CI23" s="63"/>
       <c r="CJ23" s="25"/>
-      <c r="CK23" s="112" t="str">
+      <c r="CK23" s="112">
         <f>IF(OR(CH23="",CH24="",AND(CI23="",CI24&lt;&gt;""),AND(CI24="",CI23&lt;&gt;""),AND(CJ23="",CJ24&lt;&gt;""),AND(CJ24="",CJ23&lt;&gt;"")),"",CH23*1000+CI23*10+CJ23)</f>
-        <v/>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" spans="1:95" x14ac:dyDescent="0.25">
@@ -44477,14 +44523,16 @@
       <c r="CF24" s="142"/>
       <c r="CG24" s="26" t="str">
         <f>IF(CD32&gt;CD33,BZ32,IF(CD32&lt;CD33,BZ33,""))</f>
-        <v/>
-      </c>
-      <c r="CH24" s="62"/>
+        <v>Spain</v>
+      </c>
+      <c r="CH24" s="62">
+        <v>1</v>
+      </c>
       <c r="CI24" s="64"/>
       <c r="CJ24" s="27"/>
-      <c r="CK24" s="113" t="str">
+      <c r="CK24" s="113">
         <f>IF(CK23="","",CH24*1000+CI24*10+CJ24)</f>
-        <v/>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:95" x14ac:dyDescent="0.25">
@@ -44717,7 +44765,7 @@
       </c>
       <c r="AG26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE26 &amp; "_lose")</f>
@@ -44725,11 +44773,11 @@
       </c>
       <c r="AI26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE26,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ26" s="123">
         <f>SUMIF($E$7:$E$78,$AE26,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE26,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="123">
         <f>AI26-AJ26</f>
@@ -44737,19 +44785,19 @@
       </c>
       <c r="AM26" s="123">
         <f>AL26-AL30</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" s="123">
         <f>AF26*3+AG26</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" s="123">
         <f>AN26/AN30*10+BA26</f>
-        <v>8.5714285714285712</v>
+        <v>8.75</v>
       </c>
       <c r="AP26" s="123">
         <f>AO26*10000000+BI26*100+AM26/AM30*10+AI26/AI30*1++IF(AQ26=0,ROW(),AQ26)/2000000</f>
-        <v>85714294.548455611</v>
+        <v>87500008.60083656</v>
       </c>
       <c r="AQ26" s="126">
         <f>VLOOKUP(AE26,db_fifarank,2,FALSE)</f>
@@ -44757,11 +44805,11 @@
       </c>
       <c r="AR26" s="125">
         <f>AP26/AP30</f>
-        <v>0.9999999883333347</v>
+        <v>0.9999999885714298</v>
       </c>
       <c r="AS26" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J27,"1D")</f>
-        <v>1D</v>
+        <v>United States</v>
       </c>
       <c r="AT26" s="126" cm="1">
         <f t="array" ref="AT26">SUMPRODUCT(($S$7:$S$78=AE26&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE26&amp;"_win")*($U$7:$U$78))</f>
@@ -44832,14 +44880,16 @@
       </c>
       <c r="BL26" s="24" t="str">
         <f>AS69</f>
-        <v>2K</v>
-      </c>
-      <c r="BM26" s="61"/>
+        <v>Colombia</v>
+      </c>
+      <c r="BM26" s="61">
+        <v>2</v>
+      </c>
       <c r="BN26" s="63"/>
       <c r="BO26" s="25"/>
-      <c r="BP26" s="112" t="str">
+      <c r="BP26" s="112">
         <f>IF(OR(BM26="",BM27="",AND(BN26="",BN27&lt;&gt;""),AND(BN27="",BN26&lt;&gt;""),AND(BO26="",BO27&lt;&gt;""),AND(BO27="",BO26&lt;&gt;"")),"",BM26*1000+BN26*10+BO26)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ26" s="112"/>
       <c r="BR26" s="21"/>
@@ -44905,7 +44955,7 @@
       </c>
       <c r="K27" s="31">
         <f>L27+M27+N27</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="31">
         <f>VLOOKUP(1,AD26:AN29,3,FALSE)</f>
@@ -44913,7 +44963,7 @@
       </c>
       <c r="M27" s="31">
         <f>VLOOKUP(1,AD26:AN29,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="31">
         <f>VLOOKUP(1,AD26:AN29,5,FALSE)</f>
@@ -44921,11 +44971,11 @@
       </c>
       <c r="O27" s="31" t="str">
         <f>VLOOKUP(1,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD26:AN29,7,FALSE)</f>
-        <v>2 - 0</v>
+        <v>3 - 1</v>
       </c>
       <c r="P27" s="32">
         <f>L27*3+M27</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R27" s="123">
         <f>DATE(2026,6,17)+TIME(12,0,0)+gmt_delta</f>
@@ -44973,7 +45023,7 @@
       </c>
       <c r="AD27" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR27))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" s="124" t="str">
         <f>VLOOKUP("Paraguay",T,lang,FALSE)</f>
@@ -44989,7 +45039,7 @@
       </c>
       <c r="AH27" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE27 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE27,$G$7:$G$78)</f>
@@ -44997,15 +45047,15 @@
       </c>
       <c r="AJ27" s="123">
         <f>SUMIF($E$7:$E$78,$AE27,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE27,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL27" s="123">
         <f>AI27-AJ27</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM27" s="123">
         <f>AL27-AL30</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="123">
         <f>AF27*3+AG27</f>
@@ -45013,11 +45063,11 @@
       </c>
       <c r="AO27" s="123">
         <f>AN27/AN30*10+BA27</f>
-        <v>1.4285714285714284</v>
+        <v>1.25</v>
       </c>
       <c r="AP27" s="123">
         <f>AO27*10000000+BI27*100+AM27/AM30*10+AI27/AI30*1++IF(AQ27=0,ROW(),AQ27)/2000000</f>
-        <v>14285717.869799368</v>
+        <v>12500000.20075175</v>
       </c>
       <c r="AQ27" s="126">
         <f>VLOOKUP(AE27,db_fifarank,2,FALSE)</f>
@@ -45025,11 +45075,11 @@
       </c>
       <c r="AR27" s="125">
         <f>AP27/AP30</f>
-        <v>0.16666668935899301</v>
+        <v>0.14285712947661483</v>
       </c>
       <c r="AS27" s="125" t="str">
         <f>IF(SUM(AF26:AH29)=12,J28,"2D")</f>
-        <v>2D</v>
+        <v>Turkey</v>
       </c>
       <c r="AT27" s="126" cm="1">
         <f t="array" ref="AT27">SUMPRODUCT(($S$7:$S$78=AE27&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE27&amp;"_win")*($U$7:$U$78))</f>
@@ -45098,14 +45148,16 @@
       <c r="BK27" s="142"/>
       <c r="BL27" s="26" t="str">
         <f>AS75</f>
-        <v>2L</v>
-      </c>
-      <c r="BM27" s="62"/>
+        <v>Croatia</v>
+      </c>
+      <c r="BM27" s="62">
+        <v>3</v>
+      </c>
       <c r="BN27" s="64"/>
       <c r="BO27" s="27"/>
-      <c r="BP27" s="113" t="str">
+      <c r="BP27" s="113">
         <f>IF(BP26="","",BM27*1000+BN27*10+BO27)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ27" s="112"/>
       <c r="BR27" s="21" t="str" cm="1">
@@ -45177,7 +45229,7 @@
       </c>
       <c r="K28" s="23">
         <f>L28+M28+N28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="23">
         <f>VLOOKUP(2,AD26:AN29,3,FALSE)</f>
@@ -45185,7 +45237,7 @@
       </c>
       <c r="M28" s="23">
         <f>VLOOKUP(2,AD26:AN29,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="23">
         <f>VLOOKUP(2,AD26:AN29,5,FALSE)</f>
@@ -45193,11 +45245,11 @@
       </c>
       <c r="O28" s="23" t="str">
         <f>VLOOKUP(2,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD26:AN29,7,FALSE)</f>
-        <v>3 - 1</v>
+        <v>4 - 2</v>
       </c>
       <c r="P28" s="34">
         <f>L28*3+M28</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R28" s="123">
         <f>DATE(2026,6,17)+TIME(9,0,0)+gmt_delta</f>
@@ -45245,7 +45297,7 @@
       </c>
       <c r="AD28" s="123">
         <f>COUNTIF(AR26:AR29,CONCATENATE("&gt;=",AR28))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE28" s="124" t="str">
         <f>VLOOKUP("Australia",T,lang,FALSE)</f>
@@ -45253,7 +45305,7 @@
       </c>
       <c r="AF28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE28 &amp; "_draw")</f>
@@ -45265,7 +45317,7 @@
       </c>
       <c r="AI28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE28,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" s="123">
         <f>SUMIF($E$7:$E$78,$AE28,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE28,$F$7:$F$78)</f>
@@ -45273,7 +45325,7 @@
       </c>
       <c r="AL28" s="123">
         <f>AI28-AJ28</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM28" s="123">
         <f>AL28-AL30</f>
@@ -45281,15 +45333,15 @@
       </c>
       <c r="AN28" s="123">
         <f>AF28*3+AG28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO28" s="123">
         <f>AN28/AN30*10+BA28</f>
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AP28" s="123">
         <f>AO28*10000000+BI28*100+AM28/AM30*10+AI28/AI30*1++IF(AQ28=0,ROW(),AQ28)/2000000</f>
-        <v>7.9033500000000008E-4</v>
+        <v>37500000.200790338</v>
       </c>
       <c r="AQ28" s="126">
         <f>VLOOKUP(AE28,db_fifarank,2,FALSE)</f>
@@ -45297,7 +45349,7 @@
       </c>
       <c r="AR28" s="125">
         <f>AP28/AP30</f>
-        <v>9.2205739421052768E-12</v>
+        <v>0.42857138384167459</v>
       </c>
       <c r="AT28" s="126" cm="1">
         <f t="array" ref="AT28">SUMPRODUCT(($S$7:$S$78=AE28&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE28&amp;"_win")*($U$7:$U$78))</f>
@@ -45375,14 +45427,16 @@
       </c>
       <c r="BS28" s="24" t="str">
         <f>IF(BP26&gt;BP27,BL26,IF(BP26&lt;BP27,BL27,""))</f>
-        <v/>
-      </c>
-      <c r="BT28" s="61"/>
+        <v>Croatia</v>
+      </c>
+      <c r="BT28" s="61">
+        <v>0</v>
+      </c>
       <c r="BU28" s="63"/>
       <c r="BV28" s="25"/>
-      <c r="BW28" s="112" t="str">
+      <c r="BW28" s="112">
         <f>IF(OR(BT28="",BT29="",AND(BU28="",BU29&lt;&gt;""),AND(BU29="",BU28&lt;&gt;""),AND(BV28="",BV29&lt;&gt;""),AND(BV29="",BV28&lt;&gt;"")),"",BT28*1000+BU28*10+BV28)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX28" s="112"/>
       <c r="BY28" s="21"/>
@@ -45432,31 +45486,31 @@
       </c>
       <c r="J29" s="33" t="str">
         <f>VLOOKUP(3,AD26:AN29,2,FALSE)</f>
-        <v>Paraguay</v>
+        <v>Australia</v>
       </c>
       <c r="K29" s="23">
         <f>L29+M29+N29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="23">
         <f>VLOOKUP(3,AD26:AN29,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="23">
         <f>VLOOKUP(3,AD26:AN29,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="23">
         <f>VLOOKUP(3,AD26:AN29,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="23" t="str">
         <f>VLOOKUP(3,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD26:AN29,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>1 - 3</v>
       </c>
       <c r="P29" s="34">
         <f>L29*3+M29</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29" s="123">
         <f>DATE(2026,6,17)+TIME(6,0,0)+gmt_delta</f>
@@ -45516,7 +45570,7 @@
       </c>
       <c r="AG29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE29 &amp; "_lose")</f>
@@ -45524,11 +45578,11 @@
       </c>
       <c r="AI29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE29,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ29" s="123">
         <f>SUMIF($E$7:$E$78,$AE29,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE29,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL29" s="123">
         <f>AI29-AJ29</f>
@@ -45536,19 +45590,19 @@
       </c>
       <c r="AM29" s="123">
         <f>AL29-AL30</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN29" s="123">
         <f>AF29*3+AG29</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO29" s="123">
         <f>AN29/AN30*10+BA29</f>
-        <v>5.7142857142857135</v>
+        <v>6.25</v>
       </c>
       <c r="AP29" s="123">
         <f>AO29*10000000+BI29*100+AM29/AM30*10+AI29/AI30*1++IF(AQ29=0,ROW(),AQ29)/2000000</f>
-        <v>57142866.226989992</v>
+        <v>62500008.800799519</v>
       </c>
       <c r="AQ29" s="126">
         <f>VLOOKUP(AE29,db_fifarank,2,FALSE)</f>
@@ -45556,7 +45610,7 @@
       </c>
       <c r="AR29" s="125">
         <f>AP29/AP30</f>
-        <v>0.66666669616022511</v>
+        <v>0.71428573649210181</v>
       </c>
       <c r="AT29" s="126" cm="1">
         <f t="array" ref="AT29">SUMPRODUCT(($S$7:$S$78=AE29&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE29&amp;"_win")*($U$7:$U$78))</f>
@@ -45638,14 +45692,16 @@
       <c r="BR29" s="142"/>
       <c r="BS29" s="26" t="str">
         <f>IF(BP30&gt;BP31,BL30,IF(BP30&lt;BP31,BL31,""))</f>
-        <v/>
-      </c>
-      <c r="BT29" s="62"/>
+        <v>Spain</v>
+      </c>
+      <c r="BT29" s="62">
+        <v>2</v>
+      </c>
       <c r="BU29" s="64"/>
       <c r="BV29" s="27"/>
-      <c r="BW29" s="113" t="str">
+      <c r="BW29" s="113">
         <f>IF(BW28="","",BT29*1000+BU29*10+BV29)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BX29" s="112"/>
       <c r="BY29" s="21"/>
@@ -45695,11 +45751,11 @@
       </c>
       <c r="J30" s="35" t="str">
         <f>VLOOKUP(4,AD26:AN29,2,FALSE)</f>
-        <v>Australia</v>
+        <v>Paraguay</v>
       </c>
       <c r="K30" s="36">
         <f>L30+M30+N30</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="36">
         <f>VLOOKUP(4,AD26:AN29,3,FALSE)</f>
@@ -45707,7 +45763,7 @@
       </c>
       <c r="M30" s="36">
         <f>VLOOKUP(4,AD26:AN29,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="36">
         <f>VLOOKUP(4,AD26:AN29,5,FALSE)</f>
@@ -45715,11 +45771,11 @@
       </c>
       <c r="O30" s="36" t="str">
         <f>VLOOKUP(4,AD26:AN29,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD26:AN29,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>1 - 3</v>
       </c>
       <c r="P30" s="37">
         <f>L30*3+M30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="123">
         <f>DATE(2026,6,17)+TIME(15,0,0)+gmt_delta</f>
@@ -45771,7 +45827,7 @@
       </c>
       <c r="AG30" s="123">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30" s="123">
         <f t="shared" si="15"/>
@@ -45779,27 +45835,27 @@
       </c>
       <c r="AI30" s="123">
         <f>MAX(AI26:AI29)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL30" s="123">
         <f>MIN(AL26:AL29)</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AM30" s="123">
         <f>MAX(AM26:AM29)+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN30" s="123">
         <f>MAX(AN26:AN29)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO30" s="123">
         <f>MAX(AO26:AO29)+1</f>
-        <v>9.5714285714285712</v>
+        <v>9.75</v>
       </c>
       <c r="AP30" s="123">
         <f>MAX(AP26:AP29)+1</f>
-        <v>85714295.548455611</v>
+        <v>87500009.60083656</v>
       </c>
       <c r="AT30" s="126">
         <f>MAX(AT26:AT29)-MIN(AT26:AT29)+1</f>
@@ -45854,14 +45910,16 @@
       </c>
       <c r="BL30" s="24" t="str">
         <f>AS50</f>
-        <v>1H</v>
-      </c>
-      <c r="BM30" s="61"/>
+        <v>Spain</v>
+      </c>
+      <c r="BM30" s="61">
+        <v>2</v>
+      </c>
       <c r="BN30" s="63"/>
       <c r="BO30" s="25"/>
-      <c r="BP30" s="116" t="str">
+      <c r="BP30" s="116">
         <f>IF(OR(BM30="",BM31="",AND(BN30="",BN31&lt;&gt;""),AND(BN31="",BN30&lt;&gt;""),AND(BO30="",BO31&lt;&gt;""),AND(BO31="",BO30&lt;&gt;"")),"",BM30*1000+BN30*10+BO30)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ30" s="112"/>
       <c r="BR30" s="21"/>
@@ -45963,14 +46021,16 @@
       <c r="BK31" s="142"/>
       <c r="BL31" s="26" t="str">
         <f>AS63</f>
-        <v>2J</v>
-      </c>
-      <c r="BM31" s="62"/>
+        <v>Algeria</v>
+      </c>
+      <c r="BM31" s="62">
+        <v>0</v>
+      </c>
       <c r="BN31" s="64"/>
       <c r="BO31" s="27"/>
-      <c r="BP31" s="112" t="str">
+      <c r="BP31" s="112">
         <f>IF(BP30="","",BM31*1000+BN31*10+BO31)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ31" s="112"/>
       <c r="BR31" s="21"/>
@@ -46108,7 +46168,7 @@
       </c>
       <c r="AF32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG32" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE32 &amp; "_draw")</f>
@@ -46120,31 +46180,31 @@
       </c>
       <c r="AI32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE32,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ32" s="123">
         <f>SUMIF($E$7:$E$78,$AE32,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE32,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL32" s="123">
         <f>AI32-AJ32</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM32" s="123">
         <f>AL32-AL36</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN32" s="123">
         <f>AF32*3+AG32</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO32" s="123">
         <f>AN32/AN36*10+BA32</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP32" s="123">
         <f>AO32*10000000+BI32*100+AM32/AM36*10+AI32/AI36*1++IF(AQ32=0,ROW(),AQ32)/2000000</f>
-        <v>85714295.548484236</v>
+        <v>90000010.056420758</v>
       </c>
       <c r="AQ32" s="126">
         <f>VLOOKUP(AE32,db_fifarank,2,FALSE)</f>
@@ -46152,11 +46212,11 @@
       </c>
       <c r="AR32" s="125">
         <f>AP32/AP36</f>
-        <v>0.99999998833333481</v>
+        <v>0.9999999888888903</v>
       </c>
       <c r="AS32" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J33,"1E")</f>
-        <v>1E</v>
+        <v>Germany</v>
       </c>
       <c r="AT32" s="126" cm="1">
         <f t="array" ref="AT32">SUMPRODUCT(($S$7:$S$78=AE32&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE32&amp;"_win")*($U$7:$U$78))</f>
@@ -46241,14 +46301,16 @@
       </c>
       <c r="BZ32" s="24" t="str">
         <f>IF(BW28&gt;BW29,BS28,IF(BW28&lt;BW29,BS29,""))</f>
-        <v/>
-      </c>
-      <c r="CA32" s="61"/>
+        <v>Spain</v>
+      </c>
+      <c r="CA32" s="61">
+        <v>2</v>
+      </c>
       <c r="CB32" s="63"/>
       <c r="CC32" s="25"/>
-      <c r="CD32" s="116" t="str">
+      <c r="CD32" s="116">
         <f>IF(OR(CA32="",CA33="",AND(CB32="",CB33&lt;&gt;""),AND(CB33="",CB32&lt;&gt;""),AND(CC32="",CC33&lt;&gt;""),AND(CC33="",CC32&lt;&gt;"")),"",CA32*1000+CB32*10+CC32)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CE32" s="112"/>
       <c r="CK32" s="114"/>
@@ -46290,11 +46352,11 @@
       </c>
       <c r="K33" s="31">
         <f>L33+M33+N33</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="31">
         <f>VLOOKUP(1,AD32:AN35,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M33" s="31">
         <f>VLOOKUP(1,AD32:AN35,4,FALSE)</f>
@@ -46306,11 +46368,11 @@
       </c>
       <c r="O33" s="31" t="str">
         <f>VLOOKUP(1,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD32:AN35,7,FALSE)</f>
-        <v>5 - 1</v>
+        <v>8 - 2</v>
       </c>
       <c r="P33" s="32">
         <f>L33*3+M33</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R33" s="123">
         <f>DATE(2026,6,18)+TIME(11,0,0)+gmt_delta</f>
@@ -46370,7 +46432,7 @@
       </c>
       <c r="AG33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE33 &amp; "_lose")</f>
@@ -46378,11 +46440,11 @@
       </c>
       <c r="AI33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE33,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="123">
         <f>SUMIF($E$7:$E$78,$AE33,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE33,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL33" s="123">
         <f>AI33-AJ33</f>
@@ -46394,15 +46456,15 @@
       </c>
       <c r="AN33" s="123">
         <f>AF33*3+AG33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" s="123">
         <f>AN33/AN36*10+BA33</f>
-        <v>0</v>
+        <v>1.9805825242718447</v>
       </c>
       <c r="AP33" s="123">
         <f>AO33*10000000+BI33*100+AM33/AM36*10+AI33/AI36*1++IF(AQ33=0,ROW(),AQ33)/2000000</f>
-        <v>6.4732500000000003E-4</v>
+        <v>19805923.412729312</v>
       </c>
       <c r="AQ33" s="126">
         <f>VLOOKUP(AE33,db_fifarank,2,FALSE)</f>
@@ -46410,11 +46472,11 @@
       </c>
       <c r="AR33" s="125">
         <f>AP33/AP36</f>
-        <v>7.5521240454192037E-12</v>
+        <v>0.22006578866210397</v>
       </c>
       <c r="AS33" s="125" t="str">
         <f>IF(SUM(AF32:AH35)=12,J34,"2E")</f>
-        <v>2E</v>
+        <v>Ecuador</v>
       </c>
       <c r="AT33" s="126" cm="1">
         <f t="array" ref="AT33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($U$7:$U$78))</f>
@@ -46422,15 +46484,15 @@
       </c>
       <c r="AU33" s="126" cm="1">
         <f t="array" ref="AU33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV33" s="126" cm="1">
         <f t="array" ref="AV33">SUMPRODUCT(($E$7:$E$78=AE33)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW33" s="126" cm="1">
         <f t="array" ref="AW33">SUMPRODUCT(($E$7:$E$78=AE33)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" s="126">
         <f>AV33-AW33</f>
@@ -46442,11 +46504,11 @@
       </c>
       <c r="AZ33" s="126">
         <f>AT33/AT36*1000+AU33/AU36*100+AY33/AY36*10+AV33/AV36</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA33" s="126">
         <f>AZ33/AZ36</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB33" s="126" cm="1">
         <f t="array" ref="BB33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_win")*($X$7:$X$78))</f>
@@ -46454,15 +46516,15 @@
       </c>
       <c r="BC33" s="126" cm="1">
         <f t="array" ref="BC33">SUMPRODUCT(($S$7:$S$78=AE33&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE33&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD33" s="126" cm="1">
         <f t="array" ref="BD33">SUMPRODUCT(($E$7:$E$78=AE33)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE33" s="126" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(($E$7:$E$78=AE33)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE33)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF33" s="126">
         <f>BD33-BE33</f>
@@ -46474,11 +46536,11 @@
       </c>
       <c r="BH33" s="126">
         <f>BB33/BB36*1000+BC33/BC36*100+BG33/BG36*10+BD33/BD36</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI33" s="126">
         <f>BH33/BH36</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK33" s="21" t="str" cm="1">
         <f t="array" ref="BK33">INDEX(T,24+MONTH(BP33),lang) &amp; " " &amp; DAY(BP33) &amp; ", " &amp; YEAR(BP33) &amp; "   " &amp; (IF(HOUR(BP33)&lt;10,0,"")&amp;HOUR(BP33)) &amp; ":" &amp;  (IF(MINUTE(BP33)&lt;10,0,"")&amp;MINUTE(BP33))</f>
@@ -46503,14 +46565,16 @@
       <c r="BY33" s="142"/>
       <c r="BZ33" s="26" t="str">
         <f>IF(BW36&gt;BW37,BS36,IF(BW36&lt;BW37,BS37,""))</f>
-        <v/>
-      </c>
-      <c r="CA33" s="62"/>
+        <v>Belgium</v>
+      </c>
+      <c r="CA33" s="62">
+        <v>0</v>
+      </c>
       <c r="CB33" s="64"/>
       <c r="CC33" s="27"/>
-      <c r="CD33" s="112" t="str">
+      <c r="CD33" s="112">
         <f>IF(CD32="","",CA33*1000+CB33*10+CC33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE33" s="112"/>
       <c r="CK33" s="114"/>
@@ -46560,7 +46624,7 @@
       </c>
       <c r="K34" s="23">
         <f>L34+M34+N34</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="23">
         <f>VLOOKUP(2,AD32:AN35,3,FALSE)</f>
@@ -46572,11 +46636,11 @@
       </c>
       <c r="N34" s="23">
         <f>VLOOKUP(2,AD32:AN35,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="23" t="str">
         <f>VLOOKUP(2,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD32:AN35,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>5 - 4</v>
       </c>
       <c r="P34" s="34">
         <f>L34*3+M34</f>
@@ -46640,7 +46704,7 @@
       </c>
       <c r="AG34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH34" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE34 &amp; "_lose")</f>
@@ -46648,11 +46712,11 @@
       </c>
       <c r="AI34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE34,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ34" s="123">
         <f>SUMIF($E$7:$E$78,$AE34,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE34,$F$7:$F$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL34" s="123">
         <f>AI34-AJ34</f>
@@ -46664,15 +46728,15 @@
       </c>
       <c r="AN34" s="123">
         <f>AF34*3+AG34</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" s="123">
         <f>AN34/AN36*10+BA34</f>
-        <v>0</v>
+        <v>1.9805825242718447</v>
       </c>
       <c r="AP34" s="123">
         <f>AO34*10000000+BI34*100+AM34/AM36*10+AI34/AI36*1++IF(AQ34=0,ROW(),AQ34)/2000000</f>
-        <v>3.3340998233333337</v>
+        <v>19805926.135070696</v>
       </c>
       <c r="AQ34" s="126">
         <f>VLOOKUP(AE34,db_fifarank,2,FALSE)</f>
@@ -46680,7 +46744,7 @@
       </c>
       <c r="AR34" s="125">
         <f>AP34/AP36</f>
-        <v>3.8897826355576543E-8</v>
+        <v>0.22006581891033786</v>
       </c>
       <c r="AT34" s="126" cm="1">
         <f t="array" ref="AT34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($U$7:$U$78))</f>
@@ -46688,15 +46752,15 @@
       </c>
       <c r="AU34" s="126" cm="1">
         <f t="array" ref="AU34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV34" s="126" cm="1">
         <f t="array" ref="AV34">SUMPRODUCT(($E$7:$E$78=AE34)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW34" s="126" cm="1">
         <f t="array" ref="AW34">SUMPRODUCT(($E$7:$E$78=AE34)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" s="126">
         <f>AV34-AW34</f>
@@ -46708,11 +46772,11 @@
       </c>
       <c r="AZ34" s="126">
         <f>AT34/AT36*1000+AU34/AU36*100+AY34/AY36*10+AV34/AV36</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA34" s="126">
         <f>AZ34/AZ36</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB34" s="126" cm="1">
         <f t="array" ref="BB34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_win")*($X$7:$X$78))</f>
@@ -46720,15 +46784,15 @@
       </c>
       <c r="BC34" s="126" cm="1">
         <f t="array" ref="BC34">SUMPRODUCT(($S$7:$S$78=AE34&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE34&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD34" s="126" cm="1">
         <f t="array" ref="BD34">SUMPRODUCT(($E$7:$E$78=AE34)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE34" s="126" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(($E$7:$E$78=AE34)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE34)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF34" s="126">
         <f>BD34-BE34</f>
@@ -46740,25 +46804,29 @@
       </c>
       <c r="BH34" s="126">
         <f>BB34/BB36*1000+BC34/BC36*100+BG34/BG36*10+BD34/BD36</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI34" s="126">
         <f>BH34/BH36</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK34" s="141">
         <v>81</v>
       </c>
       <c r="BL34" s="24" t="str">
         <f>AS26</f>
-        <v>1D</v>
-      </c>
-      <c r="BM34" s="61"/>
-      <c r="BN34" s="63"/>
+        <v>United States</v>
+      </c>
+      <c r="BM34" s="61">
+        <v>1</v>
+      </c>
+      <c r="BN34" s="63">
+        <v>2</v>
+      </c>
       <c r="BO34" s="25"/>
-      <c r="BP34" s="112" t="str">
+      <c r="BP34" s="112">
         <f>IF(OR(BM34="",BM35="",AND(BN34="",BN35&lt;&gt;""),AND(BN35="",BN34&lt;&gt;""),AND(BO34="",BO35&lt;&gt;""),AND(BO35="",BO34&lt;&gt;"")),"",BM34*1000+BN34*10+BO34)</f>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="BQ34" s="112"/>
       <c r="BR34" s="21"/>
@@ -46819,7 +46887,7 @@
       </c>
       <c r="K35" s="23">
         <f>L35+M35+N35</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="23">
         <f>VLOOKUP(3,AD32:AN35,3,FALSE)</f>
@@ -46827,7 +46895,7 @@
       </c>
       <c r="M35" s="23">
         <f>VLOOKUP(3,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="23">
         <f>VLOOKUP(3,AD32:AN35,5,FALSE)</f>
@@ -46835,11 +46903,11 @@
       </c>
       <c r="O35" s="23" t="str">
         <f>VLOOKUP(3,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD32:AN35,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>3 - 5</v>
       </c>
       <c r="P35" s="34">
         <f>L35*3+M35</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="123">
         <f>DATE(2026,6,19)+TIME(13,30,0)+gmt_delta</f>
@@ -46903,23 +46971,23 @@
       </c>
       <c r="AH35" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE35 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE35,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ35" s="123">
         <f>SUMIF($E$7:$E$78,$AE35,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE35,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL35" s="123">
         <f>AI35-AJ35</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM35" s="123">
         <f>AL35-AL36</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN35" s="123">
         <f>AF35*3+AG35</f>
@@ -46927,11 +46995,11 @@
       </c>
       <c r="AO35" s="123">
         <f>AN35/AN36*10+BA35</f>
-        <v>8.5714285714285712</v>
+        <v>6</v>
       </c>
       <c r="AP35" s="123">
         <f>AO35*10000000+BI35*100+AM35/AM36*10+AI35/AI36*1++IF(AQ35=0,ROW(),AQ35)/2000000</f>
-        <v>85714294.381749779</v>
+        <v>60000005.556352943</v>
       </c>
       <c r="AQ35" s="126">
         <f>VLOOKUP(AE35,db_fifarank,2,FALSE)</f>
@@ -46939,7 +47007,7 @@
       </c>
       <c r="AR35" s="125">
         <f>AP35/AP36</f>
-        <v>0.99999997472143454</v>
+        <v>0.66666664650451102</v>
       </c>
       <c r="AT35" s="126" cm="1">
         <f t="array" ref="AT35">SUMPRODUCT(($S$7:$S$78=AE35&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE35&amp;"_win")*($U$7:$U$78))</f>
@@ -47008,14 +47076,18 @@
       <c r="BK35" s="142"/>
       <c r="BL35" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!F3,AK80:AS91,9,FALSE),"3rd Group B/E/F/I/J")</f>
-        <v>3rd Group B/E/F/I/J</v>
-      </c>
-      <c r="BM35" s="62"/>
-      <c r="BN35" s="64"/>
+        <v>Bosnia and Herzegovina</v>
+      </c>
+      <c r="BM35" s="62">
+        <v>1</v>
+      </c>
+      <c r="BN35" s="64">
+        <v>1</v>
+      </c>
       <c r="BO35" s="27"/>
-      <c r="BP35" s="113" t="str">
+      <c r="BP35" s="113">
         <f>IF(BP34="","",BM35*1000+BN35*10+BO35)</f>
-        <v/>
+        <v>1010</v>
       </c>
       <c r="BQ35" s="112"/>
       <c r="BR35" s="21" t="str" cm="1">
@@ -47077,7 +47149,7 @@
       </c>
       <c r="K36" s="36">
         <f>L36+M36+N36</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="36">
         <f>VLOOKUP(4,AD32:AN35,3,FALSE)</f>
@@ -47085,7 +47157,7 @@
       </c>
       <c r="M36" s="36">
         <f>VLOOKUP(4,AD32:AN35,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="36">
         <f>VLOOKUP(4,AD32:AN35,5,FALSE)</f>
@@ -47093,11 +47165,11 @@
       </c>
       <c r="O36" s="36" t="str">
         <f>VLOOKUP(4,AD32:AN35,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD32:AN35,7,FALSE)</f>
-        <v>0 - 5</v>
+        <v>1 - 6</v>
       </c>
       <c r="P36" s="37">
         <f>L36*3+M36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="123">
         <f>DATE(2026,6,19)+TIME(11,0,0)+gmt_delta</f>
@@ -47145,11 +47217,11 @@
       </c>
       <c r="AF36" s="123">
         <f t="shared" ref="AF36:AH36" si="16">MAX(AF32:AF35)-MIN(AF32:AF35)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG36" s="123">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH36" s="123">
         <f t="shared" si="16"/>
@@ -47157,7 +47229,7 @@
       </c>
       <c r="AI36" s="123">
         <f>MAX(AI32:AI35)+1</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL36" s="123">
         <f>MIN(AL32:AL35)</f>
@@ -47165,19 +47237,19 @@
       </c>
       <c r="AM36" s="123">
         <f>MAX(AM32:AM35)+1</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN36" s="123">
         <f>MAX(AN32:AN35)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO36" s="123">
         <f>MAX(AO32:AO35)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP36" s="123">
         <f>MAX(AP32:AP35)+1</f>
-        <v>85714296.548484236</v>
+        <v>90000011.056420758</v>
       </c>
       <c r="AT36" s="126">
         <f>MAX(AT32:AT35)-MIN(AT32:AT35)+1</f>
@@ -47185,15 +47257,15 @@
       </c>
       <c r="AU36" s="126">
         <f>MAX(AU32:AU35)-MIN(AU32:AU35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV36" s="126">
         <f>MAX(AV32:AV35)-MIN(AV32:AV35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW36" s="126">
         <f>MAX(AW32:AW35)-MIN(AW32:AW35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY36" s="126">
         <f>MAX(AY32:AY35)-MIN(AY32:AY35)+1</f>
@@ -47201,7 +47273,7 @@
       </c>
       <c r="AZ36" s="126">
         <f>MAX(AZ32:AZ35)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB36" s="126">
         <f>MAX(BB32:BB35)-MIN(BB32:BB35)+1</f>
@@ -47209,15 +47281,15 @@
       </c>
       <c r="BC36" s="126">
         <f>MAX(BC32:BC35)-MIN(BC32:BC35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD36" s="126">
         <f>MAX(BD32:BD35)-MIN(BD32:BD35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE36" s="126">
         <f>MAX(BE32:BE35)-MIN(BE32:BE35)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG36" s="126">
         <f>MAX(BG32:BG35)-MIN(BG32:BG35)+1</f>
@@ -47225,7 +47297,7 @@
       </c>
       <c r="BH36" s="126">
         <f>MAX(BH32:BH35)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BK36" s="21"/>
       <c r="BL36" s="21"/>
@@ -47239,14 +47311,18 @@
       </c>
       <c r="BS36" s="24" t="str">
         <f>IF(BP34&gt;BP35,BL34,IF(BP34&lt;BP35,BL35,""))</f>
-        <v/>
-      </c>
-      <c r="BT36" s="61"/>
-      <c r="BU36" s="63"/>
+        <v>United States</v>
+      </c>
+      <c r="BT36" s="61">
+        <v>1</v>
+      </c>
+      <c r="BU36" s="63">
+        <v>1</v>
+      </c>
       <c r="BV36" s="25"/>
-      <c r="BW36" s="116" t="str">
+      <c r="BW36" s="116">
         <f>IF(OR(BT36="",BT37="",AND(BU36="",BU37&lt;&gt;""),AND(BU37="",BU36&lt;&gt;""),AND(BV36="",BV37&lt;&gt;""),AND(BV37="",BV36&lt;&gt;"")),"",BT36*1000+BU36*10+BV36)</f>
-        <v/>
+        <v>1010</v>
       </c>
       <c r="BX36" s="112"/>
       <c r="BY36" s="21"/>
@@ -47361,14 +47437,18 @@
       <c r="BR37" s="142"/>
       <c r="BS37" s="26" t="str">
         <f>IF(BP38&gt;BP39,BL38,IF(BP38&lt;BP39,BL39,""))</f>
-        <v/>
-      </c>
-      <c r="BT37" s="62"/>
-      <c r="BU37" s="64"/>
+        <v>Belgium</v>
+      </c>
+      <c r="BT37" s="62">
+        <v>1</v>
+      </c>
+      <c r="BU37" s="64">
+        <v>2</v>
+      </c>
       <c r="BV37" s="27"/>
-      <c r="BW37" s="112" t="str">
+      <c r="BW37" s="112">
         <f>IF(BW36="","",BT37*1000+BU37*10+BV37)</f>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="BX37" s="112"/>
       <c r="BY37" s="21"/>
@@ -47390,14 +47470,18 @@
       </c>
       <c r="CN37" s="24" t="str">
         <f>IF(CK23&gt;CK24,CG23,IF(CK23&lt;CK24,CG24,""))</f>
-        <v/>
-      </c>
-      <c r="CO37" s="61"/>
-      <c r="CP37" s="63"/>
+        <v>France</v>
+      </c>
+      <c r="CO37" s="61">
+        <v>2</v>
+      </c>
+      <c r="CP37" s="63">
+        <v>2</v>
+      </c>
       <c r="CQ37" s="25"/>
-      <c r="CR37" s="111" t="str">
+      <c r="CR37" s="111">
         <f>IF(OR(CO37="",CO38="",AND(CP37="",CP38&lt;&gt;""),AND(CP38="",CP37&lt;&gt;""),AND(CQ37="",CQ38&lt;&gt;""),AND(CQ38="",CQ37&lt;&gt;"")),"",CO37*1000+CP37*10+CQ37)</f>
-        <v/>
+        <v>2020</v>
       </c>
     </row>
     <row r="38" spans="1:96" x14ac:dyDescent="0.25">
@@ -47516,7 +47600,7 @@
       </c>
       <c r="AG38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE38 &amp; "_lose")</f>
@@ -47540,15 +47624,15 @@
       </c>
       <c r="AN38" s="123">
         <f>AF38*3+AG38</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO38" s="123">
         <f>AN38/AN42*10+BA38</f>
-        <v>8.5714285714285712</v>
+        <v>8.75</v>
       </c>
       <c r="AP38" s="123">
         <f>AO38*10000000+BI38*100+AM38/AM42*10+AI38/AI42*1++IF(AQ38=0,ROW(),AQ38)/2000000</f>
-        <v>85714293.965164647</v>
+        <v>87500008.100878924</v>
       </c>
       <c r="AQ38" s="126">
         <f>VLOOKUP(AE38,db_fifarank,2,FALSE)</f>
@@ -47556,11 +47640,11 @@
       </c>
       <c r="AR38" s="125">
         <f>AP38/AP42</f>
-        <v>0.99999998833333459</v>
+        <v>0.9999999885714298</v>
       </c>
       <c r="AS38" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J39,"1F")</f>
-        <v>1F</v>
+        <v>Netherlands</v>
       </c>
       <c r="AT38" s="126" cm="1">
         <f t="array" ref="AT38">SUMPRODUCT(($S$7:$S$78=AE38&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE38&amp;"_win")*($U$7:$U$78))</f>
@@ -47631,14 +47715,16 @@
       </c>
       <c r="BL38" s="24" t="str">
         <f>AS44</f>
-        <v>1G</v>
-      </c>
-      <c r="BM38" s="61"/>
+        <v>Belgium</v>
+      </c>
+      <c r="BM38" s="61">
+        <v>3</v>
+      </c>
       <c r="BN38" s="63"/>
       <c r="BO38" s="25"/>
-      <c r="BP38" s="116" t="str">
+      <c r="BP38" s="116">
         <f>IF(OR(BM38="",BM39="",AND(BN38="",BN39&lt;&gt;""),AND(BN39="",BN38&lt;&gt;""),AND(BO38="",BO39&lt;&gt;""),AND(BO39="",BO38&lt;&gt;"")),"",BM38*1000+BN38*10+BO38)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ38" s="112"/>
       <c r="BW38" s="112"/>
@@ -47659,14 +47745,18 @@
       <c r="CM38" s="142"/>
       <c r="CN38" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG55,IF(CK55&lt;CK56,CG56,""))</f>
-        <v/>
-      </c>
-      <c r="CO38" s="62"/>
-      <c r="CP38" s="64"/>
+        <v>Senegal</v>
+      </c>
+      <c r="CO38" s="62">
+        <v>2</v>
+      </c>
+      <c r="CP38" s="64">
+        <v>3</v>
+      </c>
       <c r="CQ38" s="27"/>
-      <c r="CR38" s="111" t="str">
+      <c r="CR38" s="111">
         <f>IF(CR37="","",CO38*1000+CP38*10+CQ38)</f>
-        <v/>
+        <v>2030</v>
       </c>
     </row>
     <row r="39" spans="1:96" x14ac:dyDescent="0.25">
@@ -47705,7 +47795,7 @@
       </c>
       <c r="K39" s="31">
         <f>L39+M39+N39</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="31">
         <f>VLOOKUP(1,AD38:AN41,3,FALSE)</f>
@@ -47713,7 +47803,7 @@
       </c>
       <c r="M39" s="31">
         <f>VLOOKUP(1,AD38:AN41,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="31">
         <f>VLOOKUP(1,AD38:AN41,5,FALSE)</f>
@@ -47725,7 +47815,7 @@
       </c>
       <c r="P39" s="32">
         <f>L39*3+M39</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R39" s="123">
         <f>DATE(2026,6,20)+TIME(9,0,0)+gmt_delta</f>
@@ -47785,7 +47875,7 @@
       </c>
       <c r="AG39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH39" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE39 &amp; "_lose")</f>
@@ -47793,11 +47883,11 @@
       </c>
       <c r="AI39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE39,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ39" s="123">
         <f>SUMIF($E$7:$E$78,$AE39,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE39,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL39" s="123">
         <f>AI39-AJ39</f>
@@ -47809,15 +47899,15 @@
       </c>
       <c r="AN39" s="123">
         <f>AF39*3+AG39</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO39" s="123">
         <f>AN39/AN42*10+BA39</f>
-        <v>1.4285714285714284</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP39" s="123">
         <f>AO39*10000000+BI39*100+AM39/AM42*10+AI39/AI42*1++IF(AQ39=0,ROW(),AQ39)/2000000</f>
-        <v>14285714.786544498</v>
+        <v>34806550.478249565</v>
       </c>
       <c r="AQ39" s="126">
         <f>VLOOKUP(AE39,db_fifarank,2,FALSE)</f>
@@ -47825,11 +47915,11 @@
       </c>
       <c r="AR39" s="125">
         <f>AP39/AP42</f>
-        <v>0.16666665452186696</v>
+        <v>0.39778910694878933</v>
       </c>
       <c r="AS39" s="125" t="str">
         <f>IF(SUM(AF38:AH41)=12,J40,"2F")</f>
-        <v>2F</v>
+        <v>Tunisia</v>
       </c>
       <c r="AT39" s="126" cm="1">
         <f t="array" ref="AT39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($U$7:$U$78))</f>
@@ -47837,15 +47927,15 @@
       </c>
       <c r="AU39" s="126" cm="1">
         <f t="array" ref="AU39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV39" s="126" cm="1">
         <f t="array" ref="AV39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" s="126" cm="1">
         <f t="array" ref="AW39">SUMPRODUCT(($E$7:$E$78=AE39)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX39" s="126">
         <f>AV39-AW39</f>
@@ -47857,11 +47947,11 @@
       </c>
       <c r="AZ39" s="126">
         <f>AT39/AT42*1000+AU39/AU42*100+AY39/AY42*10+AV39/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA39" s="126">
         <f>AZ39/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB39" s="126" cm="1">
         <f t="array" ref="BB39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_win")*($X$7:$X$78))</f>
@@ -47869,15 +47959,15 @@
       </c>
       <c r="BC39" s="126" cm="1">
         <f t="array" ref="BC39">SUMPRODUCT(($S$7:$S$78=AE39&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE39&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD39" s="126" cm="1">
         <f t="array" ref="BD39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE39" s="126" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(($E$7:$E$78=AE39)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE39)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF39" s="126">
         <f>BD39-BE39</f>
@@ -47889,23 +47979,25 @@
       </c>
       <c r="BH39" s="126">
         <f>BB39/BB42*1000+BC39/BC42*100+BG39/BG42*10+BD39/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI39" s="126">
         <f>BH39/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BK39" s="142"/>
       <c r="BL39" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!H3,AK80:AS91,9,FALSE),"3rd Group A/E/H/I/J")</f>
-        <v>3rd Group A/E/H/I/J</v>
-      </c>
-      <c r="BM39" s="62"/>
+        <v>Korea Republic</v>
+      </c>
+      <c r="BM39" s="62">
+        <v>2</v>
+      </c>
       <c r="BN39" s="64"/>
       <c r="BO39" s="27"/>
-      <c r="BP39" s="112" t="str">
+      <c r="BP39" s="112">
         <f>IF(BP38="","",BM39*1000+BN39*10+BO39)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ39" s="112"/>
       <c r="BY39" s="21"/>
@@ -47964,7 +48056,7 @@
       </c>
       <c r="K40" s="23">
         <f>L40+M40+N40</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="23">
         <f>VLOOKUP(2,AD38:AN41,3,FALSE)</f>
@@ -47972,7 +48064,7 @@
       </c>
       <c r="M40" s="23">
         <f>VLOOKUP(2,AD38:AN41,4,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="23">
         <f>VLOOKUP(2,AD38:AN41,5,FALSE)</f>
@@ -47984,7 +48076,7 @@
       </c>
       <c r="P40" s="34">
         <f>L40*3+M40</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R40" s="123">
         <f>DATE(2026,6,20)+TIME(13,0,0)+gmt_delta</f>
@@ -48044,7 +48136,7 @@
       </c>
       <c r="AG40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH40" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE40 &amp; "_lose")</f>
@@ -48052,11 +48144,11 @@
       </c>
       <c r="AI40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE40,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ40" s="123">
         <f>SUMIF($E$7:$E$78,$AE40,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE40,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL40" s="123">
         <f>AI40-AJ40</f>
@@ -48068,15 +48160,15 @@
       </c>
       <c r="AN40" s="123">
         <f>AF40*3+AG40</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO40" s="123">
         <f>AN40/AN42*10+BA40</f>
-        <v>1.4285714285714284</v>
+        <v>3.4806451612903224</v>
       </c>
       <c r="AP40" s="123">
         <f>AO40*10000000+BI40*100+AM40/AM42*10+AI40/AI42*1++IF(AQ40=0,ROW(),AQ40)/2000000</f>
-        <v>14285714.536471669</v>
+        <v>34806550.278176732</v>
       </c>
       <c r="AQ40" s="126">
         <f>VLOOKUP(AE40,db_fifarank,2,FALSE)</f>
@@ -48084,7 +48176,7 @@
       </c>
       <c r="AR40" s="125">
         <f>AP40/AP42</f>
-        <v>0.16666665160435096</v>
+        <v>0.39778910466224288</v>
       </c>
       <c r="AT40" s="126" cm="1">
         <f t="array" ref="AT40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($U$7:$U$78))</f>
@@ -48092,15 +48184,15 @@
       </c>
       <c r="AU40" s="126" cm="1">
         <f t="array" ref="AU40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV40" s="126" cm="1">
         <f t="array" ref="AV40">SUMPRODUCT(($E$7:$E$78=AE40)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE40)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW40" s="126" cm="1">
         <f t="array" ref="AW40">SUMPRODUCT(($E$7:$E$78=AE40)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE40)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX40" s="126">
         <f>AV40-AW40</f>
@@ -48112,11 +48204,11 @@
       </c>
       <c r="AZ40" s="126">
         <f>AT40/AT42*1000+AU40/AU42*100+AY40/AY42*10+AV40/AV42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BA40" s="126">
         <f>AZ40/AZ42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="BB40" s="126" cm="1">
         <f t="array" ref="BB40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_win")*($X$7:$X$78))</f>
@@ -48124,15 +48216,15 @@
       </c>
       <c r="BC40" s="126" cm="1">
         <f t="array" ref="BC40">SUMPRODUCT(($S$7:$S$78=AE40&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE40&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD40" s="126" cm="1">
         <f t="array" ref="BD40">SUMPRODUCT(($E$7:$E$78=AE40)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE40)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE40" s="126" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(($E$7:$E$78=AE40)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE40)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF40" s="126">
         <f>BD40-BE40</f>
@@ -48144,11 +48236,11 @@
       </c>
       <c r="BH40" s="126">
         <f>BB40/BB42*1000+BC40/BC42*100+BG40/BG42*10+BD40/BD42</f>
-        <v>0</v>
+        <v>50.666666666666664</v>
       </c>
       <c r="BI40" s="126">
         <f>BH40/BH42</f>
-        <v>0</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="CK40" s="114"/>
       <c r="CL40" s="112"/>
@@ -48189,7 +48281,7 @@
       </c>
       <c r="K41" s="23">
         <f>L41+M41+N41</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="23">
         <f>VLOOKUP(3,AD38:AN41,3,FALSE)</f>
@@ -48197,7 +48289,7 @@
       </c>
       <c r="M41" s="23">
         <f>VLOOKUP(3,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" s="23">
         <f>VLOOKUP(3,AD38:AN41,5,FALSE)</f>
@@ -48205,11 +48297,11 @@
       </c>
       <c r="O41" s="23" t="str">
         <f>VLOOKUP(3,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD38:AN41,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>4 - 5</v>
       </c>
       <c r="P41" s="34">
         <f>L41*3+M41</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" s="123">
         <f>DATE(2026,6,20)+TIME(6,0,0)+gmt_delta</f>
@@ -48269,7 +48361,7 @@
       </c>
       <c r="AG41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_draw")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH41" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE41 &amp; "_lose")</f>
@@ -48293,15 +48385,15 @@
       </c>
       <c r="AN41" s="123">
         <f>AF41*3+AG41</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO41" s="123">
         <f>AN41/AN42*10+BA41</f>
-        <v>2.8571428571428568</v>
+        <v>3.75</v>
       </c>
       <c r="AP41" s="123">
         <f>AO41*10000000+BI41*100+AM41/AM42*10+AI41/AI42*1++IF(AQ41=0,ROW(),AQ41)/2000000</f>
-        <v>28571431.572170094</v>
+        <v>37500002.900741525</v>
       </c>
       <c r="AQ41" s="126">
         <f>VLOOKUP(AE41,db_fifarank,2,FALSE)</f>
@@ -48309,7 +48401,7 @@
       </c>
       <c r="AR41" s="125">
         <f>AP41/AP42</f>
-        <v>0.33333333236634421</v>
+        <v>0.42857141714702796</v>
       </c>
       <c r="AT41" s="126" cm="1">
         <f t="array" ref="AT41">SUMPRODUCT(($S$7:$S$78=AE41&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE41&amp;"_win")*($U$7:$U$78))</f>
@@ -48433,7 +48525,7 @@
       </c>
       <c r="K42" s="36">
         <f>L42+M42+N42</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="36">
         <f>VLOOKUP(4,AD38:AN41,3,FALSE)</f>
@@ -48441,7 +48533,7 @@
       </c>
       <c r="M42" s="36">
         <f>VLOOKUP(4,AD38:AN41,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="36">
         <f>VLOOKUP(4,AD38:AN41,5,FALSE)</f>
@@ -48449,11 +48541,11 @@
       </c>
       <c r="O42" s="36" t="str">
         <f>VLOOKUP(4,AD38:AN41,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD38:AN41,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>3 - 4</v>
       </c>
       <c r="P42" s="37">
         <f>L42*3+M42</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" s="123">
         <f>DATE(2026,6,20)+TIME(17,0,0)+gmt_delta</f>
@@ -48513,7 +48605,7 @@
       </c>
       <c r="AI42" s="123">
         <f>MAX(AI38:AI41)+1</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL42" s="123">
         <f>MIN(AL38:AL41)</f>
@@ -48525,15 +48617,15 @@
       </c>
       <c r="AN42" s="123">
         <f>MAX(AN38:AN41)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO42" s="123">
         <f>MAX(AO38:AO41)+1</f>
-        <v>9.5714285714285712</v>
+        <v>9.75</v>
       </c>
       <c r="AP42" s="123">
         <f>MAX(AP38:AP41)+1</f>
-        <v>85714294.965164647</v>
+        <v>87500009.100878924</v>
       </c>
       <c r="AT42" s="126">
         <f>MAX(AT38:AT41)-MIN(AT38:AT41)+1</f>
@@ -48541,15 +48633,15 @@
       </c>
       <c r="AU42" s="126">
         <f>MAX(AU38:AU41)-MIN(AU38:AU41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV42" s="126">
         <f>MAX(AV38:AV41)-MIN(AV38:AV41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW42" s="126">
         <f>MAX(AW38:AW41)-MIN(AW38:AW41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY42" s="126">
         <f>MAX(AY38:AY41)-MIN(AY38:AY41)+1</f>
@@ -48557,7 +48649,7 @@
       </c>
       <c r="AZ42" s="126">
         <f>MAX(AZ38:AZ41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BB42" s="126">
         <f>MAX(BB38:BB41)-MIN(BB38:BB41)+1</f>
@@ -48565,15 +48657,15 @@
       </c>
       <c r="BC42" s="126">
         <f>MAX(BC38:BC41)-MIN(BC38:BC41)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD42" s="126">
         <f>MAX(BD38:BD41)-MIN(BD38:BD41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE42" s="126">
         <f>MAX(BE38:BE41)-MIN(BE38:BE41)+1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG42" s="126">
         <f>MAX(BG38:BG41)-MIN(BG38:BG41)+1</f>
@@ -48581,7 +48673,7 @@
       </c>
       <c r="BH42" s="126">
         <f>MAX(BH38:BH41)+1</f>
-        <v>1</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="BK42" s="141">
         <v>76</v>
@@ -48590,12 +48682,14 @@
         <f>AS20</f>
         <v>Brazil</v>
       </c>
-      <c r="BM42" s="61"/>
+      <c r="BM42" s="61">
+        <v>3</v>
+      </c>
       <c r="BN42" s="63"/>
       <c r="BO42" s="25"/>
-      <c r="BP42" s="112" t="str">
+      <c r="BP42" s="112">
         <f>IF(OR(BM42="",BM43="",AND(BN42="",BN43&lt;&gt;""),AND(BN43="",BN42&lt;&gt;""),AND(BO42="",BO43&lt;&gt;""),AND(BO43="",BO42&lt;&gt;"")),"",BM42*1000+BN42*10+BO42)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="BQ42" s="112"/>
       <c r="BR42" s="21"/>
@@ -48683,14 +48777,16 @@
       <c r="BK43" s="142"/>
       <c r="BL43" s="26" t="str">
         <f>AS39</f>
-        <v>2F</v>
-      </c>
-      <c r="BM43" s="62"/>
+        <v>Tunisia</v>
+      </c>
+      <c r="BM43" s="62">
+        <v>1</v>
+      </c>
       <c r="BN43" s="64"/>
       <c r="BO43" s="27"/>
-      <c r="BP43" s="113" t="str">
+      <c r="BP43" s="113">
         <f>IF(BP42="","",BM43*1000+BN43*10+BO43)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ43" s="112"/>
       <c r="BR43" s="21" t="str" cm="1">
@@ -48823,7 +48919,7 @@
       </c>
       <c r="AG44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE44 &amp; "_lose")</f>
@@ -48831,11 +48927,11 @@
       </c>
       <c r="AI44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE44,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ44" s="123">
         <f>SUMIF($E$7:$E$78,$AE44,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE44,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL44" s="123">
         <f>AI44-AJ44</f>
@@ -48843,19 +48939,19 @@
       </c>
       <c r="AM44" s="123">
         <f>AL44-AL48</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN44" s="123">
         <f>AF44*3+AG44</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO44" s="123">
         <f>AN44/AN48*10+BA44</f>
-        <v>8.5714285714285712</v>
+        <v>8.75</v>
       </c>
       <c r="AP44" s="123">
         <f>AO44*10000000+BI44*100+AM44/AM48*10+AI44/AI48*1++IF(AQ44=0,ROW(),AQ44)/2000000</f>
-        <v>85714294.515153065</v>
+        <v>87500009.167534009</v>
       </c>
       <c r="AQ44" s="126">
         <f>VLOOKUP(AE44,db_fifarank,2,FALSE)</f>
@@ -48863,11 +48959,11 @@
       </c>
       <c r="AR44" s="125">
         <f>AP44/AP48</f>
-        <v>0.9999999883333347</v>
+        <v>0.99999998857142991</v>
       </c>
       <c r="AS44" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J45,"1G")</f>
-        <v>1G</v>
+        <v>Belgium</v>
       </c>
       <c r="AT44" s="126" cm="1">
         <f t="array" ref="AT44">SUMPRODUCT(($S$7:$S$78=AE44&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE44&amp;"_win")*($U$7:$U$78))</f>
@@ -48945,14 +49041,18 @@
       </c>
       <c r="BS44" s="24" t="str">
         <f>IF(BP42&gt;BP43,BL42,IF(BP42&lt;BP43,BL43,""))</f>
-        <v/>
-      </c>
-      <c r="BT44" s="61"/>
-      <c r="BU44" s="63"/>
+        <v>Brazil</v>
+      </c>
+      <c r="BT44" s="61">
+        <v>2</v>
+      </c>
+      <c r="BU44" s="63">
+        <v>2</v>
+      </c>
       <c r="BV44" s="25"/>
-      <c r="BW44" s="112" t="str">
+      <c r="BW44" s="112">
         <f>IF(OR(BT44="",BT45="",AND(BU44="",BU45&lt;&gt;""),AND(BU45="",BU44&lt;&gt;""),AND(BV44="",BV45&lt;&gt;""),AND(BV45="",BV44&lt;&gt;"")),"",BT44*1000+BU44*10+BV44)</f>
-        <v/>
+        <v>2020</v>
       </c>
       <c r="CK44" s="114"/>
       <c r="CM44" s="144" t="str" cm="1">
@@ -49000,7 +49100,7 @@
       </c>
       <c r="K45" s="31">
         <f>L45+M45+N45</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="31">
         <f>VLOOKUP(1,AD44:AN47,3,FALSE)</f>
@@ -49008,7 +49108,7 @@
       </c>
       <c r="M45" s="31">
         <f>VLOOKUP(1,AD44:AN47,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="31">
         <f>VLOOKUP(1,AD44:AN47,5,FALSE)</f>
@@ -49016,11 +49116,11 @@
       </c>
       <c r="O45" s="31" t="str">
         <f>VLOOKUP(1,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD44:AN47,7,FALSE)</f>
-        <v>4 - 1</v>
+        <v>5 - 2</v>
       </c>
       <c r="P45" s="32">
         <f>L45*3+M45</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R45" s="123">
         <f>DATE(2026,6,21)+TIME(8,0,0)+gmt_delta</f>
@@ -49076,7 +49176,7 @@
       </c>
       <c r="AF45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG45" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE45 &amp; "_draw")</f>
@@ -49088,7 +49188,7 @@
       </c>
       <c r="AI45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE45,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ45" s="123">
         <f>SUMIF($E$7:$E$78,$AE45,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE45,$F$7:$F$78)</f>
@@ -49096,23 +49196,23 @@
       </c>
       <c r="AL45" s="123">
         <f>AI45-AJ45</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM45" s="123">
         <f>AL45-AL48</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN45" s="123">
         <f>AF45*3+AG45</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO45" s="123">
         <f>AN45/AN48*10+BA45</f>
-        <v>4.2857142857142856</v>
+        <v>7.5</v>
       </c>
       <c r="AP45" s="123">
         <f>AO45*10000000+BI45*100+AM45/AM48*10+AI45/AI48*1++IF(AQ45=0,ROW(),AQ45)/2000000</f>
-        <v>42857143.257924475</v>
+        <v>75000003.834114954</v>
       </c>
       <c r="AQ45" s="126">
         <f>VLOOKUP(AE45,db_fifarank,2,FALSE)</f>
@@ -49120,11 +49220,11 @@
       </c>
       <c r="AR45" s="125">
         <f>AP45/AP48</f>
-        <v>0.49999994750406535</v>
+        <v>0.85714280136098708</v>
       </c>
       <c r="AS45" s="125" t="str">
         <f>IF(SUM(AF44:AH47)=12,J46,"2G")</f>
-        <v>2G</v>
+        <v>Egypt</v>
       </c>
       <c r="AT45" s="126" cm="1">
         <f t="array" ref="AT45">SUMPRODUCT(($S$7:$S$78=AE45&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE45&amp;"_win")*($U$7:$U$78))</f>
@@ -49206,14 +49306,18 @@
       <c r="BR45" s="142"/>
       <c r="BS45" s="26" t="str">
         <f>IF(BP46&gt;BP47,BL46,IF(BP46&lt;BP47,BL47,""))</f>
-        <v/>
-      </c>
-      <c r="BT45" s="62"/>
-      <c r="BU45" s="64"/>
+        <v>Senegal</v>
+      </c>
+      <c r="BT45" s="62">
+        <v>2</v>
+      </c>
+      <c r="BU45" s="64">
+        <v>3</v>
+      </c>
       <c r="BV45" s="27"/>
-      <c r="BW45" s="113" t="str">
+      <c r="BW45" s="113">
         <f>IF(BW44="","",BT45*1000+BU45*10+BV45)</f>
-        <v/>
+        <v>2030</v>
       </c>
       <c r="CK45" s="114"/>
       <c r="CM45" s="147"/>
@@ -49258,11 +49362,11 @@
       </c>
       <c r="K46" s="23">
         <f>L46+M46+N46</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="23">
         <f>VLOOKUP(2,AD44:AN47,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="23">
         <f>VLOOKUP(2,AD44:AN47,4,FALSE)</f>
@@ -49274,11 +49378,11 @@
       </c>
       <c r="O46" s="23" t="str">
         <f>VLOOKUP(2,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD44:AN47,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>3 - 3</v>
       </c>
       <c r="P46" s="34">
         <f>L46*3+M46</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R46" s="123">
         <f>DATE(2026,6,21)+TIME(14,0,0)+gmt_delta</f>
@@ -49326,7 +49430,7 @@
       </c>
       <c r="AD46" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR46))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE46" s="124" t="str">
         <f>VLOOKUP("Iran",T,lang,FALSE)</f>
@@ -49342,7 +49446,7 @@
       </c>
       <c r="AH46" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE46 &amp; "_lose")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE46,$G$7:$G$78)</f>
@@ -49350,11 +49454,11 @@
       </c>
       <c r="AJ46" s="123">
         <f>SUMIF($E$7:$E$78,$AE46,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE46,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL46" s="123">
         <f>AI46-AJ46</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM46" s="123">
         <f>AL46-AL48</f>
@@ -49366,11 +49470,11 @@
       </c>
       <c r="AO46" s="123">
         <f>AN46/AN48*10+BA46</f>
-        <v>2.4089635854341735</v>
+        <v>1.25</v>
       </c>
       <c r="AP46" s="123">
         <f>AO46*10000000+BI46*100+AM46/AM48*10+AI46/AI48*1++IF(AQ46=0,ROW(),AQ46)/2000000</f>
-        <v>24089733.894365072</v>
+        <v>12500000.00080765</v>
       </c>
       <c r="AQ46" s="126">
         <f>VLOOKUP(AE46,db_fifarank,2,FALSE)</f>
@@ -49378,7 +49482,7 @@
       </c>
       <c r="AR46" s="125">
         <f>AP46/AP48</f>
-        <v>0.28104686329839051</v>
+        <v>0.14285712626631955</v>
       </c>
       <c r="AT46" s="126" cm="1">
         <f t="array" ref="AT46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($U$7:$U$78))</f>
@@ -49386,7 +49490,7 @@
       </c>
       <c r="AU46" s="126" cm="1">
         <f t="array" ref="AU46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV46" s="126" cm="1">
         <f t="array" ref="AV46">SUMPRODUCT(($E$7:$E$78=AE46)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -49406,11 +49510,11 @@
       </c>
       <c r="AZ46" s="126">
         <f>AT46/AT48*1000+AU46/AU48*100+AY46/AY48*10+AV46/AV48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA46" s="126">
         <f>AZ46/AZ48</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BB46" s="126" cm="1">
         <f t="array" ref="BB46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_win")*($X$7:$X$78))</f>
@@ -49418,7 +49522,7 @@
       </c>
       <c r="BC46" s="126" cm="1">
         <f t="array" ref="BC46">SUMPRODUCT(($S$7:$S$78=AE46&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE46&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD46" s="126" cm="1">
         <f t="array" ref="BD46">SUMPRODUCT(($E$7:$E$78=AE46)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE46)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -49438,25 +49542,27 @@
       </c>
       <c r="BH46" s="126">
         <f>BB46/BB48*1000+BC46/BC48*100+BG46/BG48*10+BD46/BD48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI46" s="126">
         <f>BH46/BH48</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BK46" s="141">
         <v>78</v>
       </c>
       <c r="BL46" s="24" t="str">
         <f>AS33</f>
-        <v>2E</v>
-      </c>
-      <c r="BM46" s="61"/>
+        <v>Ecuador</v>
+      </c>
+      <c r="BM46" s="61">
+        <v>0</v>
+      </c>
       <c r="BN46" s="63"/>
       <c r="BO46" s="25"/>
-      <c r="BP46" s="116" t="str">
+      <c r="BP46" s="116">
         <f>IF(OR(BM46="",BM47="",AND(BN46="",BN47&lt;&gt;""),AND(BN47="",BN46&lt;&gt;""),AND(BO46="",BO47&lt;&gt;""),AND(BO47="",BO46&lt;&gt;"")),"",BM46*1000+BN46*10+BO46)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ46" s="112"/>
       <c r="BR46" s="21"/>
@@ -49500,11 +49606,11 @@
       </c>
       <c r="J47" s="33" t="str">
         <f>VLOOKUP(3,AD44:AN47,2,FALSE)</f>
-        <v>Iran</v>
+        <v>New Zealand</v>
       </c>
       <c r="K47" s="23">
         <f>L47+M47+N47</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="23">
         <f>VLOOKUP(3,AD44:AN47,3,FALSE)</f>
@@ -49512,7 +49618,7 @@
       </c>
       <c r="M47" s="23">
         <f>VLOOKUP(3,AD44:AN47,4,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" s="23">
         <f>VLOOKUP(3,AD44:AN47,5,FALSE)</f>
@@ -49520,11 +49626,11 @@
       </c>
       <c r="O47" s="23" t="str">
         <f>VLOOKUP(3,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD44:AN47,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>1 - 2</v>
       </c>
       <c r="P47" s="34">
         <f>L47*3+M47</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" s="123">
         <f>DATE(2026,6,22)+TIME(13,0,0)+gmt_delta</f>
@@ -49540,15 +49646,15 @@
       </c>
       <c r="U47" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="123">
         <f t="shared" ref="V47:V78" si="21">U47*F47</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" s="123">
         <f t="shared" ref="W47:W78" si="22">U47*G47</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X47" s="123">
         <f t="shared" si="9"/>
@@ -49572,7 +49678,7 @@
       </c>
       <c r="AD47" s="123">
         <f>COUNTIF(AR44:AR47,CONCATENATE("&gt;=",AR47))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE47" s="124" t="str">
         <f>VLOOKUP("New Zealand",T,lang,FALSE)</f>
@@ -49584,7 +49690,7 @@
       </c>
       <c r="AG47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_draw")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH47" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE47 &amp; "_lose")</f>
@@ -49592,11 +49698,11 @@
       </c>
       <c r="AI47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE47,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ47" s="123">
         <f>SUMIF($E$7:$E$78,$AE47,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE47,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL47" s="123">
         <f>AI47-AJ47</f>
@@ -49604,19 +49710,19 @@
       </c>
       <c r="AM47" s="123">
         <f>AL47-AL48</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" s="123">
         <f>AF47*3+AG47</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO47" s="123">
         <f>AN47/AN48*10+BA47</f>
-        <v>2.4089635854341735</v>
+        <v>2.5</v>
       </c>
       <c r="AP47" s="123">
         <f>AO47*10000000+BI47*100+AM47/AM48*10+AI47/AI48*1++IF(AQ47=0,ROW(),AQ47)/2000000</f>
-        <v>24089733.894198205</v>
+        <v>25000001.833974119</v>
       </c>
       <c r="AQ47" s="126">
         <f>VLOOKUP(AE47,db_fifarank,2,FALSE)</f>
@@ -49624,7 +49730,7 @@
       </c>
       <c r="AR47" s="125">
         <f>AP47/AP48</f>
-        <v>0.28104686329644374</v>
+        <v>0.28571427347388029</v>
       </c>
       <c r="AT47" s="126" cm="1">
         <f t="array" ref="AT47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($U$7:$U$78))</f>
@@ -49632,7 +49738,7 @@
       </c>
       <c r="AU47" s="126" cm="1">
         <f t="array" ref="AU47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV47" s="126" cm="1">
         <f t="array" ref="AV47">SUMPRODUCT(($E$7:$E$78=AE47)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($U$7:$U$78)*($G$7:$G$78))</f>
@@ -49652,11 +49758,11 @@
       </c>
       <c r="AZ47" s="126">
         <f>AT47/AT48*1000+AU47/AU48*100+AY47/AY48*10+AV47/AV48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA47" s="126">
         <f>AZ47/AZ48</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BB47" s="126" cm="1">
         <f t="array" ref="BB47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_win")*($X$7:$X$78))</f>
@@ -49664,7 +49770,7 @@
       </c>
       <c r="BC47" s="126" cm="1">
         <f t="array" ref="BC47">SUMPRODUCT(($S$7:$S$78=AE47&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE47&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD47" s="126" cm="1">
         <f t="array" ref="BD47">SUMPRODUCT(($E$7:$E$78=AE47)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE47)*($X$7:$X$78)*($G$7:$G$78))</f>
@@ -49684,23 +49790,25 @@
       </c>
       <c r="BH47" s="126">
         <f>BB47/BB48*1000+BC47/BC48*100+BG47/BG48*10+BD47/BD48</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BI47" s="126">
         <f>BH47/BH48</f>
-        <v>0.98039215686274506</v>
+        <v>0</v>
       </c>
       <c r="BK47" s="142"/>
       <c r="BL47" s="26" t="str">
         <f>AS57</f>
-        <v>2I</v>
-      </c>
-      <c r="BM47" s="62"/>
+        <v>Senegal</v>
+      </c>
+      <c r="BM47" s="62">
+        <v>4</v>
+      </c>
       <c r="BN47" s="64"/>
       <c r="BO47" s="27"/>
-      <c r="BP47" s="112" t="str">
+      <c r="BP47" s="112">
         <f>IF(BP46="","",BM47*1000+BN47*10+BO47)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="BQ47" s="112"/>
       <c r="BR47" s="21"/>
@@ -49769,11 +49877,11 @@
       </c>
       <c r="J48" s="35" t="str">
         <f>VLOOKUP(4,AD44:AN47,2,FALSE)</f>
-        <v>New Zealand</v>
+        <v>Iran</v>
       </c>
       <c r="K48" s="36">
         <f>L48+M48+N48</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="36">
         <f>VLOOKUP(4,AD44:AN47,3,FALSE)</f>
@@ -49785,11 +49893,11 @@
       </c>
       <c r="N48" s="36">
         <f>VLOOKUP(4,AD44:AN47,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" s="36" t="str">
         <f>VLOOKUP(4,AD44:AN47,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD44:AN47,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>0 - 2</v>
       </c>
       <c r="P48" s="37">
         <f>L48*3+M48</f>
@@ -49845,35 +49953,35 @@
       </c>
       <c r="AG48" s="123">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH48" s="123">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" s="123">
         <f>MAX(AI44:AI47)+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL48" s="123">
         <f>MIN(AL44:AL47)</f>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM48" s="123">
         <f>MAX(AM44:AM47)+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN48" s="123">
         <f>MAX(AN44:AN47)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO48" s="123">
         <f>MAX(AO44:AO47)+1</f>
-        <v>9.5714285714285712</v>
+        <v>9.75</v>
       </c>
       <c r="AP48" s="123">
         <f>MAX(AP44:AP47)+1</f>
-        <v>85714295.515153065</v>
+        <v>87500010.167534009</v>
       </c>
       <c r="AT48" s="126">
         <f>MAX(AT44:AT47)-MIN(AT44:AT47)+1</f>
@@ -49881,7 +49989,7 @@
       </c>
       <c r="AU48" s="126">
         <f>MAX(AU44:AU47)-MIN(AU44:AU47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV48" s="126">
         <f>MAX(AV44:AV47)-MIN(AV44:AV47)+1</f>
@@ -49897,7 +50005,7 @@
       </c>
       <c r="AZ48" s="126">
         <f>MAX(AZ44:AZ47)+1</f>
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="BB48" s="126">
         <f>MAX(BB44:BB47)-MIN(BB44:BB47)+1</f>
@@ -49905,7 +50013,7 @@
       </c>
       <c r="BC48" s="126">
         <f>MAX(BC44:BC47)-MIN(BC44:BC47)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD48" s="126">
         <f>MAX(BD44:BD47)-MIN(BD44:BD47)+1</f>
@@ -49921,7 +50029,7 @@
       </c>
       <c r="BH48" s="126">
         <f>MAX(BH44:BH47)+1</f>
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
@@ -49942,14 +50050,16 @@
       </c>
       <c r="BZ48" s="24" t="str">
         <f>IF(BW44&gt;BW45,BS44,IF(BW44&lt;BW45,BS45,""))</f>
-        <v/>
-      </c>
-      <c r="CA48" s="61"/>
+        <v>Senegal</v>
+      </c>
+      <c r="CA48" s="61">
+        <v>2</v>
+      </c>
       <c r="CB48" s="63"/>
       <c r="CC48" s="25"/>
-      <c r="CD48" s="112" t="str">
+      <c r="CD48" s="112">
         <f>IF(OR(CA48="",CA49="",AND(CB48="",CB49&lt;&gt;""),AND(CB49="",CB48&lt;&gt;""),AND(CC48="",CC49&lt;&gt;""),AND(CC49="",CC48&lt;&gt;"")),"",CA48*1000+CB48*10+CC48)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CK48" s="114"/>
       <c r="CL48" s="112"/>
@@ -49958,14 +50068,16 @@
       </c>
       <c r="CN48" s="24" t="str">
         <f>IF(CK23&gt;CK24,CG24,IF(CK23&lt;CK24,CG23,""))</f>
-        <v/>
-      </c>
-      <c r="CO48" s="61"/>
+        <v>Spain</v>
+      </c>
+      <c r="CO48" s="61">
+        <v>1</v>
+      </c>
       <c r="CP48" s="63"/>
       <c r="CQ48" s="25"/>
-      <c r="CR48" s="111" t="str">
+      <c r="CR48" s="111">
         <f>IF(OR(CO48="",CO49="",AND(CP48="",CP49&lt;&gt;""),AND(CP49="",CP48&lt;&gt;""),AND(CQ48="",CQ49&lt;&gt;""),AND(CQ49="",CQ48&lt;&gt;"")),"",CO48*1000+CP48*10+CQ48)</f>
-        <v/>
+        <v>1000</v>
       </c>
     </row>
     <row r="49" spans="1:96" x14ac:dyDescent="0.25">
@@ -50065,28 +50177,32 @@
       <c r="BY49" s="142"/>
       <c r="BZ49" s="26" t="str">
         <f>IF(BW52&gt;BW53,BS52,IF(BW52&lt;BW53,BS53,""))</f>
-        <v/>
-      </c>
-      <c r="CA49" s="62"/>
+        <v>Norway</v>
+      </c>
+      <c r="CA49" s="62">
+        <v>0</v>
+      </c>
       <c r="CB49" s="64"/>
       <c r="CC49" s="27"/>
-      <c r="CD49" s="113" t="str">
+      <c r="CD49" s="113">
         <f>IF(CD48="","",CA49*1000+CB49*10+CC49)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK49" s="114"/>
       <c r="CL49" s="115"/>
       <c r="CM49" s="142"/>
       <c r="CN49" s="26" t="str">
         <f>IF(CK55&gt;CK56,CG56,IF(CK55&lt;CK56,CG55,""))</f>
-        <v/>
-      </c>
-      <c r="CO49" s="62"/>
+        <v>Argentina</v>
+      </c>
+      <c r="CO49" s="62">
+        <v>0</v>
+      </c>
       <c r="CP49" s="64"/>
       <c r="CQ49" s="27"/>
-      <c r="CR49" s="111" t="str">
+      <c r="CR49" s="111">
         <f>IF(CR48="","",CO49*1000+CP49*10+CQ49)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:96" x14ac:dyDescent="0.25">
@@ -50201,7 +50317,7 @@
       </c>
       <c r="AF50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG50" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE50 &amp; "_draw")</f>
@@ -50213,31 +50329,31 @@
       </c>
       <c r="AI50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE50,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ50" s="123">
         <f>SUMIF($E$7:$E$78,$AE50,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE50,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" s="123">
         <f>AI50-AJ50</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM50" s="123">
         <f>AL50-AL54</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN50" s="123">
         <f>AF50*3+AG50</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO50" s="123">
         <f>AN50/AN54*10+BA50</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP50" s="123">
         <f>AO50*10000000+BI50*100+AM50/AM54*10+AI50/AI54*1++IF(AQ50=0,ROW(),AQ50)/2000000</f>
-        <v>85714295.923557252</v>
+        <v>90000010.186652496</v>
       </c>
       <c r="AQ50" s="126">
         <f>VLOOKUP(AE50,db_fifarank,2,FALSE)</f>
@@ -50245,11 +50361,11 @@
       </c>
       <c r="AR50" s="125">
         <f>AP50/AP54</f>
-        <v>0.99999998833333481</v>
+        <v>0.9999999888888903</v>
       </c>
       <c r="AS50" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J51,"1H")</f>
-        <v>1H</v>
+        <v>Spain</v>
       </c>
       <c r="AT50" s="126" cm="1">
         <f t="array" ref="AT50">SUMPRODUCT(($S$7:$S$78=AE50&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE50&amp;"_win")*($U$7:$U$78))</f>
@@ -50320,14 +50436,16 @@
       </c>
       <c r="BL50" s="24" t="str">
         <f>AS8</f>
-        <v>1A</v>
-      </c>
-      <c r="BM50" s="61"/>
+        <v>Mexico</v>
+      </c>
+      <c r="BM50" s="61">
+        <v>2</v>
+      </c>
       <c r="BN50" s="63"/>
       <c r="BO50" s="25"/>
-      <c r="BP50" s="112" t="str">
+      <c r="BP50" s="112">
         <f>IF(OR(BM50="",BM51="",AND(BN50="",BN51&lt;&gt;""),AND(BN51="",BN50&lt;&gt;""),AND(BO50="",BO51&lt;&gt;""),AND(BO51="",BO50&lt;&gt;"")),"",BM50*1000+BN50*10+BO50)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ50" s="112"/>
       <c r="BR50" s="21"/>
@@ -50382,11 +50500,11 @@
       </c>
       <c r="K51" s="31">
         <f>L51+M51+N51</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="31">
         <f>VLOOKUP(1,AD50:AN53,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51" s="31">
         <f>VLOOKUP(1,AD50:AN53,4,FALSE)</f>
@@ -50398,11 +50516,11 @@
       </c>
       <c r="O51" s="31" t="str">
         <f>VLOOKUP(1,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD50:AN53,7,FALSE)</f>
-        <v>7 - 0</v>
+        <v>9 - 1</v>
       </c>
       <c r="P51" s="32">
         <f>L51*3+M51</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R51" s="123">
         <f>DATE(2026,6,23)+TIME(9,0,0)+gmt_delta</f>
@@ -50418,27 +50536,27 @@
       </c>
       <c r="U51" s="123">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="123">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W51" s="123">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51" s="123">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="123">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="123">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA51" s="123">
         <f t="shared" si="17"/>
@@ -50450,7 +50568,7 @@
       </c>
       <c r="AD51" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR51))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE51" s="124" t="str">
         <f>VLOOKUP("Cape Verde",T,lang,FALSE)</f>
@@ -50458,7 +50576,7 @@
       </c>
       <c r="AF51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG51" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE51 &amp; "_draw")</f>
@@ -50470,7 +50588,7 @@
       </c>
       <c r="AI51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE51,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ51" s="123">
         <f>SUMIF($E$7:$E$78,$AE51,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE51,$F$7:$F$78)</f>
@@ -50478,7 +50596,7 @@
       </c>
       <c r="AL51" s="123">
         <f>AI51-AJ51</f>
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="AM51" s="123">
         <f>AL51-AL54</f>
@@ -50486,15 +50604,15 @@
       </c>
       <c r="AN51" s="123">
         <f>AF51*3+AG51</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO51" s="123">
         <f>AN51/AN54*10+BA51</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP51" s="123">
         <f>AO51*10000000+BI51*100+AM51/AM54*10+AI51/AI54*1++IF(AQ51=0,ROW(),AQ51)/2000000</f>
-        <v>6.8306500000000006E-4</v>
+        <v>30000000.200683065</v>
       </c>
       <c r="AQ51" s="126">
         <f>VLOOKUP(AE51,db_fifarank,2,FALSE)</f>
@@ -50502,11 +50620,11 @@
       </c>
       <c r="AR51" s="125">
         <f>AP51/AP54</f>
-        <v>7.9690906245101591E-12</v>
+        <v>0.33333329413110374</v>
       </c>
       <c r="AS51" s="125" t="str">
         <f>IF(SUM(AF50:AH53)=12,J52,"2H")</f>
-        <v>2H</v>
+        <v>Uruguay</v>
       </c>
       <c r="AT51" s="126" cm="1">
         <f t="array" ref="AT51">SUMPRODUCT(($S$7:$S$78=AE51&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE51&amp;"_win")*($U$7:$U$78))</f>
@@ -50575,14 +50693,16 @@
       <c r="BK51" s="142"/>
       <c r="BL51" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!D3,AK80:AS91,9,FALSE),"3rd Group C/E/F/H/I")</f>
-        <v>3rd Group C/E/F/H/I</v>
-      </c>
-      <c r="BM51" s="62"/>
+        <v>Cape Verde</v>
+      </c>
+      <c r="BM51" s="62">
+        <v>1</v>
+      </c>
       <c r="BN51" s="64"/>
       <c r="BO51" s="27"/>
-      <c r="BP51" s="113" t="str">
+      <c r="BP51" s="113">
         <f>IF(BP50="","",BM51*1000+BN51*10+BO51)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ51" s="112"/>
       <c r="BR51" s="21" t="str" cm="1">
@@ -50643,7 +50763,7 @@
       </c>
       <c r="K52" s="23">
         <f>L52+M52+N52</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="23">
         <f>VLOOKUP(2,AD50:AN53,3,FALSE)</f>
@@ -50655,11 +50775,11 @@
       </c>
       <c r="N52" s="23">
         <f>VLOOKUP(2,AD50:AN53,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="23" t="str">
         <f>VLOOKUP(2,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD50:AN53,7,FALSE)</f>
-        <v>3 - 0</v>
+        <v>4 - 2</v>
       </c>
       <c r="P52" s="34">
         <f>L52*3+M52</f>
@@ -50711,7 +50831,7 @@
       </c>
       <c r="AD52" s="123">
         <f>COUNTIF(AR50:AR53,CONCATENATE("&gt;=",AR52))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE52" s="124" t="str">
         <f>VLOOKUP("Saudi Arabia",T,lang,FALSE)</f>
@@ -50727,7 +50847,7 @@
       </c>
       <c r="AH52" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE52 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE52,$G$7:$G$78)</f>
@@ -50735,15 +50855,15 @@
       </c>
       <c r="AJ52" s="123">
         <f>SUMIF($E$7:$E$78,$AE52,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE52,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL52" s="123">
         <f>AI52-AJ52</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM52" s="123">
         <f>AL52-AL54</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN52" s="123">
         <f>AF52*3+AG52</f>
@@ -50755,7 +50875,7 @@
       </c>
       <c r="AP52" s="123">
         <f>AO52*10000000+BI52*100+AM52/AM54*10+AI52/AI54*1++IF(AQ52=0,ROW(),AQ52)/2000000</f>
-        <v>2.6673773816666664</v>
+        <v>7.10715E-4</v>
       </c>
       <c r="AQ52" s="126">
         <f>VLOOKUP(AE52,db_fifarank,2,FALSE)</f>
@@ -50763,7 +50883,7 @@
       </c>
       <c r="AR52" s="125">
         <f>AP52/AP54</f>
-        <v>3.1119398716476891E-8</v>
+        <v>7.8968323517875633E-12</v>
       </c>
       <c r="AT52" s="126" cm="1">
         <f t="array" ref="AT52">SUMPRODUCT(($S$7:$S$78=AE52&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE52&amp;"_win")*($U$7:$U$78))</f>
@@ -50841,14 +50961,18 @@
       </c>
       <c r="BS52" s="24" t="str">
         <f>IF(BP50&gt;BP51,BL50,IF(BP50&lt;BP51,BL51,""))</f>
-        <v/>
-      </c>
-      <c r="BT52" s="61"/>
-      <c r="BU52" s="63"/>
+        <v>Mexico</v>
+      </c>
+      <c r="BT52" s="61">
+        <v>0</v>
+      </c>
+      <c r="BU52" s="63">
+        <v>0</v>
+      </c>
       <c r="BV52" s="25"/>
-      <c r="BW52" s="116" t="str">
+      <c r="BW52" s="116">
         <f>IF(OR(BT52="",BT53="",AND(BU52="",BU53&lt;&gt;""),AND(BU53="",BU52&lt;&gt;""),AND(BV52="",BV53&lt;&gt;""),AND(BV53="",BV52&lt;&gt;"")),"",BT52*1000+BU52*10+BV52)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX52" s="112"/>
       <c r="BY52" s="21"/>
@@ -50892,15 +51016,15 @@
       </c>
       <c r="J53" s="33" t="str">
         <f>VLOOKUP(3,AD50:AN53,2,FALSE)</f>
-        <v>Saudi Arabia</v>
+        <v>Cape Verde</v>
       </c>
       <c r="K53" s="23">
         <f>L53+M53+N53</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="23">
         <f>VLOOKUP(3,AD50:AN53,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="23">
         <f>VLOOKUP(3,AD50:AN53,4,FALSE)</f>
@@ -50912,11 +51036,11 @@
       </c>
       <c r="O53" s="23" t="str">
         <f>VLOOKUP(3,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD50:AN53,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>2 - 7</v>
       </c>
       <c r="P53" s="34">
         <f>L53*3+M53</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" s="123">
         <f>DATE(2026,6,23)+TIME(6,0,0)+gmt_delta</f>
@@ -50980,23 +51104,23 @@
       </c>
       <c r="AH53" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE53 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE53,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ53" s="123">
         <f>SUMIF($E$7:$E$78,$AE53,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE53,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL53" s="123">
         <f>AI53-AJ53</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM53" s="123">
         <f>AL53-AL54</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AN53" s="123">
         <f>AF53*3+AG53</f>
@@ -51004,11 +51128,11 @@
       </c>
       <c r="AO53" s="123">
         <f>AN53/AN54*10+BA53</f>
-        <v>8.5714285714285712</v>
+        <v>6</v>
       </c>
       <c r="AP53" s="123">
         <f>AO53*10000000+BI53*100+AM53/AM54*10+AI53/AI54*1++IF(AQ53=0,ROW(),AQ53)/2000000</f>
-        <v>85714292.756788924</v>
+        <v>60000005.400836535</v>
       </c>
       <c r="AQ53" s="126">
         <f>VLOOKUP(AE53,db_fifarank,2,FALSE)</f>
@@ -51016,7 +51140,7 @@
       </c>
       <c r="AR53" s="125">
         <f>AP53/AP54</f>
-        <v>0.99999995138770925</v>
+        <v>0.6666666438118718</v>
       </c>
       <c r="AT53" s="126" cm="1">
         <f t="array" ref="AT53">SUMPRODUCT(($S$7:$S$78=AE53&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE53&amp;"_win")*($U$7:$U$78))</f>
@@ -51098,14 +51222,18 @@
       <c r="BR53" s="142"/>
       <c r="BS53" s="26" t="str">
         <f>IF(BP54&gt;BP55,BL54,IF(BP54&lt;BP55,BL55,""))</f>
-        <v/>
-      </c>
-      <c r="BT53" s="62"/>
-      <c r="BU53" s="64"/>
+        <v>Norway</v>
+      </c>
+      <c r="BT53" s="62">
+        <v>0</v>
+      </c>
+      <c r="BU53" s="64">
+        <v>1</v>
+      </c>
       <c r="BV53" s="27"/>
-      <c r="BW53" s="112" t="str">
+      <c r="BW53" s="112">
         <f>IF(BW52="","",BT53*1000+BU53*10+BV53)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="BX53" s="112"/>
       <c r="BY53" s="21"/>
@@ -51149,11 +51277,11 @@
       </c>
       <c r="J54" s="35" t="str">
         <f>VLOOKUP(4,AD50:AN53,2,FALSE)</f>
-        <v>Cape Verde</v>
+        <v>Saudi Arabia</v>
       </c>
       <c r="K54" s="36">
         <f>L54+M54+N54</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="36">
         <f>VLOOKUP(4,AD50:AN53,3,FALSE)</f>
@@ -51165,11 +51293,11 @@
       </c>
       <c r="N54" s="36">
         <f>VLOOKUP(4,AD50:AN53,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O54" s="36" t="str">
         <f>VLOOKUP(4,AD50:AN53,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD50:AN53,7,FALSE)</f>
-        <v>0 - 7</v>
+        <v>0 - 5</v>
       </c>
       <c r="P54" s="37">
         <f>L54*3+M54</f>
@@ -51221,7 +51349,7 @@
       </c>
       <c r="AF54" s="123">
         <f t="shared" ref="AF54:AH54" si="25">MAX(AF50:AF53)-MIN(AF50:AF53)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG54" s="123">
         <f t="shared" si="25"/>
@@ -51229,31 +51357,31 @@
       </c>
       <c r="AH54" s="123">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI54" s="123">
         <f>MAX(AI50:AI53)+1</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL54" s="123">
         <f>MIN(AL50:AL53)</f>
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="AM54" s="123">
         <f>MAX(AM50:AM53)+1</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN54" s="123">
         <f>MAX(AN50:AN53)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO54" s="123">
         <f>MAX(AO50:AO53)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP54" s="123">
         <f>MAX(AP50:AP53)+1</f>
-        <v>85714296.923557252</v>
+        <v>90000011.186652496</v>
       </c>
       <c r="AT54" s="126">
         <f>MAX(AT50:AT53)-MIN(AT50:AT53)+1</f>
@@ -51308,14 +51436,20 @@
       </c>
       <c r="BL54" s="24" t="str">
         <f>AS74</f>
-        <v>1L</v>
-      </c>
-      <c r="BM54" s="61"/>
-      <c r="BN54" s="63"/>
-      <c r="BO54" s="25"/>
-      <c r="BP54" s="116" t="str">
+        <v>England</v>
+      </c>
+      <c r="BM54" s="61">
+        <v>1</v>
+      </c>
+      <c r="BN54" s="63">
+        <v>1</v>
+      </c>
+      <c r="BO54" s="25">
+        <v>5</v>
+      </c>
+      <c r="BP54" s="116">
         <f>IF(OR(BM54="",BM55="",AND(BN54="",BN55&lt;&gt;""),AND(BN55="",BN54&lt;&gt;""),AND(BO54="",BO55&lt;&gt;""),AND(BO55="",BO54&lt;&gt;"")),"",BM54*1000+BN54*10+BO54)</f>
-        <v/>
+        <v>1015</v>
       </c>
       <c r="BQ54" s="112"/>
       <c r="BR54" s="21"/>
@@ -51431,14 +51565,20 @@
       <c r="BK55" s="142"/>
       <c r="BL55" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!K3,AK80:AS91,9,FALSE),"3rd Group E/H/I/J/K")</f>
-        <v>3rd Group E/H/I/J/K</v>
-      </c>
-      <c r="BM55" s="62"/>
-      <c r="BN55" s="64"/>
-      <c r="BO55" s="27"/>
-      <c r="BP55" s="112" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="BM55" s="62">
+        <v>1</v>
+      </c>
+      <c r="BN55" s="64">
+        <v>1</v>
+      </c>
+      <c r="BO55" s="27">
+        <v>6</v>
+      </c>
+      <c r="BP55" s="112">
         <f>IF(BP54="","",BM55*1000+BN55*10+BO55)</f>
-        <v/>
+        <v>1016</v>
       </c>
       <c r="BQ55" s="112"/>
       <c r="BR55" s="21"/>
@@ -51460,14 +51600,18 @@
       </c>
       <c r="CG55" s="24" t="str">
         <f>IF(CD48&gt;CD49,BZ48,IF(CD48&lt;CD49,BZ49,""))</f>
-        <v/>
-      </c>
-      <c r="CH55" s="61"/>
-      <c r="CI55" s="63"/>
+        <v>Senegal</v>
+      </c>
+      <c r="CH55" s="61">
+        <v>2</v>
+      </c>
+      <c r="CI55" s="63">
+        <v>3</v>
+      </c>
       <c r="CJ55" s="25"/>
-      <c r="CK55" s="116" t="str">
+      <c r="CK55" s="116">
         <f>IF(OR(CH55="",CH56="",AND(CI55="",CI56&lt;&gt;""),AND(CI56="",CI55&lt;&gt;""),AND(CJ55="",CJ56&lt;&gt;""),AND(CJ56="",CJ55&lt;&gt;"")),"",CH55*1000+CI55*10+CJ55)</f>
-        <v/>
+        <v>2030</v>
       </c>
       <c r="CL55" s="112"/>
     </row>
@@ -51588,7 +51732,7 @@
       </c>
       <c r="AG56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH56" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE56 &amp; "_lose")</f>
@@ -51596,11 +51740,11 @@
       </c>
       <c r="AI56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE56,$G$7:$G$78)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ56" s="123">
         <f>SUMIF($E$7:$E$78,$AE56,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE56,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL56" s="123">
         <f>AI56-AJ56</f>
@@ -51608,19 +51752,19 @@
       </c>
       <c r="AM56" s="123">
         <f>AL56-AL60</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN56" s="123">
         <f>AF56*3+AG56</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO56" s="123">
         <f>AN56/AN60*10+BA56</f>
-        <v>8.5779859484777514</v>
+        <v>8.75</v>
       </c>
       <c r="AP56" s="123">
         <f>AO56*10000000+BI56*100+AM56/AM60*10+AI56/AI60*1++IF(AQ56=0,ROW(),AQ56)/2000000</f>
-        <v>85779869.342859015</v>
+        <v>87500010.056494221</v>
       </c>
       <c r="AQ56" s="126">
         <f>VLOOKUP(AE56,db_fifarank,2,FALSE)</f>
@@ -51628,11 +51772,11 @@
       </c>
       <c r="AR56" s="125">
         <f>AP56/AP60</f>
-        <v>0.99999998834225334</v>
+        <v>0.99999998857143002</v>
       </c>
       <c r="AS56" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J57,"1I")</f>
-        <v>1I</v>
+        <v>France</v>
       </c>
       <c r="AT56" s="126" cm="1">
         <f t="array" ref="AT56">SUMPRODUCT(($S$7:$S$78=AE56&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE56&amp;"_win")*($U$7:$U$78))</f>
@@ -51656,15 +51800,15 @@
       </c>
       <c r="AY56" s="126">
         <f>AX56-MIN(AX56:AX59)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ56" s="126">
         <f>AT56/AT60*1000+AU56/AU60*100+AY56/AY60*10+AV56/AV60</f>
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BA56" s="126">
         <f>AZ56/AZ60</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="BB56" s="126" cm="1">
         <f t="array" ref="BB56">SUMPRODUCT(($S$7:$S$78=AE56&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE56&amp;"_win")*($X$7:$X$78))</f>
@@ -51721,14 +51865,18 @@
       <c r="CF56" s="142"/>
       <c r="CG56" s="26" t="str">
         <f>IF(CD64&gt;CD65,BZ64,IF(CD64&lt;CD65,BZ65,""))</f>
-        <v/>
-      </c>
-      <c r="CH56" s="62"/>
-      <c r="CI56" s="64"/>
+        <v>Argentina</v>
+      </c>
+      <c r="CH56" s="62">
+        <v>2</v>
+      </c>
+      <c r="CI56" s="64">
+        <v>2</v>
+      </c>
       <c r="CJ56" s="27"/>
-      <c r="CK56" s="112" t="str">
+      <c r="CK56" s="112">
         <f>IF(CK55="","",CH56*1000+CI56*10+CJ56)</f>
-        <v/>
+        <v>2020</v>
       </c>
       <c r="CL56" s="112"/>
     </row>
@@ -51769,7 +51917,7 @@
       </c>
       <c r="K57" s="31">
         <f>L57+M57+N57</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" s="31">
         <f>VLOOKUP(1,AD56:AN59,3,FALSE)</f>
@@ -51777,7 +51925,7 @@
       </c>
       <c r="M57" s="31">
         <f>VLOOKUP(1,AD56:AN59,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="31">
         <f>VLOOKUP(1,AD56:AN59,5,FALSE)</f>
@@ -51785,11 +51933,11 @@
       </c>
       <c r="O57" s="31" t="str">
         <f>VLOOKUP(1,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD56:AN59,7,FALSE)</f>
-        <v>6 - 2</v>
+        <v>8 - 4</v>
       </c>
       <c r="P57" s="32">
         <f>L57*3+M57</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R57" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -51845,7 +51993,7 @@
       </c>
       <c r="AF57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG57" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE57 &amp; "_draw")</f>
@@ -51857,7 +52005,7 @@
       </c>
       <c r="AI57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE57,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ57" s="123">
         <f>SUMIF($E$7:$E$78,$AE57,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE57,$F$7:$F$78)</f>
@@ -51865,23 +52013,23 @@
       </c>
       <c r="AL57" s="123">
         <f>AI57-AJ57</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM57" s="123">
         <f>AL57-AL60</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN57" s="123">
         <f>AF57*3+AG57</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO57" s="123">
         <f>AN57/AN60*10+BA57</f>
-        <v>5.2837470725995317</v>
+        <v>7.5</v>
       </c>
       <c r="AP57" s="123">
         <f>AO57*10000000+BI57*100+AM57/AM60*10+AI57/AI60*1++IF(AQ57=0,ROW(),AQ57)/2000000</f>
-        <v>52837476.298268385</v>
+        <v>75000008.167511165</v>
       </c>
       <c r="AQ57" s="126">
         <f>VLOOKUP(AE57,db_fifarank,2,FALSE)</f>
@@ -51889,15 +52037,15 @@
       </c>
       <c r="AR57" s="125">
         <f>AP57/AP60</f>
-        <v>0.61596591469629081</v>
+        <v>0.85714284217732895</v>
       </c>
       <c r="AS57" s="125" t="str">
         <f>IF(SUM(AF56:AH59)=12,J58,"2I")</f>
-        <v>2I</v>
+        <v>Senegal</v>
       </c>
       <c r="AT57" s="126" cm="1">
         <f t="array" ref="AT57">SUMPRODUCT(($S$7:$S$78=AE57&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE57&amp;"_win")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU57" s="126" cm="1">
         <f t="array" ref="AU57">SUMPRODUCT(($S$7:$S$78=AE57&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE57&amp;"_draw")*($U$7:$U$78))</f>
@@ -51905,27 +52053,27 @@
       </c>
       <c r="AV57" s="126" cm="1">
         <f t="array" ref="AV57">SUMPRODUCT(($E$7:$E$78=AE57)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE57)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW57" s="126" cm="1">
         <f t="array" ref="AW57">SUMPRODUCT(($E$7:$E$78=AE57)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE57)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX57" s="126">
         <f>AV57-AW57</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY57" s="126">
         <f>AX57-MIN(AX56:AX59)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ57" s="126">
         <f>AT57/AT60*1000+AU57/AU60*100+AY57/AY60*10+AV57/AV60</f>
-        <v>507.33333333333337</v>
+        <v>0</v>
       </c>
       <c r="BA57" s="126">
         <f>AZ57/AZ60</f>
-        <v>0.99803278688524588</v>
+        <v>0</v>
       </c>
       <c r="BB57" s="126" cm="1">
         <f t="array" ref="BB57">SUMPRODUCT(($S$7:$S$78=AE57&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE57&amp;"_win")*($X$7:$X$78))</f>
@@ -52023,11 +52171,11 @@
       </c>
       <c r="K58" s="23">
         <f>L58+M58+N58</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="23">
         <f>VLOOKUP(2,AD56:AN59,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="23">
         <f>VLOOKUP(2,AD56:AN59,4,FALSE)</f>
@@ -52039,11 +52187,11 @@
       </c>
       <c r="O58" s="23" t="str">
         <f>VLOOKUP(2,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD56:AN59,7,FALSE)</f>
-        <v>4 - 4</v>
+        <v>6 - 4</v>
       </c>
       <c r="P58" s="34">
         <f>L58*3+M58</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R58" s="123">
         <f>DATE(2026,6,24)+TIME(8,0,0)+gmt_delta</f>
@@ -52107,7 +52255,7 @@
       </c>
       <c r="AH58" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE58 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE58,$G$7:$G$78)</f>
@@ -52115,11 +52263,11 @@
       </c>
       <c r="AJ58" s="123">
         <f>SUMIF($E$7:$E$78,$AE58,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE58,$F$7:$F$78)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL58" s="123">
         <f>AI58-AJ58</f>
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="AM58" s="123">
         <f>AL58-AL60</f>
@@ -52131,11 +52279,11 @@
       </c>
       <c r="AO58" s="123">
         <f>AN58/AN60*10+BA58</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="AP58" s="123">
         <f>AO58*10000000+BI58*100+AM58/AM60*10+AI58/AI60*1++IF(AQ58=0,ROW(),AQ58)/2000000</f>
-        <v>65573.914072516127</v>
+        <v>0.11183468111111111</v>
       </c>
       <c r="AQ58" s="126">
         <f>VLOOKUP(AE58,db_fifarank,2,FALSE)</f>
@@ -52143,7 +52291,7 @@
       </c>
       <c r="AR58" s="125">
         <f>AP58/AP60</f>
-        <v>7.6444408006703186E-4</v>
+        <v>1.2781104797678854E-9</v>
       </c>
       <c r="AT58" s="126" cm="1">
         <f t="array" ref="AT58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($U$7:$U$78))</f>
@@ -52167,15 +52315,15 @@
       </c>
       <c r="AY58" s="126">
         <f>AX58-MIN(AX56:AX59)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ58" s="126">
         <f>AT58/AT60*1000+AU58/AU60*100+AY58/AY60*10+AV58/AV60</f>
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BA58" s="126">
         <f>AZ58/AZ60</f>
-        <v>6.557377049180327E-3</v>
+        <v>0</v>
       </c>
       <c r="BB58" s="126" cm="1">
         <f t="array" ref="BB58">SUMPRODUCT(($S$7:$S$78=AE58&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE58&amp;"_win")*($X$7:$X$78))</f>
@@ -52214,14 +52362,16 @@
       </c>
       <c r="BL58" s="24" t="str">
         <f>AS62</f>
-        <v>1J</v>
-      </c>
-      <c r="BM58" s="61"/>
+        <v>Argentina</v>
+      </c>
+      <c r="BM58" s="61">
+        <v>2</v>
+      </c>
       <c r="BN58" s="63"/>
       <c r="BO58" s="25"/>
-      <c r="BP58" s="112" t="str">
+      <c r="BP58" s="112">
         <f>IF(OR(BM58="",BM59="",AND(BN58="",BN59&lt;&gt;""),AND(BN59="",BN58&lt;&gt;""),AND(BO58="",BO59&lt;&gt;""),AND(BO59="",BO58&lt;&gt;"")),"",BM58*1000+BN58*10+BO58)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ58" s="112"/>
       <c r="BR58" s="21"/>
@@ -52275,7 +52425,7 @@
       </c>
       <c r="K59" s="23">
         <f>L59+M59+N59</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L59" s="23">
         <f>VLOOKUP(3,AD56:AN59,3,FALSE)</f>
@@ -52283,7 +52433,7 @@
       </c>
       <c r="M59" s="23">
         <f>VLOOKUP(3,AD56:AN59,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="23">
         <f>VLOOKUP(3,AD56:AN59,5,FALSE)</f>
@@ -52291,11 +52441,11 @@
       </c>
       <c r="O59" s="23" t="str">
         <f>VLOOKUP(3,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD56:AN59,7,FALSE)</f>
-        <v>4 - 3</v>
+        <v>6 - 5</v>
       </c>
       <c r="P59" s="34">
         <f>L59*3+M59</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R59" s="123">
         <f>DATE(2026,6,24)+TIME(14,0,0)+gmt_delta</f>
@@ -52355,7 +52505,7 @@
       </c>
       <c r="AG59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH59" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE59 &amp; "_lose")</f>
@@ -52363,11 +52513,11 @@
       </c>
       <c r="AI59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE59,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ59" s="123">
         <f>SUMIF($E$7:$E$78,$AE59,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE59,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL59" s="123">
         <f>AI59-AJ59</f>
@@ -52375,19 +52525,19 @@
       </c>
       <c r="AM59" s="123">
         <f>AL59-AL60</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN59" s="123">
         <f>AF59*3+AG59</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO59" s="123">
         <f>AN59/AN60*10+BA59</f>
-        <v>4.2863700234192033</v>
+        <v>5</v>
       </c>
       <c r="AP59" s="123">
         <f>AO59*10000000+BI59*100+AM59/AM60*10+AI59/AI60*1++IF(AQ59=0,ROW(),AQ59)/2000000</f>
-        <v>42863706.806396082</v>
+        <v>50000007.3341088</v>
       </c>
       <c r="AQ59" s="126">
         <f>VLOOKUP(AE59,db_fifarank,2,FALSE)</f>
@@ -52395,7 +52545,7 @@
       </c>
       <c r="AR59" s="125">
         <f>AP59/AP60</f>
-        <v>0.49969423636421234</v>
+        <v>0.57142858304127975</v>
       </c>
       <c r="AT59" s="126" cm="1">
         <f t="array" ref="AT59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($U$7:$U$78))</f>
@@ -52407,15 +52557,15 @@
       </c>
       <c r="AV59" s="126" cm="1">
         <f t="array" ref="AV59">SUMPRODUCT(($E$7:$E$78=AE59)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE59)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW59" s="126" cm="1">
         <f t="array" ref="AW59">SUMPRODUCT(($E$7:$E$78=AE59)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE59)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX59" s="126">
         <f>AV59-AW59</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY59" s="126">
         <f>AX59-MIN(AX56:AX59)</f>
@@ -52423,11 +52573,11 @@
       </c>
       <c r="AZ59" s="126">
         <f>AT59/AT60*1000+AU59/AU60*100+AY59/AY60*10+AV59/AV60</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="BA59" s="126">
         <f>AZ59/AZ60</f>
-        <v>6.5573770491803268E-4</v>
+        <v>0</v>
       </c>
       <c r="BB59" s="126" cm="1">
         <f t="array" ref="BB59">SUMPRODUCT(($S$7:$S$78=AE59&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE59&amp;"_win")*($X$7:$X$78))</f>
@@ -52464,14 +52614,16 @@
       <c r="BK59" s="142"/>
       <c r="BL59" s="26" t="str">
         <f>AS51</f>
-        <v>2H</v>
-      </c>
-      <c r="BM59" s="62"/>
+        <v>Uruguay</v>
+      </c>
+      <c r="BM59" s="62">
+        <v>1</v>
+      </c>
       <c r="BN59" s="64"/>
       <c r="BO59" s="27"/>
-      <c r="BP59" s="113" t="str">
+      <c r="BP59" s="113">
         <f>IF(BP58="","",BM59*1000+BN59*10+BO59)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ59" s="112"/>
       <c r="BR59" s="21" t="str" cm="1">
@@ -52514,8 +52666,12 @@
         <f>AE9</f>
         <v>South Africa</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="20"/>
+      <c r="F60" s="19">
+        <v>0</v>
+      </c>
+      <c r="G60" s="20">
+        <v>1</v>
+      </c>
       <c r="H60" s="80" t="str">
         <f>AE10</f>
         <v>Korea Republic</v>
@@ -52527,7 +52683,7 @@
       </c>
       <c r="K60" s="36">
         <f>L60+M60+N60</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="36">
         <f>VLOOKUP(4,AD56:AN59,3,FALSE)</f>
@@ -52539,11 +52695,11 @@
       </c>
       <c r="N60" s="36">
         <f>VLOOKUP(4,AD56:AN59,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O60" s="36" t="str">
         <f>VLOOKUP(4,AD56:AN59,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD56:AN59,7,FALSE)</f>
-        <v>1 - 6</v>
+        <v>1 - 8</v>
       </c>
       <c r="P60" s="37">
         <f>L60*3+M60</f>
@@ -52555,11 +52711,11 @@
       </c>
       <c r="S60" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>South Africa_lose</v>
       </c>
       <c r="T60" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Korea Republic_win</v>
       </c>
       <c r="U60" s="123">
         <f t="shared" si="8"/>
@@ -52589,9 +52745,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB60" s="123" t="str">
+      <c r="AB60" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF60" s="123">
         <f t="shared" ref="AF60:AH60" si="27">MAX(AF56:AF59)-MIN(AF56:AF59)+1</f>
@@ -52599,39 +52755,39 @@
       </c>
       <c r="AG60" s="123">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH60" s="123">
         <f t="shared" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI60" s="123">
         <f>MAX(AI56:AI59)+1</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL60" s="123">
         <f>MIN(AL56:AL59)</f>
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="AM60" s="123">
         <f>MAX(AM56:AM59)+1</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN60" s="123">
         <f>MAX(AN56:AN59)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO60" s="123">
         <f>MAX(AO56:AO59)+1</f>
-        <v>9.5779859484777514</v>
+        <v>9.75</v>
       </c>
       <c r="AP60" s="123">
         <f>MAX(AP56:AP59)+1</f>
-        <v>85779870.342859015</v>
+        <v>87500011.056494221</v>
       </c>
       <c r="AT60" s="126">
         <f>MAX(AT56:AT59)-MIN(AT56:AT59)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU60" s="126">
         <f>MAX(AU56:AU59)-MIN(AU56:AU59)+1</f>
@@ -52639,19 +52795,19 @@
       </c>
       <c r="AV60" s="126">
         <f>MAX(AV56:AV59)-MIN(AV56:AV59)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW60" s="126">
         <f>MAX(AW56:AW59)-MIN(AW56:AW59)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY60" s="126">
         <f>MAX(AY56:AY59)-MIN(AY56:AY59)+1</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ60" s="126">
         <f>MAX(AZ56:AZ59)+1</f>
-        <v>508.33333333333337</v>
+        <v>1</v>
       </c>
       <c r="BB60" s="126">
         <f>MAX(BB56:BB59)-MIN(BB56:BB59)+1</f>
@@ -52689,14 +52845,16 @@
       </c>
       <c r="BS60" s="24" t="str">
         <f>IF(BP58&gt;BP59,BL58,IF(BP58&lt;BP59,BL59,""))</f>
-        <v/>
-      </c>
-      <c r="BT60" s="61"/>
+        <v>Argentina</v>
+      </c>
+      <c r="BT60" s="61">
+        <v>2</v>
+      </c>
       <c r="BU60" s="63"/>
       <c r="BV60" s="25"/>
-      <c r="BW60" s="112" t="str">
+      <c r="BW60" s="112">
         <f>IF(OR(BT60="",BT61="",AND(BU60="",BU61&lt;&gt;""),AND(BU61="",BU60&lt;&gt;""),AND(BV60="",BV61&lt;&gt;""),AND(BV61="",BV60&lt;&gt;"")),"",BT60*1000+BU60*10+BV60)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BX60" s="112"/>
       <c r="BY60" s="21"/>
@@ -52726,8 +52884,12 @@
         <f>AE33</f>
         <v>Curaçao</v>
       </c>
-      <c r="F61" s="19"/>
-      <c r="G61" s="20"/>
+      <c r="F61" s="19">
+        <v>1</v>
+      </c>
+      <c r="G61" s="20">
+        <v>1</v>
+      </c>
       <c r="H61" s="80" t="str">
         <f>AE34</f>
         <v>Ivory Coast</v>
@@ -52746,43 +52908,43 @@
       </c>
       <c r="S61" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Curaçao_draw</v>
       </c>
       <c r="T61" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Ivory Coast_draw</v>
       </c>
       <c r="U61" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z61" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" s="123">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB61" s="123" t="str">
+      <c r="AB61" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK61" s="21" t="str" cm="1">
         <f t="array" ref="BK61">INDEX(T,24+MONTH(BP61),lang) &amp; " " &amp; DAY(BP61) &amp; ", " &amp; YEAR(BP61) &amp; "   " &amp; (IF(HOUR(BP61)&lt;10,0,"")&amp;HOUR(BP61)) &amp; ":" &amp;  (IF(MINUTE(BP61)&lt;10,0,"")&amp;MINUTE(BP61))</f>
@@ -52800,14 +52962,16 @@
       <c r="BR61" s="142"/>
       <c r="BS61" s="26" t="str">
         <f>IF(BP62&gt;BP63,BL62,IF(BP62&lt;BP63,BL63,""))</f>
-        <v/>
-      </c>
-      <c r="BT61" s="62"/>
+        <v>Turkey</v>
+      </c>
+      <c r="BT61" s="62">
+        <v>1</v>
+      </c>
       <c r="BU61" s="64"/>
       <c r="BV61" s="27"/>
-      <c r="BW61" s="113" t="str">
+      <c r="BW61" s="113">
         <f>IF(BW60="","",BT61*1000+BU61*10+BV61)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BX61" s="112"/>
       <c r="BY61" s="21"/>
@@ -52837,8 +53001,12 @@
         <f>AE35</f>
         <v>Ecuador</v>
       </c>
-      <c r="F62" s="19"/>
-      <c r="G62" s="20"/>
+      <c r="F62" s="19">
+        <v>1</v>
+      </c>
+      <c r="G62" s="20">
+        <v>3</v>
+      </c>
       <c r="H62" s="80" t="str">
         <f>AE32</f>
         <v>Germany</v>
@@ -52878,11 +53046,11 @@
       </c>
       <c r="S62" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Ecuador_lose</v>
       </c>
       <c r="T62" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Germany_win</v>
       </c>
       <c r="U62" s="123">
         <f t="shared" si="8"/>
@@ -52912,9 +53080,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB62" s="123" t="str">
+      <c r="AB62" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD62" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR62))</f>
@@ -52926,7 +53094,7 @@
       </c>
       <c r="AF62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG62" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE62 &amp; "_draw")</f>
@@ -52938,7 +53106,7 @@
       </c>
       <c r="AI62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE62,$G$7:$G$78)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ62" s="123">
         <f>SUMIF($E$7:$E$78,$AE62,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE62,$F$7:$F$78)</f>
@@ -52946,23 +53114,23 @@
       </c>
       <c r="AL62" s="123">
         <f>AI62-AJ62</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM62" s="123">
         <f>AL62-AL66</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN62" s="123">
         <f>AF62*3+AG62</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO62" s="123">
         <f>AN62/AN66*10+BA62</f>
-        <v>8.5714285714285712</v>
+        <v>9</v>
       </c>
       <c r="AP62" s="123">
         <f>AO62*10000000+BI62*100+AM62/AM66*10+AI62/AI66*1++IF(AQ62=0,ROW(),AQ62)/2000000</f>
-        <v>85714295.119985029</v>
+        <v>90000009.966846511</v>
       </c>
       <c r="AQ62" s="126">
         <f>VLOOKUP(AE62,db_fifarank,2,FALSE)</f>
@@ -52970,11 +53138,11 @@
       </c>
       <c r="AR62" s="125">
         <f>AP62/AP66</f>
-        <v>0.9999999883333347</v>
+        <v>0.99999998888889019</v>
       </c>
       <c r="AS62" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J63,"1J")</f>
-        <v>1J</v>
+        <v>Argentina</v>
       </c>
       <c r="AT62" s="126" cm="1">
         <f t="array" ref="AT62">SUMPRODUCT(($S$7:$S$78=AE62&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE62&amp;"_win")*($U$7:$U$78))</f>
@@ -53045,14 +53213,16 @@
       </c>
       <c r="BL62" s="24" t="str">
         <f>AS27</f>
-        <v>2D</v>
-      </c>
-      <c r="BM62" s="61"/>
+        <v>Turkey</v>
+      </c>
+      <c r="BM62" s="61">
+        <v>2</v>
+      </c>
       <c r="BN62" s="63"/>
       <c r="BO62" s="25"/>
-      <c r="BP62" s="116" t="str">
+      <c r="BP62" s="116">
         <f>IF(OR(BM62="",BM63="",AND(BN62="",BN63&lt;&gt;""),AND(BN63="",BN62&lt;&gt;""),AND(BO62="",BO63&lt;&gt;""),AND(BO63="",BO62&lt;&gt;"")),"",BM62*1000+BN62*10+BO62)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ62" s="112"/>
       <c r="BR62" s="21"/>
@@ -53089,8 +53259,12 @@
         <f>AE39</f>
         <v>Japan</v>
       </c>
-      <c r="F63" s="19"/>
-      <c r="G63" s="20"/>
+      <c r="F63" s="19">
+        <v>2</v>
+      </c>
+      <c r="G63" s="20">
+        <v>2</v>
+      </c>
       <c r="H63" s="80" t="str">
         <f>AE40</f>
         <v>Sweden</v>
@@ -53102,11 +53276,11 @@
       </c>
       <c r="K63" s="31">
         <f>L63+M63+N63</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="31">
         <f>VLOOKUP(1,AD62:AN65,3,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63" s="31">
         <f>VLOOKUP(1,AD62:AN65,4,FALSE)</f>
@@ -53118,11 +53292,11 @@
       </c>
       <c r="O63" s="31" t="str">
         <f>VLOOKUP(1,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD62:AN65,7,FALSE)</f>
-        <v>5 - 1</v>
+        <v>7 - 1</v>
       </c>
       <c r="P63" s="32">
         <f>L63*3+M63</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R63" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -53130,43 +53304,43 @@
       </c>
       <c r="S63" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Japan_draw</v>
       </c>
       <c r="T63" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Sweden_draw</v>
       </c>
       <c r="U63" s="123">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W63" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X63" s="123">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="123">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z63" s="123">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA63" s="123">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB63" s="123" t="str">
+      <c r="AB63" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD63" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR63))</f>
@@ -53182,7 +53356,7 @@
       </c>
       <c r="AG63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH63" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE63 &amp; "_lose")</f>
@@ -53190,11 +53364,11 @@
       </c>
       <c r="AI63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE63,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ63" s="123">
         <f>SUMIF($E$7:$E$78,$AE63,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE63,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL63" s="123">
         <f>AI63-AJ63</f>
@@ -53202,19 +53376,19 @@
       </c>
       <c r="AM63" s="123">
         <f>AL63-AL66</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN63" s="123">
         <f>AF63*3+AG63</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO63" s="123">
         <f>AN63/AN66*10+BA63</f>
-        <v>4.2857142857142856</v>
+        <v>4.9805825242718447</v>
       </c>
       <c r="AP63" s="123">
         <f>AO63*10000000+BI63*100+AM63/AM66*10+AI63/AI66*1++IF(AQ63=0,ROW(),AQ63)/2000000</f>
-        <v>42857144.619829752</v>
+        <v>49805926.404025726</v>
       </c>
       <c r="AQ63" s="126">
         <f>VLOOKUP(AE63,db_fifarank,2,FALSE)</f>
@@ -53222,11 +53396,11 @@
       </c>
       <c r="AR63" s="125">
         <f>AP63/AP66</f>
-        <v>0.49999995986477264</v>
+        <v>0.55339911483313975</v>
       </c>
       <c r="AS63" s="125" t="str">
         <f>IF(SUM(AF62:AH65)=12,J64,"2J")</f>
-        <v>2J</v>
+        <v>Algeria</v>
       </c>
       <c r="AT63" s="126" cm="1">
         <f t="array" ref="AT63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_win")*($U$7:$U$78))</f>
@@ -53234,15 +53408,15 @@
       </c>
       <c r="AU63" s="126" cm="1">
         <f t="array" ref="AU63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" s="126" cm="1">
         <f t="array" ref="AV63">SUMPRODUCT(($E$7:$E$78=AE63)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW63" s="126" cm="1">
         <f t="array" ref="AW63">SUMPRODUCT(($E$7:$E$78=AE63)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX63" s="126">
         <f>AV63-AW63</f>
@@ -53254,11 +53428,11 @@
       </c>
       <c r="AZ63" s="126">
         <f>AT63/AT66*1000+AU63/AU66*100+AY63/AY66*10+AV63/AV66</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA63" s="126">
         <f>AZ63/AZ66</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB63" s="126" cm="1">
         <f t="array" ref="BB63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_win")*($X$7:$X$78))</f>
@@ -53266,15 +53440,15 @@
       </c>
       <c r="BC63" s="126" cm="1">
         <f t="array" ref="BC63">SUMPRODUCT(($S$7:$S$78=AE63&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE63&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD63" s="126" cm="1">
         <f t="array" ref="BD63">SUMPRODUCT(($E$7:$E$78=AE63)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE63" s="126" cm="1">
         <f t="array" ref="BE63">SUMPRODUCT(($E$7:$E$78=AE63)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE63)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF63" s="126">
         <f>BD63-BE63</f>
@@ -53286,23 +53460,25 @@
       </c>
       <c r="BH63" s="126">
         <f>BB63/BB66*1000+BC63/BC66*100+BG63/BG66*10+BD63/BD66</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI63" s="126">
         <f>BH63/BH66</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK63" s="142"/>
       <c r="BL63" s="26" t="str">
         <f>AS45</f>
-        <v>2G</v>
-      </c>
-      <c r="BM63" s="62"/>
+        <v>Egypt</v>
+      </c>
+      <c r="BM63" s="62">
+        <v>1</v>
+      </c>
       <c r="BN63" s="64"/>
       <c r="BO63" s="27"/>
-      <c r="BP63" s="112" t="str">
+      <c r="BP63" s="112">
         <f>IF(BP62="","",BM63*1000+BN63*10+BO63)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="BQ63" s="112"/>
       <c r="BR63" s="21"/>
@@ -53345,8 +53521,12 @@
         <f>AE41</f>
         <v>Tunisia</v>
       </c>
-      <c r="F64" s="19"/>
-      <c r="G64" s="20"/>
+      <c r="F64" s="19">
+        <v>0</v>
+      </c>
+      <c r="G64" s="20">
+        <v>0</v>
+      </c>
       <c r="H64" s="80" t="str">
         <f>AE38</f>
         <v>Netherlands</v>
@@ -53358,7 +53538,7 @@
       </c>
       <c r="K64" s="23">
         <f>L64+M64+N64</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="23">
         <f>VLOOKUP(2,AD62:AN65,3,FALSE)</f>
@@ -53366,7 +53546,7 @@
       </c>
       <c r="M64" s="23">
         <f>VLOOKUP(2,AD62:AN65,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" s="23">
         <f>VLOOKUP(2,AD62:AN65,5,FALSE)</f>
@@ -53374,11 +53554,11 @@
       </c>
       <c r="O64" s="23" t="str">
         <f>VLOOKUP(2,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD62:AN65,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>3 - 4</v>
       </c>
       <c r="P64" s="34">
         <f>L64*3+M64</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R64" s="123">
         <f>DATE(2026,6,25)+TIME(12,0,0)+gmt_delta</f>
@@ -53386,11 +53566,11 @@
       </c>
       <c r="S64" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Tunisia_draw</v>
       </c>
       <c r="T64" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Netherlands_draw</v>
       </c>
       <c r="U64" s="123">
         <f t="shared" si="8"/>
@@ -53420,9 +53600,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB64" s="123" t="str">
+      <c r="AB64" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD64" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR64))</f>
@@ -53438,7 +53618,7 @@
       </c>
       <c r="AG64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH64" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE64 &amp; "_lose")</f>
@@ -53446,11 +53626,11 @@
       </c>
       <c r="AI64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE64,$G$7:$G$78)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ64" s="123">
         <f>SUMIF($E$7:$E$78,$AE64,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE64,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL64" s="123">
         <f>AI64-AJ64</f>
@@ -53458,19 +53638,19 @@
       </c>
       <c r="AM64" s="123">
         <f>AL64-AL66</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN64" s="123">
         <f>AF64*3+AG64</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO64" s="123">
         <f>AN64/AN66*10+BA64</f>
-        <v>4.2857142857142856</v>
+        <v>4.9805825242718447</v>
       </c>
       <c r="AP64" s="123">
         <f>AO64*10000000+BI64*100+AM64/AM66*10+AI64/AI66*1++IF(AQ64=0,ROW(),AQ64)/2000000</f>
-        <v>42857144.453177676</v>
+        <v>49805926.279040322</v>
       </c>
       <c r="AQ64" s="126">
         <f>VLOOKUP(AE64,db_fifarank,2,FALSE)</f>
@@ -53478,7 +53658,7 @@
       </c>
       <c r="AR64" s="125">
         <f>AP64/AP66</f>
-        <v>0.49999995792049867</v>
+        <v>0.55339911344441317</v>
       </c>
       <c r="AT64" s="126" cm="1">
         <f t="array" ref="AT64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($U$7:$U$78))</f>
@@ -53486,15 +53666,15 @@
       </c>
       <c r="AU64" s="126" cm="1">
         <f t="array" ref="AU64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV64" s="126" cm="1">
         <f t="array" ref="AV64">SUMPRODUCT(($E$7:$E$78=AE64)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW64" s="126" cm="1">
         <f t="array" ref="AW64">SUMPRODUCT(($E$7:$E$78=AE64)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX64" s="126">
         <f>AV64-AW64</f>
@@ -53506,11 +53686,11 @@
       </c>
       <c r="AZ64" s="126">
         <f>AT64/AT66*1000+AU64/AU66*100+AY64/AY66*10+AV64/AV66</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BA64" s="126">
         <f>AZ64/AZ66</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BB64" s="126" cm="1">
         <f t="array" ref="BB64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_win")*($X$7:$X$78))</f>
@@ -53518,15 +53698,15 @@
       </c>
       <c r="BC64" s="126" cm="1">
         <f t="array" ref="BC64">SUMPRODUCT(($S$7:$S$78=AE64&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE64&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD64" s="126" cm="1">
         <f t="array" ref="BD64">SUMPRODUCT(($E$7:$E$78=AE64)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE64" s="126" cm="1">
         <f t="array" ref="BE64">SUMPRODUCT(($E$7:$E$78=AE64)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE64)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF64" s="126">
         <f>BD64-BE64</f>
@@ -53538,11 +53718,11 @@
       </c>
       <c r="BH64" s="126">
         <f>BB64/BB66*1000+BC64/BC66*100+BG64/BG66*10+BD64/BD66</f>
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="BI64" s="126">
         <f>BH64/BH66</f>
-        <v>0</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="BK64" s="21"/>
       <c r="BL64" s="21"/>
@@ -53563,14 +53743,18 @@
       </c>
       <c r="BZ64" s="24" t="str">
         <f>IF(BW60&gt;BW61,BS60,IF(BW60&lt;BW61,BS61,""))</f>
-        <v/>
-      </c>
-      <c r="CA64" s="61"/>
-      <c r="CB64" s="63"/>
+        <v>Argentina</v>
+      </c>
+      <c r="CA64" s="61">
+        <v>2</v>
+      </c>
+      <c r="CB64" s="63">
+        <v>3</v>
+      </c>
       <c r="CC64" s="25"/>
-      <c r="CD64" s="116" t="str">
+      <c r="CD64" s="116">
         <f>IF(OR(CA64="",CA65="",AND(CB64="",CB65&lt;&gt;""),AND(CB65="",CB64&lt;&gt;""),AND(CC64="",CC65&lt;&gt;""),AND(CC65="",CC64&lt;&gt;"")),"",CA64*1000+CB64*10+CC64)</f>
-        <v/>
+        <v>2030</v>
       </c>
     </row>
     <row r="65" spans="1:95" x14ac:dyDescent="0.25">
@@ -53593,8 +53777,12 @@
         <f>AE29</f>
         <v>Turkey</v>
       </c>
-      <c r="F65" s="19"/>
-      <c r="G65" s="20"/>
+      <c r="F65" s="19">
+        <v>1</v>
+      </c>
+      <c r="G65" s="20">
+        <v>1</v>
+      </c>
       <c r="H65" s="80" t="str">
         <f>AE26</f>
         <v>United States</v>
@@ -53606,7 +53794,7 @@
       </c>
       <c r="K65" s="23">
         <f>L65+M65+N65</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="23">
         <f>VLOOKUP(3,AD62:AN65,3,FALSE)</f>
@@ -53614,7 +53802,7 @@
       </c>
       <c r="M65" s="23">
         <f>VLOOKUP(3,AD62:AN65,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="23">
         <f>VLOOKUP(3,AD62:AN65,5,FALSE)</f>
@@ -53622,11 +53810,11 @@
       </c>
       <c r="O65" s="23" t="str">
         <f>VLOOKUP(3,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD62:AN65,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>2 - 3</v>
       </c>
       <c r="P65" s="34">
         <f>L65*3+M65</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R65" s="123">
         <f>DATE(2026,6,25)+TIME(15,0,0)+gmt_delta</f>
@@ -53634,11 +53822,11 @@
       </c>
       <c r="S65" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Turkey_draw</v>
       </c>
       <c r="T65" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>United States_draw</v>
       </c>
       <c r="U65" s="123">
         <f t="shared" si="8"/>
@@ -53668,9 +53856,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB65" s="123" t="str">
+      <c r="AB65" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD65" s="123">
         <f>COUNTIF(AR62:AR65,CONCATENATE("&gt;=",AR65))</f>
@@ -53690,7 +53878,7 @@
       </c>
       <c r="AH65" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE65 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE65,$G$7:$G$78)</f>
@@ -53698,11 +53886,11 @@
       </c>
       <c r="AJ65" s="123">
         <f>SUMIF($E$7:$E$78,$AE65,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE65,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL65" s="123">
         <f>AI65-AJ65</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AM65" s="123">
         <f>AL65-AL66</f>
@@ -53726,7 +53914,7 @@
       </c>
       <c r="AR65" s="125">
         <f>AP65/AP66</f>
-        <v>8.1167906812896954E-12</v>
+        <v>7.7302768358137833E-12</v>
       </c>
       <c r="AT65" s="126" cm="1">
         <f t="array" ref="AT65">SUMPRODUCT(($S$7:$S$78=AE65&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE65&amp;"_win")*($U$7:$U$78))</f>
@@ -53815,14 +54003,18 @@
       <c r="BY65" s="142"/>
       <c r="BZ65" s="26" t="str">
         <f>IF(BW68&gt;BW69,BS68,IF(BW68&lt;BW69,BS69,""))</f>
-        <v/>
-      </c>
-      <c r="CA65" s="62"/>
-      <c r="CB65" s="64"/>
+        <v>Portugal</v>
+      </c>
+      <c r="CA65" s="62">
+        <v>2</v>
+      </c>
+      <c r="CB65" s="64">
+        <v>2</v>
+      </c>
       <c r="CC65" s="27"/>
-      <c r="CD65" s="112" t="str">
+      <c r="CD65" s="112">
         <f>IF(CD64="","",CA65*1000+CB65*10+CC65)</f>
-        <v/>
+        <v>2020</v>
       </c>
     </row>
     <row r="66" spans="1:95" x14ac:dyDescent="0.25">
@@ -53845,8 +54037,12 @@
         <f>AE27</f>
         <v>Paraguay</v>
       </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="20"/>
+      <c r="F66" s="19">
+        <v>0</v>
+      </c>
+      <c r="G66" s="20">
+        <v>1</v>
+      </c>
       <c r="H66" s="80" t="str">
         <f>AE28</f>
         <v>Australia</v>
@@ -53858,7 +54054,7 @@
       </c>
       <c r="K66" s="36">
         <f>L66+M66+N66</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="36">
         <f>VLOOKUP(4,AD62:AN65,3,FALSE)</f>
@@ -53870,11 +54066,11 @@
       </c>
       <c r="N66" s="36">
         <f>VLOOKUP(4,AD62:AN65,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" s="36" t="str">
         <f>VLOOKUP(4,AD62:AN65,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD62:AN65,7,FALSE)</f>
-        <v>0 - 2</v>
+        <v>0 - 4</v>
       </c>
       <c r="P66" s="37">
         <f>L66*3+M66</f>
@@ -53886,11 +54082,11 @@
       </c>
       <c r="S66" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Paraguay_lose</v>
       </c>
       <c r="T66" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Australia_win</v>
       </c>
       <c r="U66" s="123">
         <f t="shared" si="8"/>
@@ -53920,45 +54116,45 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB66" s="123" t="str">
+      <c r="AB66" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF66" s="123">
         <f t="shared" ref="AF66:AH66" si="28">MAX(AF62:AF65)-MIN(AF62:AF65)+1</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG66" s="123">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH66" s="123">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI66" s="123">
         <f>MAX(AI62:AI65)+1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL66" s="123">
         <f>MIN(AL62:AL65)</f>
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AM66" s="123">
         <f>MAX(AM62:AM65)+1</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AN66" s="123">
         <f>MAX(AN62:AN65)+1</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO66" s="123">
         <f>MAX(AO62:AO65)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10</v>
       </c>
       <c r="AP66" s="123">
         <f>MAX(AP62:AP65)+1</f>
-        <v>85714296.119985029</v>
+        <v>90000010.966846511</v>
       </c>
       <c r="AT66" s="126">
         <f>MAX(AT62:AT65)-MIN(AT62:AT65)+1</f>
@@ -53966,15 +54162,15 @@
       </c>
       <c r="AU66" s="126">
         <f>MAX(AU62:AU65)-MIN(AU62:AU65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV66" s="126">
         <f>MAX(AV62:AV65)-MIN(AV62:AV65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW66" s="126">
         <f>MAX(AW62:AW65)-MIN(AW62:AW65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY66" s="126">
         <f>MAX(AY62:AY65)-MIN(AY62:AY65)+1</f>
@@ -53982,7 +54178,7 @@
       </c>
       <c r="AZ66" s="126">
         <f>MAX(AZ62:AZ65)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BB66" s="126">
         <f>MAX(BB62:BB65)-MIN(BB62:BB65)+1</f>
@@ -53990,15 +54186,15 @@
       </c>
       <c r="BC66" s="126">
         <f>MAX(BC62:BC65)-MIN(BC62:BC65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD66" s="126">
         <f>MAX(BD62:BD65)-MIN(BD62:BD65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE66" s="126">
         <f>MAX(BE62:BE65)-MIN(BE62:BE65)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG66" s="126">
         <f>MAX(BG62:BG65)-MIN(BG62:BG65)+1</f>
@@ -54006,7 +54202,7 @@
       </c>
       <c r="BH66" s="126">
         <f>MAX(BH62:BH65)+1</f>
-        <v>1</v>
+        <v>51.5</v>
       </c>
       <c r="BK66" s="141">
         <v>85</v>
@@ -54015,12 +54211,16 @@
         <f>AS14</f>
         <v>Switzerland</v>
       </c>
-      <c r="BM66" s="61"/>
-      <c r="BN66" s="63"/>
+      <c r="BM66" s="61">
+        <v>1</v>
+      </c>
+      <c r="BN66" s="63">
+        <v>2</v>
+      </c>
       <c r="BO66" s="25"/>
-      <c r="BP66" s="112" t="str">
+      <c r="BP66" s="112">
         <f>IF(OR(BM66="",BM67="",AND(BN66="",BN67&lt;&gt;""),AND(BN67="",BN66&lt;&gt;""),AND(BO66="",BO67&lt;&gt;""),AND(BO67="",BO66&lt;&gt;"")),"",BM66*1000+BN66*10+BO66)</f>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="BQ66" s="112"/>
       <c r="BR66" s="21"/>
@@ -54050,8 +54250,12 @@
         <f>AE59</f>
         <v>Norway</v>
       </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="20"/>
+      <c r="F67" s="19">
+        <v>2</v>
+      </c>
+      <c r="G67" s="20">
+        <v>2</v>
+      </c>
       <c r="H67" s="80" t="str">
         <f>AE56</f>
         <v>France</v>
@@ -54070,11 +54274,11 @@
       </c>
       <c r="S67" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Norway_draw</v>
       </c>
       <c r="T67" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>France_draw</v>
       </c>
       <c r="U67" s="123">
         <f t="shared" si="8"/>
@@ -54104,21 +54308,25 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB67" s="123" t="str">
+      <c r="AB67" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK67" s="142"/>
       <c r="BL67" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!E3,AK80:AS91,9,FALSE),"3rd Group E/F/G/I/J")</f>
-        <v>3rd Group E/F/G/I/J</v>
-      </c>
-      <c r="BM67" s="62"/>
-      <c r="BN67" s="64"/>
+        <v>Austria</v>
+      </c>
+      <c r="BM67" s="62">
+        <v>1</v>
+      </c>
+      <c r="BN67" s="64">
+        <v>1</v>
+      </c>
       <c r="BO67" s="27"/>
-      <c r="BP67" s="113" t="str">
+      <c r="BP67" s="113">
         <f>IF(BP66="","",BM67*1000+BN67*10+BO67)</f>
-        <v/>
+        <v>1010</v>
       </c>
       <c r="BQ67" s="112"/>
       <c r="BR67" s="21" t="str" cm="1">
@@ -54154,8 +54362,12 @@
         <f>AE57</f>
         <v>Senegal</v>
       </c>
-      <c r="F68" s="19"/>
-      <c r="G68" s="20"/>
+      <c r="F68" s="19">
+        <v>2</v>
+      </c>
+      <c r="G68" s="20">
+        <v>0</v>
+      </c>
       <c r="H68" s="80" t="str">
         <f>AE58</f>
         <v>Iraq</v>
@@ -54195,11 +54407,11 @@
       </c>
       <c r="S68" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Senegal_win</v>
       </c>
       <c r="T68" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Iraq_lose</v>
       </c>
       <c r="U68" s="123">
         <f t="shared" si="8"/>
@@ -54229,9 +54441,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB68" s="123" t="str">
+      <c r="AB68" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD68" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR68))</f>
@@ -54247,7 +54459,7 @@
       </c>
       <c r="AG68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH68" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE68 &amp; "_lose")</f>
@@ -54255,11 +54467,11 @@
       </c>
       <c r="AI68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE68,$G$7:$G$78)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ68" s="123">
         <f>SUMIF($E$7:$E$78,$AE68,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE68,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL68" s="123">
         <f>AI68-AJ68</f>
@@ -54271,15 +54483,15 @@
       </c>
       <c r="AN68" s="123">
         <f>AF68*3+AG68</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO68" s="123">
         <f>AN68/AN72*10+BA68</f>
-        <v>8.5714285714285712</v>
+        <v>9.735294117647058</v>
       </c>
       <c r="AP68" s="123">
         <f>AO68*10000000+BI68*100+AM68/AM72*10+AI68/AI72*1++IF(AQ68=0,ROW(),AQ68)/2000000</f>
-        <v>85714295.87588191</v>
+        <v>97353049.88136743</v>
       </c>
       <c r="AQ68" s="126">
         <f>VLOOKUP(AE68,db_fifarank,2,FALSE)</f>
@@ -54287,11 +54499,11 @@
       </c>
       <c r="AR68" s="125">
         <f>AP68/AP72</f>
-        <v>0.99999998833333481</v>
+        <v>0.99999998972810822</v>
       </c>
       <c r="AS68" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J69,"1K")</f>
-        <v>1K</v>
+        <v>Portugal</v>
       </c>
       <c r="AT68" s="126" cm="1">
         <f t="array" ref="AT68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($U$7:$U$78))</f>
@@ -54299,15 +54511,15 @@
       </c>
       <c r="AU68" s="126" cm="1">
         <f t="array" ref="AU68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV68" s="126" cm="1">
         <f t="array" ref="AV68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW68" s="126" cm="1">
         <f t="array" ref="AW68">SUMPRODUCT(($E$7:$E$78=AE68)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX68" s="126">
         <f>AV68-AW68</f>
@@ -54319,11 +54531,11 @@
       </c>
       <c r="AZ68" s="126">
         <f>AT68/AT72*1000+AU68/AU72*100+AY68/AY72*10+AV68/AV72</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA68" s="126">
         <f>AZ68/AZ72</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BB68" s="126" cm="1">
         <f t="array" ref="BB68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_win")*($X$7:$X$78))</f>
@@ -54331,15 +54543,15 @@
       </c>
       <c r="BC68" s="126" cm="1">
         <f t="array" ref="BC68">SUMPRODUCT(($S$7:$S$78=AE68&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE68&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD68" s="126" cm="1">
         <f t="array" ref="BD68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE68" s="126" cm="1">
         <f t="array" ref="BE68">SUMPRODUCT(($E$7:$E$78=AE68)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE68)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF68" s="126">
         <f>BD68-BE68</f>
@@ -54351,11 +54563,11 @@
       </c>
       <c r="BH68" s="126">
         <f>BB68/BB72*1000+BC68/BC72*100+BG68/BG72*10+BD68/BD72</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI68" s="126">
         <f>BH68/BH72</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BK68" s="21"/>
       <c r="BL68" s="21"/>
@@ -54369,14 +54581,16 @@
       </c>
       <c r="BS68" s="24" t="str">
         <f>IF(BP66&gt;BP67,BL66,IF(BP66&lt;BP67,BL67,""))</f>
-        <v/>
-      </c>
-      <c r="BT68" s="61"/>
+        <v>Switzerland</v>
+      </c>
+      <c r="BT68" s="61">
+        <v>2</v>
+      </c>
       <c r="BU68" s="63"/>
       <c r="BV68" s="25"/>
-      <c r="BW68" s="116" t="str">
+      <c r="BW68" s="116">
         <f>IF(OR(BT68="",BT69="",AND(BU68="",BU69&lt;&gt;""),AND(BU69="",BU68&lt;&gt;""),AND(BV68="",BV69&lt;&gt;""),AND(BV69="",BV68&lt;&gt;"")),"",BT68*1000+BU68*10+BV68)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="CE68" s="143" t="str">
         <f>INDEX(T,144,lang)</f>
@@ -54389,7 +54603,7 @@
       <c r="CJ68" s="143"/>
       <c r="CK68" s="131" t="str">
         <f>IF(CR37&gt;CR38,CN37,IF(CR37&lt;CR38,CN38,""))</f>
-        <v/>
+        <v>Senegal</v>
       </c>
       <c r="CL68" s="131"/>
       <c r="CM68" s="131"/>
@@ -54418,8 +54632,12 @@
         <f>AE45</f>
         <v>Egypt</v>
       </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="20"/>
+      <c r="F69" s="19">
+        <v>1</v>
+      </c>
+      <c r="G69" s="20">
+        <v>0</v>
+      </c>
       <c r="H69" s="80" t="str">
         <f>AE46</f>
         <v>Iran</v>
@@ -54431,7 +54649,7 @@
       </c>
       <c r="K69" s="31">
         <f>L69+M69+N69</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="31">
         <f>VLOOKUP(1,AD68:AN71,3,FALSE)</f>
@@ -54439,7 +54657,7 @@
       </c>
       <c r="M69" s="31">
         <f>VLOOKUP(1,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" s="31">
         <f>VLOOKUP(1,AD68:AN71,5,FALSE)</f>
@@ -54447,11 +54665,11 @@
       </c>
       <c r="O69" s="31" t="str">
         <f>VLOOKUP(1,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD68:AN71,7,FALSE)</f>
-        <v>7 - 0</v>
+        <v>8 - 1</v>
       </c>
       <c r="P69" s="32">
         <f>L69*3+M69</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R69" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -54459,11 +54677,11 @@
       </c>
       <c r="S69" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Egypt_win</v>
       </c>
       <c r="T69" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Iran_lose</v>
       </c>
       <c r="U69" s="123">
         <f t="shared" si="8"/>
@@ -54493,9 +54711,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB69" s="123" t="str">
+      <c r="AB69" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD69" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR69))</f>
@@ -54511,7 +54729,7 @@
       </c>
       <c r="AG69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH69" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE69 &amp; "_lose")</f>
@@ -54519,11 +54737,11 @@
       </c>
       <c r="AI69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE69,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ69" s="123">
         <f>SUMIF($E$7:$E$78,$AE69,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE69,$F$7:$F$78)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL69" s="123">
         <f>AI69-AJ69</f>
@@ -54535,15 +54753,15 @@
       </c>
       <c r="AN69" s="123">
         <f>AF69*3+AG69</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO69" s="123">
         <f>AN69/AN72*10+BA69</f>
-        <v>0</v>
+        <v>2.2401960784313726</v>
       </c>
       <c r="AP69" s="123">
         <f>AO69*10000000+BI69*100+AM69/AM72*10+AI69/AI72*1++IF(AQ69=0,ROW(),AQ69)/2000000</f>
-        <v>0.71502488928571417</v>
+        <v>22402060.741168682</v>
       </c>
       <c r="AQ69" s="126">
         <f>VLOOKUP(AE69,db_fifarank,2,FALSE)</f>
@@ -54551,11 +54769,11 @@
       </c>
       <c r="AR69" s="125">
         <f>AP69/AP72</f>
-        <v>8.3419559553886544E-9</v>
+        <v>0.23011154286748964</v>
       </c>
       <c r="AS69" s="125" t="str">
         <f>IF(SUM(AF68:AH71)=12,J70,"2K")</f>
-        <v>2K</v>
+        <v>Colombia</v>
       </c>
       <c r="AT69" s="126" cm="1">
         <f t="array" ref="AT69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($U$7:$U$78))</f>
@@ -54563,15 +54781,15 @@
       </c>
       <c r="AU69" s="126" cm="1">
         <f t="array" ref="AU69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69" s="126" cm="1">
         <f t="array" ref="AV69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW69" s="126" cm="1">
         <f t="array" ref="AW69">SUMPRODUCT(($E$7:$E$78=AE69)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX69" s="126">
         <f>AV69-AW69</f>
@@ -54583,11 +54801,11 @@
       </c>
       <c r="AZ69" s="126">
         <f>AT69/AT72*1000+AU69/AU72*100+AY69/AY72*10+AV69/AV72</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA69" s="126">
         <f>AZ69/AZ72</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB69" s="126" cm="1">
         <f t="array" ref="BB69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_win")*($X$7:$X$78))</f>
@@ -54595,15 +54813,15 @@
       </c>
       <c r="BC69" s="126" cm="1">
         <f t="array" ref="BC69">SUMPRODUCT(($S$7:$S$78=AE69&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE69&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD69" s="126" cm="1">
         <f t="array" ref="BD69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE69" s="126" cm="1">
         <f t="array" ref="BE69">SUMPRODUCT(($E$7:$E$78=AE69)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE69)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF69" s="126">
         <f>BD69-BE69</f>
@@ -54615,11 +54833,11 @@
       </c>
       <c r="BH69" s="126">
         <f>BB69/BB72*1000+BC69/BC72*100+BG69/BG72*10+BD69/BD72</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI69" s="126">
         <f>BH69/BH72</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK69" s="21" t="str" cm="1">
         <f t="array" ref="BK69">INDEX(T,24+MONTH(BP69),lang) &amp; " " &amp; DAY(BP69) &amp; ", " &amp; YEAR(BP69) &amp; "   " &amp; (IF(HOUR(BP69)&lt;10,0,"")&amp;HOUR(BP69)) &amp; ":" &amp;  (IF(MINUTE(BP69)&lt;10,0,"")&amp;MINUTE(BP69))</f>
@@ -54637,14 +54855,16 @@
       <c r="BR69" s="142"/>
       <c r="BS69" s="26" t="str">
         <f>IF(BP70&gt;BP71,BL70,IF(BP70&lt;BP71,BL71,""))</f>
-        <v/>
-      </c>
-      <c r="BT69" s="62"/>
+        <v>Portugal</v>
+      </c>
+      <c r="BT69" s="62">
+        <v>3</v>
+      </c>
       <c r="BU69" s="64"/>
       <c r="BV69" s="27"/>
-      <c r="BW69" s="112" t="str">
+      <c r="BW69" s="112">
         <f>IF(BW68="","",BT69*1000+BU69*10+BV69)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="CE69" s="143"/>
       <c r="CF69" s="143"/>
@@ -54680,8 +54900,12 @@
         <f>AE47</f>
         <v>New Zealand</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="F70" s="19">
+        <v>1</v>
+      </c>
+      <c r="G70" s="20">
+        <v>1</v>
+      </c>
       <c r="H70" s="80" t="str">
         <f>AE44</f>
         <v>Belgium</v>
@@ -54693,7 +54917,7 @@
       </c>
       <c r="K70" s="23">
         <f>L70+M70+N70</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="23">
         <f>VLOOKUP(2,AD68:AN71,3,FALSE)</f>
@@ -54701,7 +54925,7 @@
       </c>
       <c r="M70" s="23">
         <f>VLOOKUP(2,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" s="23">
         <f>VLOOKUP(2,AD68:AN71,5,FALSE)</f>
@@ -54709,11 +54933,11 @@
       </c>
       <c r="O70" s="23" t="str">
         <f>VLOOKUP(2,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD68:AN71,7,FALSE)</f>
-        <v>4 - 0</v>
+        <v>5 - 1</v>
       </c>
       <c r="P70" s="34">
         <f>L70*3+M70</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R70" s="123">
         <f>DATE(2026,6,26)+TIME(16,0,0)+gmt_delta</f>
@@ -54721,11 +54945,11 @@
       </c>
       <c r="S70" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>New Zealand_draw</v>
       </c>
       <c r="T70" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Belgium_draw</v>
       </c>
       <c r="U70" s="123">
         <f t="shared" si="8"/>
@@ -54755,9 +54979,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB70" s="123" t="str">
+      <c r="AB70" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD70" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR70))</f>
@@ -54773,7 +54997,7 @@
       </c>
       <c r="AG70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH70" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE70 &amp; "_lose")</f>
@@ -54781,11 +55005,11 @@
       </c>
       <c r="AI70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE70,$G$7:$G$78)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ70" s="123">
         <f>SUMIF($E$7:$E$78,$AE70,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE70,$F$7:$F$78)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL70" s="123">
         <f>AI70-AJ70</f>
@@ -54797,15 +55021,15 @@
       </c>
       <c r="AN70" s="123">
         <f>AF70*3+AG70</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO70" s="123">
         <f>AN70/AN72*10+BA70</f>
-        <v>0</v>
+        <v>2.2401960784313726</v>
       </c>
       <c r="AP70" s="123">
         <f>AO70*10000000+BI70*100+AM70/AM72*10+AI70/AI72*1++IF(AQ70=0,ROW(),AQ70)/2000000</f>
-        <v>7.3266999999999994E-4</v>
+        <v>22402060.026876464</v>
       </c>
       <c r="AQ70" s="126">
         <f>VLOOKUP(AE70,db_fifarank,2,FALSE)</f>
@@ -54813,7 +55037,7 @@
       </c>
       <c r="AR70" s="125">
         <f>AP70/AP72</f>
-        <v>8.5478155535819018E-12</v>
+        <v>0.23011153553035732</v>
       </c>
       <c r="AT70" s="126" cm="1">
         <f t="array" ref="AT70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($U$7:$U$78))</f>
@@ -54821,15 +55045,15 @@
       </c>
       <c r="AU70" s="126" cm="1">
         <f t="array" ref="AU70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV70" s="126" cm="1">
         <f t="array" ref="AV70">SUMPRODUCT(($E$7:$E$78=AE70)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE70)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW70" s="126" cm="1">
         <f t="array" ref="AW70">SUMPRODUCT(($E$7:$E$78=AE70)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE70)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX70" s="126">
         <f>AV70-AW70</f>
@@ -54841,11 +55065,11 @@
       </c>
       <c r="AZ70" s="126">
         <f>AT70/AT72*1000+AU70/AU72*100+AY70/AY72*10+AV70/AV72</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BA70" s="126">
         <f>AZ70/AZ72</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BB70" s="126" cm="1">
         <f t="array" ref="BB70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_win")*($X$7:$X$78))</f>
@@ -54853,15 +55077,15 @@
       </c>
       <c r="BC70" s="126" cm="1">
         <f t="array" ref="BC70">SUMPRODUCT(($S$7:$S$78=AE70&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE70&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD70" s="126" cm="1">
         <f t="array" ref="BD70">SUMPRODUCT(($E$7:$E$78=AE70)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE70)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE70" s="126" cm="1">
         <f t="array" ref="BE70">SUMPRODUCT(($E$7:$E$78=AE70)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE70)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF70" s="126">
         <f>BD70-BE70</f>
@@ -54873,25 +55097,27 @@
       </c>
       <c r="BH70" s="126">
         <f>BB70/BB72*1000+BC70/BC72*100+BG70/BG72*10+BD70/BD72</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="BI70" s="126">
         <f>BH70/BH72</f>
-        <v>0</v>
+        <v>0.99019607843137258</v>
       </c>
       <c r="BK70" s="141">
         <v>87</v>
       </c>
       <c r="BL70" s="24" t="str">
         <f>AS68</f>
-        <v>1K</v>
-      </c>
-      <c r="BM70" s="61"/>
+        <v>Portugal</v>
+      </c>
+      <c r="BM70" s="61">
+        <v>4</v>
+      </c>
       <c r="BN70" s="63"/>
       <c r="BO70" s="25"/>
-      <c r="BP70" s="116" t="str">
+      <c r="BP70" s="116">
         <f>IF(OR(BM70="",BM71="",AND(BN70="",BN71&lt;&gt;""),AND(BN71="",BN70&lt;&gt;""),AND(BO70="",BO71&lt;&gt;""),AND(BO71="",BO70&lt;&gt;"")),"",BM70*1000+BN70*10+BO70)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="BQ70" s="112"/>
       <c r="BW70" s="112"/>
@@ -54916,8 +55142,12 @@
         <f>AE51</f>
         <v>Cape Verde</v>
       </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="F71" s="19">
+        <v>2</v>
+      </c>
+      <c r="G71" s="20">
+        <v>0</v>
+      </c>
       <c r="H71" s="80" t="str">
         <f>AE52</f>
         <v>Saudi Arabia</v>
@@ -54929,7 +55159,7 @@
       </c>
       <c r="K71" s="23">
         <f>L71+M71+N71</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" s="23">
         <f>VLOOKUP(3,AD68:AN71,3,FALSE)</f>
@@ -54937,7 +55167,7 @@
       </c>
       <c r="M71" s="23">
         <f>VLOOKUP(3,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" s="23">
         <f>VLOOKUP(3,AD68:AN71,5,FALSE)</f>
@@ -54945,11 +55175,11 @@
       </c>
       <c r="O71" s="23" t="str">
         <f>VLOOKUP(3,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD68:AN71,7,FALSE)</f>
-        <v>0 - 5</v>
+        <v>2 - 7</v>
       </c>
       <c r="P71" s="34">
         <f>L71*3+M71</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="123">
         <f>DATE(2026,6,26)+TIME(13,0,0)+gmt_delta</f>
@@ -54957,11 +55187,11 @@
       </c>
       <c r="S71" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Cape Verde_win</v>
       </c>
       <c r="T71" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Saudi Arabia_lose</v>
       </c>
       <c r="U71" s="123">
         <f t="shared" si="8"/>
@@ -54991,9 +55221,9 @@
         <f t="shared" ref="AA71:AA78" si="29">IF(OR(E71=my_team,H71=my_team),1,IF(INT(MATCH(E71,$AE$8:$AE$78,0)/6)=$AA$6,1,0))</f>
         <v>0</v>
       </c>
-      <c r="AB71" s="123" t="str">
+      <c r="AB71" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD71" s="123">
         <f>COUNTIF(AR68:AR71,CONCATENATE("&gt;=",AR71))</f>
@@ -55009,7 +55239,7 @@
       </c>
       <c r="AG71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_draw")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE71 &amp; "_lose")</f>
@@ -55017,11 +55247,11 @@
       </c>
       <c r="AI71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE71,$G$7:$G$78)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ71" s="123">
         <f>SUMIF($E$7:$E$78,$AE71,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE71,$F$7:$F$78)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL71" s="123">
         <f>AI71-AJ71</f>
@@ -55033,15 +55263,15 @@
       </c>
       <c r="AN71" s="123">
         <f>AF71*3+AG71</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO71" s="123">
         <f>AN71/AN72*10+BA71</f>
-        <v>8.5714285714285712</v>
+        <v>9.735294117647058</v>
       </c>
       <c r="AP71" s="123">
         <f>AO71*10000000+BI71*100+AM71/AM72*10+AI71/AI72*1++IF(AQ71=0,ROW(),AQ71)/2000000</f>
-        <v>85714293.357989416</v>
+        <v>97353047.405141592</v>
       </c>
       <c r="AQ71" s="126">
         <f>VLOOKUP(AE71,db_fifarank,2,FALSE)</f>
@@ -55049,7 +55279,7 @@
       </c>
       <c r="AR71" s="125">
         <f>AP71/AP72</f>
-        <v>0.99999995895792626</v>
+        <v>0.99999996429258453</v>
       </c>
       <c r="AT71" s="126" cm="1">
         <f t="array" ref="AT71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($U$7:$U$78))</f>
@@ -55057,15 +55287,15 @@
       </c>
       <c r="AU71" s="126" cm="1">
         <f t="array" ref="AU71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_draw")*($U$7:$U$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV71" s="126" cm="1">
         <f t="array" ref="AV71">SUMPRODUCT(($E$7:$E$78=AE71)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE71)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW71" s="126" cm="1">
         <f t="array" ref="AW71">SUMPRODUCT(($E$7:$E$78=AE71)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE71)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX71" s="126">
         <f>AV71-AW71</f>
@@ -55077,11 +55307,11 @@
       </c>
       <c r="AZ71" s="126">
         <f>AT71/AT72*1000+AU71/AU72*100+AY71/AY72*10+AV71/AV72</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BA71" s="126">
         <f>AZ71/AZ72</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BB71" s="126" cm="1">
         <f t="array" ref="BB71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_win")*($X$7:$X$78))</f>
@@ -55089,15 +55319,15 @@
       </c>
       <c r="BC71" s="126" cm="1">
         <f t="array" ref="BC71">SUMPRODUCT(($S$7:$S$78=AE71&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE71&amp;"_draw")*($X$7:$X$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD71" s="126" cm="1">
         <f t="array" ref="BD71">SUMPRODUCT(($E$7:$E$78=AE71)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE71)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE71" s="126" cm="1">
         <f t="array" ref="BE71">SUMPRODUCT(($E$7:$E$78=AE71)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE71)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF71" s="126">
         <f>BD71-BE71</f>
@@ -55109,23 +55339,25 @@
       </c>
       <c r="BH71" s="126">
         <f>BB71/BB72*1000+BC71/BC72*100+BG71/BG72*10+BD71/BD72</f>
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="BI71" s="126">
         <f>BH71/BH72</f>
-        <v>0</v>
+        <v>0.98529411764705888</v>
       </c>
       <c r="BK71" s="142"/>
       <c r="BL71" s="26" t="str">
         <f>IF(group_round_completed,VLOOKUP('3rd places'!J3,AK80:AS91,9,FALSE),"3rd Group D/E/I/J/L")</f>
-        <v>3rd Group D/E/I/J/L</v>
-      </c>
-      <c r="BM71" s="62"/>
+        <v>Ghana</v>
+      </c>
+      <c r="BM71" s="62">
+        <v>2</v>
+      </c>
       <c r="BN71" s="64"/>
       <c r="BO71" s="27"/>
-      <c r="BP71" s="112" t="str">
+      <c r="BP71" s="112">
         <f>IF(BP70="","",BM71*1000+BN71*10+BO71)</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="BQ71" s="112"/>
     </row>
@@ -55149,8 +55381,12 @@
         <f>AE53</f>
         <v>Uruguay</v>
       </c>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="F72" s="19">
+        <v>1</v>
+      </c>
+      <c r="G72" s="20">
+        <v>2</v>
+      </c>
       <c r="H72" s="80" t="str">
         <f>AE50</f>
         <v>Spain</v>
@@ -55162,7 +55398,7 @@
       </c>
       <c r="K72" s="36">
         <f>L72+M72+N72</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" s="36">
         <f>VLOOKUP(4,AD68:AN71,3,FALSE)</f>
@@ -55170,7 +55406,7 @@
       </c>
       <c r="M72" s="36">
         <f>VLOOKUP(4,AD68:AN71,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" s="36">
         <f>VLOOKUP(4,AD68:AN71,5,FALSE)</f>
@@ -55178,11 +55414,11 @@
       </c>
       <c r="O72" s="36" t="str">
         <f>VLOOKUP(4,AD68:AN71,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD68:AN71,7,FALSE)</f>
-        <v>0 - 6</v>
+        <v>2 - 8</v>
       </c>
       <c r="P72" s="37">
         <f>L72*3+M72</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="123">
         <f>DATE(2026,6,26)+TIME(13,0,0)+gmt_delta</f>
@@ -55190,11 +55426,11 @@
       </c>
       <c r="S72" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Uruguay_lose</v>
       </c>
       <c r="T72" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Spain_win</v>
       </c>
       <c r="U72" s="123">
         <f t="shared" ref="U72:U78" si="31">IF(S72="",0,IF(VLOOKUP(E72,$AE$8:$AN$77,10,FALSE)=VLOOKUP(H72,$AE$8:$AN$77,10,FALSE),1,0))</f>
@@ -55224,9 +55460,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB72" s="123" t="str">
+      <c r="AB72" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AF72" s="123">
         <f t="shared" ref="AF72:AH72" si="35">MAX(AF68:AF71)-MIN(AF68:AF71)+1</f>
@@ -55242,7 +55478,7 @@
       </c>
       <c r="AI72" s="123">
         <f>MAX(AI68:AI71)+1</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL72" s="123">
         <f>MIN(AL68:AL71)</f>
@@ -55254,15 +55490,15 @@
       </c>
       <c r="AN72" s="123">
         <f>MAX(AN68:AN71)+1</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO72" s="123">
         <f>MAX(AO68:AO71)+1</f>
-        <v>9.5714285714285712</v>
+        <v>10.735294117647058</v>
       </c>
       <c r="AP72" s="123">
         <f>MAX(AP68:AP71)+1</f>
-        <v>85714296.87588191</v>
+        <v>97353050.88136743</v>
       </c>
       <c r="AT72" s="126">
         <f>MAX(AT68:AT71)-MIN(AT68:AT71)+1</f>
@@ -55274,11 +55510,11 @@
       </c>
       <c r="AV72" s="126">
         <f>MAX(AV68:AV71)-MIN(AV68:AV71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW72" s="126">
         <f>MAX(AW68:AW71)-MIN(AW68:AW71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY72" s="126">
         <f>MAX(AY68:AY71)-MIN(AY68:AY71)+1</f>
@@ -55286,7 +55522,7 @@
       </c>
       <c r="AZ72" s="126">
         <f>MAX(AZ68:AZ71)+1</f>
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="BB72" s="126">
         <f>MAX(BB68:BB71)-MIN(BB68:BB71)+1</f>
@@ -55298,11 +55534,11 @@
       </c>
       <c r="BD72" s="126">
         <f>MAX(BD68:BD71)-MIN(BD68:BD71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE72" s="126">
         <f>MAX(BE68:BE71)-MIN(BE68:BE71)+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG72" s="126">
         <f>MAX(BG68:BG71)-MIN(BG68:BG71)+1</f>
@@ -55310,7 +55546,7 @@
       </c>
       <c r="BH72" s="126">
         <f>MAX(BH68:BH71)+1</f>
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.25">
@@ -55333,8 +55569,12 @@
         <f>AE77</f>
         <v>Panama</v>
       </c>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="F73" s="19">
+        <v>0</v>
+      </c>
+      <c r="G73" s="20">
+        <v>2</v>
+      </c>
       <c r="H73" s="80" t="str">
         <f>AE74</f>
         <v>England</v>
@@ -55353,11 +55593,11 @@
       </c>
       <c r="S73" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Panama_lose</v>
       </c>
       <c r="T73" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>England_win</v>
       </c>
       <c r="U73" s="123">
         <f t="shared" si="31"/>
@@ -55387,9 +55627,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB73" s="123" t="str">
+      <c r="AB73" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
     </row>
     <row r="74" spans="1:95" x14ac:dyDescent="0.25">
@@ -55412,8 +55652,12 @@
         <f>AE75</f>
         <v>Croatia</v>
       </c>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="F74" s="19">
+        <v>2</v>
+      </c>
+      <c r="G74" s="20">
+        <v>1</v>
+      </c>
       <c r="H74" s="80" t="str">
         <f>AE76</f>
         <v>Ghana</v>
@@ -55453,11 +55697,11 @@
       </c>
       <c r="S74" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Croatia_win</v>
       </c>
       <c r="T74" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Ghana_lose</v>
       </c>
       <c r="U74" s="123">
         <f t="shared" si="31"/>
@@ -55487,9 +55731,9 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB74" s="123" t="str">
+      <c r="AB74" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD74" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR74))</f>
@@ -55501,7 +55745,7 @@
       </c>
       <c r="AF74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG74" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE74 &amp; "_draw")</f>
@@ -55513,7 +55757,7 @@
       </c>
       <c r="AI74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE74,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ74" s="123">
         <f>SUMIF($E$7:$E$78,$AE74,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE74,$F$7:$F$78)</f>
@@ -55521,23 +55765,23 @@
       </c>
       <c r="AL74" s="123">
         <f>AI74-AJ74</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM74" s="123">
         <f>AL74-AL78</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN74" s="123">
         <f>AF74*3+AG74</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO74" s="123">
         <f>AN74/AN78*10+BA74</f>
-        <v>8.9805825242718456</v>
+        <v>8.75</v>
       </c>
       <c r="AP74" s="123">
         <f>AO74*10000000+BI74*100+AM74/AM78*10+AI74/AI78*1++IF(AQ74=0,ROW(),AQ74)/2000000</f>
-        <v>89805932.051883861</v>
+        <v>87500009.723135203</v>
       </c>
       <c r="AQ74" s="126">
         <f>VLOOKUP(AE74,db_fifarank,2,FALSE)</f>
@@ -55545,11 +55789,11 @@
       </c>
       <c r="AR74" s="125">
         <f>AP74/AP78</f>
-        <v>0.99999998886487829</v>
+        <v>0.99999998857143002</v>
       </c>
       <c r="AS74" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J75,"1L")</f>
-        <v>1L</v>
+        <v>England</v>
       </c>
       <c r="AT74" s="126" cm="1">
         <f t="array" ref="AT74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_win")*($U$7:$U$78))</f>
@@ -55557,15 +55801,15 @@
       </c>
       <c r="AU74" s="126" cm="1">
         <f t="array" ref="AU74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV74" s="126" cm="1">
         <f t="array" ref="AV74">SUMPRODUCT(($E$7:$E$78=AE74)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW74" s="126" cm="1">
         <f t="array" ref="AW74">SUMPRODUCT(($E$7:$E$78=AE74)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX74" s="126">
         <f>AV74-AW74</f>
@@ -55577,11 +55821,11 @@
       </c>
       <c r="AZ74" s="126">
         <f>AT74/AT78*1000+AU74/AU78*100+AY74/AY78*10+AV74/AV78</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA74" s="126">
         <f>AZ74/AZ78</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB74" s="126" cm="1">
         <f t="array" ref="BB74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_win")*($X$7:$X$78))</f>
@@ -55589,15 +55833,15 @@
       </c>
       <c r="BC74" s="126" cm="1">
         <f t="array" ref="BC74">SUMPRODUCT(($S$7:$S$78=AE74&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE74&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD74" s="126" cm="1">
         <f t="array" ref="BD74">SUMPRODUCT(($E$7:$E$78=AE74)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE74" s="126" cm="1">
         <f t="array" ref="BE74">SUMPRODUCT(($E$7:$E$78=AE74)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE74)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF74" s="126">
         <f>BD74-BE74</f>
@@ -55609,11 +55853,11 @@
       </c>
       <c r="BH74" s="126">
         <f>BB74/BB78*1000+BC74/BC78*100+BG74/BG78*10+BD74/BD78</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI74" s="126">
         <f>BH74/BH78</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:95" x14ac:dyDescent="0.25">
@@ -55636,8 +55880,12 @@
         <f>AE63</f>
         <v>Algeria</v>
       </c>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="F75" s="19">
+        <v>1</v>
+      </c>
+      <c r="G75" s="20">
+        <v>1</v>
+      </c>
       <c r="H75" s="80" t="str">
         <f>AE64</f>
         <v>Austria</v>
@@ -55649,11 +55897,11 @@
       </c>
       <c r="K75" s="31">
         <f>L75+M75+N75</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="31">
         <f>VLOOKUP(1,AD74:AN77,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="31">
         <f>VLOOKUP(1,AD74:AN77,4,FALSE)</f>
@@ -55665,11 +55913,11 @@
       </c>
       <c r="O75" s="31" t="str">
         <f>VLOOKUP(1,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(1,AD74:AN77,7,FALSE)</f>
-        <v>3 - 2</v>
+        <v>5 - 2</v>
       </c>
       <c r="P75" s="32">
         <f>L75*3+M75</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R75" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -55677,47 +55925,47 @@
       </c>
       <c r="S75" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Algeria_draw</v>
       </c>
       <c r="T75" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Austria_draw</v>
       </c>
       <c r="U75" s="123">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X75" s="123">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="123">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z75" s="123">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA75" s="123">
         <f t="shared" si="29"/>
         <v>1</v>
       </c>
-      <c r="AB75" s="123" t="str">
+      <c r="AB75" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD75" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR75))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE75" s="124" t="str">
         <f>VLOOKUP("Croatia",T,lang,FALSE)</f>
@@ -55725,7 +55973,7 @@
       </c>
       <c r="AF75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG75" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE75 &amp; "_draw")</f>
@@ -55737,31 +55985,31 @@
       </c>
       <c r="AI75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE75,$G$7:$G$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ75" s="123">
         <f>SUMIF($E$7:$E$78,$AE75,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE75,$F$7:$F$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL75" s="123">
         <f>AI75-AJ75</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM75" s="123">
         <f>AL75-AL78</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN75" s="123">
         <f>AF75*3+AG75</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO75" s="123">
         <f>AN75/AN78*10+BA75</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AP75" s="123">
         <f>AO75*10000000+BI75*100+AM75/AM78*10+AI75/AI78*1++IF(AQ75=0,ROW(),AQ75)/2000000</f>
-        <v>60000008.750858538</v>
+        <v>75000008.611969635</v>
       </c>
       <c r="AQ75" s="126">
         <f>VLOOKUP(AE75,db_fifarank,2,FALSE)</f>
@@ -55769,11 +56017,11 @@
       </c>
       <c r="AR75" s="125">
         <f>AP75/AP78</f>
-        <v>0.6681074035074559</v>
+        <v>0.85714285052241102</v>
       </c>
       <c r="AS75" s="125" t="str">
         <f>IF(SUM(AF74:AH77)=12,J76,"2L")</f>
-        <v>2L</v>
+        <v>Croatia</v>
       </c>
       <c r="AT75" s="126" cm="1">
         <f t="array" ref="AT75">SUMPRODUCT(($S$7:$S$78=AE75&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE75&amp;"_win")*($U$7:$U$78))</f>
@@ -55860,8 +56108,12 @@
         <f>AE65</f>
         <v>Jordan</v>
       </c>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="F76" s="19">
+        <v>0</v>
+      </c>
+      <c r="G76" s="20">
+        <v>2</v>
+      </c>
       <c r="H76" s="80" t="str">
         <f>AE62</f>
         <v>Argentina</v>
@@ -55869,31 +56121,31 @@
       <c r="I76" s="69"/>
       <c r="J76" s="33" t="str">
         <f>VLOOKUP(2,AD74:AN77,2,FALSE)</f>
-        <v>Ghana</v>
+        <v>Croatia</v>
       </c>
       <c r="K76" s="23">
         <f>L76+M76+N76</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="23">
         <f>VLOOKUP(2,AD74:AN77,3,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="23">
         <f>VLOOKUP(2,AD74:AN77,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" s="23">
         <f>VLOOKUP(2,AD74:AN77,5,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" s="23" t="str">
         <f>VLOOKUP(2,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(2,AD74:AN77,7,FALSE)</f>
-        <v>2 - 1</v>
+        <v>5 - 3</v>
       </c>
       <c r="P76" s="34">
         <f>L76*3+M76</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R76" s="123">
         <f>DATE(2026,6,27)+TIME(15,0,0)+gmt_delta</f>
@@ -55901,11 +56153,11 @@
       </c>
       <c r="S76" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Jordan_lose</v>
       </c>
       <c r="T76" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Argentina_win</v>
       </c>
       <c r="U76" s="123">
         <f t="shared" si="31"/>
@@ -55935,13 +56187,13 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB76" s="123" t="str">
+      <c r="AB76" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="AD76" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR76))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE76" s="124" t="str">
         <f>VLOOKUP("Ghana",T,lang,FALSE)</f>
@@ -55957,23 +56209,23 @@
       </c>
       <c r="AH76" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE76 &amp; "_lose")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE76,$G$7:$G$78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ76" s="123">
         <f>SUMIF($E$7:$E$78,$AE76,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE76,$F$7:$F$78)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL76" s="123">
         <f>AI76-AJ76</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM76" s="123">
         <f>AL76-AL78</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN76" s="123">
         <f>AF76*3+AG76</f>
@@ -55981,11 +56233,11 @@
       </c>
       <c r="AO76" s="123">
         <f>AN76/AN78*10+BA76</f>
-        <v>8.9805825242718456</v>
+        <v>5</v>
       </c>
       <c r="AP76" s="123">
         <f>AO76*10000000+BI76*100+AM76/AM78*10+AI76/AI78*1++IF(AQ76=0,ROW(),AQ76)/2000000</f>
-        <v>89805931.801644042</v>
+        <v>50000006.056228705</v>
       </c>
       <c r="AQ76" s="126">
         <f>VLOOKUP(AE76,db_fifarank,2,FALSE)</f>
@@ -55993,7 +56245,7 @@
       </c>
       <c r="AR76" s="125">
         <f>AP76/AP78</f>
-        <v>0.99999998607842733</v>
+        <v>0.57142857061397578</v>
       </c>
       <c r="AT76" s="126" cm="1">
         <f t="array" ref="AT76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($U$7:$U$78))</f>
@@ -56001,15 +56253,15 @@
       </c>
       <c r="AU76" s="126" cm="1">
         <f t="array" ref="AU76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($U$7:$U$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV76" s="126" cm="1">
         <f t="array" ref="AV76">SUMPRODUCT(($E$7:$E$78=AE76)*($U$7:$U$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($U$7:$U$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" s="126" cm="1">
         <f t="array" ref="AW76">SUMPRODUCT(($E$7:$E$78=AE76)*($U$7:$U$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($U$7:$U$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX76" s="126">
         <f>AV76-AW76</f>
@@ -56021,11 +56273,11 @@
       </c>
       <c r="AZ76" s="126">
         <f>AT76/AT78*1000+AU76/AU78*100+AY76/AY78*10+AV76/AV78</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BA76" s="126">
         <f>AZ76/AZ78</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
       <c r="BB76" s="126" cm="1">
         <f t="array" ref="BB76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_win")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_win")*($X$7:$X$78))</f>
@@ -56033,15 +56285,15 @@
       </c>
       <c r="BC76" s="126" cm="1">
         <f t="array" ref="BC76">SUMPRODUCT(($S$7:$S$78=AE76&amp;"_draw")*($X$7:$X$78))+SUMPRODUCT(($T$7:$T$78=AE76&amp;"_draw")*($X$7:$X$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD76" s="126" cm="1">
         <f t="array" ref="BD76">SUMPRODUCT(($E$7:$E$78=AE76)*($X$7:$X$78)*($F$7:$F$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($X$7:$X$78)*($G$7:$G$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE76" s="126" cm="1">
         <f t="array" ref="BE76">SUMPRODUCT(($E$7:$E$78=AE76)*($X$7:$X$78)*($G$7:$G$78))+SUMPRODUCT(($H$7:$H$78=AE76)*($X$7:$X$78)*($F$7:$F$78))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF76" s="126">
         <f>BD76-BE76</f>
@@ -56053,11 +56305,11 @@
       </c>
       <c r="BH76" s="126">
         <f>BB76/BB78*1000+BC76/BC78*100+BG76/BG78*10+BD76/BD78</f>
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="BI76" s="126">
         <f>BH76/BH78</f>
-        <v>0.98058252427184467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:95" x14ac:dyDescent="0.25">
@@ -56080,8 +56332,12 @@
         <f>AE71</f>
         <v>Colombia</v>
       </c>
-      <c r="F77" s="19"/>
-      <c r="G77" s="20"/>
+      <c r="F77" s="19">
+        <v>1</v>
+      </c>
+      <c r="G77" s="20">
+        <v>1</v>
+      </c>
       <c r="H77" s="80" t="str">
         <f>AE68</f>
         <v>Portugal</v>
@@ -56089,11 +56345,11 @@
       <c r="I77" s="69"/>
       <c r="J77" s="33" t="str">
         <f>VLOOKUP(3,AD74:AN77,2,FALSE)</f>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="K77" s="23">
         <f>L77+M77+N77</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="23">
         <f>VLOOKUP(3,AD74:AN77,3,FALSE)</f>
@@ -56101,7 +56357,7 @@
       </c>
       <c r="M77" s="23">
         <f>VLOOKUP(3,AD74:AN77,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="23">
         <f>VLOOKUP(3,AD74:AN77,5,FALSE)</f>
@@ -56109,11 +56365,11 @@
       </c>
       <c r="O77" s="23" t="str">
         <f>VLOOKUP(3,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(3,AD74:AN77,7,FALSE)</f>
-        <v>3 - 2</v>
+        <v>3 - 3</v>
       </c>
       <c r="P77" s="34">
         <f>L77*3+M77</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R77" s="123">
         <f>DATE(2026,6,27)+TIME(12,30,0)+gmt_delta</f>
@@ -56121,43 +56377,43 @@
       </c>
       <c r="S77" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Colombia_draw</v>
       </c>
       <c r="T77" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Portugal_draw</v>
       </c>
       <c r="U77" s="123">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="123">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77" s="123">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z77" s="123">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA77" s="123">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB77" s="123" t="str">
+      <c r="AB77" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD77" s="123">
         <f>COUNTIF(AR74:AR77,CONCATENATE("&gt;=",AR77))</f>
@@ -56177,7 +56433,7 @@
       </c>
       <c r="AH77" s="123">
         <f>COUNTIF($S$7:$T$78,"=" &amp; AE77 &amp; "_lose")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$F$7:$F$78) + SUMIF($H$7:$H$78,$AE77,$G$7:$G$78)</f>
@@ -56185,11 +56441,11 @@
       </c>
       <c r="AJ77" s="123">
         <f>SUMIF($E$7:$E$78,$AE77,$G$7:$G$78) + SUMIF($H$7:$H$78,$AE77,$F$7:$F$78)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL77" s="123">
         <f>AI77-AJ77</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM77" s="123">
         <f>AL77-AL78</f>
@@ -56213,7 +56469,7 @@
       </c>
       <c r="AR77" s="125">
         <f>AP77/AP78</f>
-        <v>8.5776070001406329E-12</v>
+        <v>8.8036560639680661E-12</v>
       </c>
       <c r="AT77" s="126" cm="1">
         <f t="array" ref="AT77">SUMPRODUCT(($S$7:$S$78=AE77&amp;"_win")*($U$7:$U$78))+SUMPRODUCT(($T$7:$T$78=AE77&amp;"_win")*($U$7:$U$78))</f>
@@ -56300,8 +56556,12 @@
         <f>AE69</f>
         <v>DR Congo</v>
       </c>
-      <c r="F78" s="19"/>
-      <c r="G78" s="20"/>
+      <c r="F78" s="19">
+        <v>2</v>
+      </c>
+      <c r="G78" s="20">
+        <v>2</v>
+      </c>
       <c r="H78" s="80" t="str">
         <f>AE70</f>
         <v>Uzbekistan</v>
@@ -56313,7 +56573,7 @@
       </c>
       <c r="K78" s="36">
         <f>L78+M78+N78</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="36">
         <f>VLOOKUP(4,AD74:AN77,3,FALSE)</f>
@@ -56325,11 +56585,11 @@
       </c>
       <c r="N78" s="36">
         <f>VLOOKUP(4,AD74:AN77,5,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78" s="36" t="str">
         <f>VLOOKUP(4,AD74:AN77,6,FALSE) &amp; " - " &amp; VLOOKUP(4,AD74:AN77,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>0 - 5</v>
       </c>
       <c r="P78" s="37">
         <f>L78*3+M78</f>
@@ -56341,47 +56601,47 @@
       </c>
       <c r="S78" s="127" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>DR Congo_draw</v>
       </c>
       <c r="T78" s="127" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Uzbekistan_draw</v>
       </c>
       <c r="U78" s="123">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" s="123">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W78" s="123">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X78" s="123">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y78" s="123">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z78" s="123">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA78" s="123">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AB78" s="123" t="str">
+      <c r="AB78" s="123">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF78" s="123">
         <f t="shared" ref="AF78:AH78" si="36">MAX(AF74:AF77)-MIN(AF74:AF77)+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG78" s="123">
         <f t="shared" si="36"/>
@@ -56389,31 +56649,31 @@
       </c>
       <c r="AH78" s="123">
         <f t="shared" si="36"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI78" s="123">
         <f>MAX(AI74:AI77)+1</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL78" s="123">
         <f>MIN(AL74:AL77)</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM78" s="123">
         <f>MAX(AM74:AM77)+1</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN78" s="123">
         <f>MAX(AN74:AN77)+1</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO78" s="123">
         <f>MAX(AO74:AO77)+1</f>
-        <v>9.9805825242718456</v>
+        <v>9.75</v>
       </c>
       <c r="AP78" s="123">
         <f>MAX(AP74:AP77)+1</f>
-        <v>89805933.051883861</v>
+        <v>87500010.723135203</v>
       </c>
       <c r="AT78" s="126">
         <f>MAX(AT74:AT77)-MIN(AT74:AT77)+1</f>
@@ -56421,15 +56681,15 @@
       </c>
       <c r="AU78" s="126">
         <f>MAX(AU74:AU77)-MIN(AU74:AU77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV78" s="126">
         <f>MAX(AV74:AV77)-MIN(AV74:AV77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW78" s="126">
         <f>MAX(AW74:AW77)-MIN(AW74:AW77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY78" s="126">
         <f>MAX(AY74:AY77)-MIN(AY74:AY77)+1</f>
@@ -56437,7 +56697,7 @@
       </c>
       <c r="AZ78" s="126">
         <f>MAX(AZ74:AZ77)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
       <c r="BB78" s="126">
         <f>MAX(BB74:BB77)-MIN(BB74:BB77)+1</f>
@@ -56445,15 +56705,15 @@
       </c>
       <c r="BC78" s="126">
         <f>MAX(BC74:BC77)-MIN(BC74:BC77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD78" s="126">
         <f>MAX(BD74:BD77)-MIN(BD74:BD77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE78" s="126">
         <f>MAX(BE74:BE77)-MIN(BE74:BE77)+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG78" s="126">
         <f>MAX(BG74:BG77)-MIN(BG74:BG77)+1</f>
@@ -56461,7 +56721,7 @@
       </c>
       <c r="BH78" s="126">
         <f>MAX(BH74:BH77)+1</f>
-        <v>51.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:95" x14ac:dyDescent="0.25">
@@ -56522,7 +56782,7 @@
       </c>
       <c r="AD80" s="123">
         <f>COUNTIF($AP$80:$AP$91,CONCATENATE("&gt;=",AP80))</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE80" s="124" t="str">
         <f>J11</f>
@@ -56530,7 +56790,7 @@
       </c>
       <c r="AF80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,3,FALSE)</f>
@@ -56542,7 +56802,7 @@
       </c>
       <c r="AI80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,5,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,6,FALSE)</f>
@@ -56553,19 +56813,19 @@
       </c>
       <c r="AL80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM80" s="123">
         <f>AL80-$AL$92</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN80" s="123">
         <f>VLOOKUP($AE80,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP80" s="123">
         <f>AN80/AN92*10000+AM80/AM92*1000+AI80/AI92*100+IF(AQ80=0,ROW(),AQ80)/2000000</f>
-        <v>488.57222290142857</v>
+        <v>5628.5722229014282</v>
       </c>
       <c r="AQ80" s="126">
         <f t="shared" ref="AQ80:AQ91" si="37">VLOOKUP($AE80,$AE$8:$AQ$78,13,FALSE)</f>
@@ -56573,11 +56833,11 @@
       </c>
       <c r="AR80" s="125" t="str">
         <f>IF(AD80&lt;=8,RIGHT(AK80,1),"")</f>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AS80" s="129" t="str">
         <f>IF(AD80&lt;=8,AE80,"")</f>
-        <v/>
+        <v>Korea Republic</v>
       </c>
       <c r="AT80" s="130" t="str">
         <f>"Ⓐ "&amp;AE80</f>
@@ -56667,7 +56927,7 @@
       </c>
       <c r="AP81" s="123">
         <f>AN81/AN92*10000+AM81/AM92*1000+AI81/AI92*100+IF(AQ81=0,ROW(),AQ81)/2000000</f>
-        <v>9250.4768833961916</v>
+        <v>9233.3340262533347</v>
       </c>
       <c r="AQ81" s="126">
         <f t="shared" si="37"/>
@@ -56675,7 +56935,7 @@
       </c>
       <c r="AR81" s="125" t="str">
         <f>AR80&amp;IF(AD81&lt;=8,RIGHT(AK81,1),"")</f>
-        <v>B</v>
+        <v>AB</v>
       </c>
       <c r="AS81" s="129" t="str">
         <f t="shared" ref="AS81:AS91" si="46">IF(AD81&lt;=8,AE81,"")</f>
@@ -56702,7 +56962,7 @@
       </c>
       <c r="K82" s="100">
         <f t="shared" ref="K82:K92" si="47">L82+M82+N82</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,3,FALSE)</f>
@@ -56710,7 +56970,7 @@
       </c>
       <c r="M82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="100">
         <f>VLOOKUP(2,$AD$80:$AN$91,5,FALSE)</f>
@@ -56718,15 +56978,15 @@
       </c>
       <c r="O82" s="100" t="str">
         <f>VLOOKUP(2,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(2,$AD$80:$AN$91,7,FALSE)</f>
-        <v>4 - 3</v>
+        <v>6 - 5</v>
       </c>
       <c r="P82" s="101">
         <f t="shared" ref="P82:P92" si="48">L82*3+M82</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD82" s="123">
         <f t="shared" si="38"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE82" s="124" t="str">
         <f>J23</f>
@@ -56769,7 +57029,7 @@
       </c>
       <c r="AP82" s="123">
         <f>AN82/AN92*10000+AM82/AM92*1000+AI82/AI92*100+IF(AQ82=0,ROW(),AQ82)/2000000</f>
-        <v>5774.2864634607149</v>
+        <v>5757.143606317858</v>
       </c>
       <c r="AQ82" s="126">
         <f t="shared" si="37"/>
@@ -56777,7 +57037,7 @@
       </c>
       <c r="AR82" s="125" t="str">
         <f t="shared" ref="AR82:AR91" si="50">AR81&amp;IF(AD82&lt;=8,RIGHT(AK82,1),"")</f>
-        <v>BC</v>
+        <v>ABC</v>
       </c>
       <c r="AS82" s="129" t="str">
         <f t="shared" si="46"/>
@@ -56802,11 +57062,11 @@
       <c r="I83" s="69"/>
       <c r="J83" s="99" t="str">
         <f>VLOOKUP(3,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓛ Croatia</v>
+        <v>Ⓛ Ghana</v>
       </c>
       <c r="K83" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,3,FALSE)</f>
@@ -56814,7 +57074,7 @@
       </c>
       <c r="M83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="100">
         <f>VLOOKUP(3,$AD$80:$AN$91,5,FALSE)</f>
@@ -56822,11 +57082,11 @@
       </c>
       <c r="O83" s="100" t="str">
         <f>VLOOKUP(3,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(3,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 2</v>
+        <v>3 - 3</v>
       </c>
       <c r="P83" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD83" s="123">
         <f t="shared" si="38"/>
@@ -56834,19 +57094,19 @@
       </c>
       <c r="AE83" s="124" t="str">
         <f>J29</f>
-        <v>Paraguay</v>
+        <v>Australia</v>
       </c>
       <c r="AF83" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH83" s="123">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI83" s="123">
         <f t="shared" si="41"/>
@@ -56854,42 +57114,42 @@
       </c>
       <c r="AJ83" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK83" s="123" t="s">
         <v>3184</v>
       </c>
       <c r="AL83" s="123">
         <f t="shared" si="43"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM83" s="123">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN83" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP83" s="123">
         <f>AN83/AN92*10000+AM83/AM92*1000+AI83/AI92*100+IF(AQ83=0,ROW(),AQ83)/2000000</f>
-        <v>2258.0959898452379</v>
+        <v>5442.8579331921428</v>
       </c>
       <c r="AQ83" s="126">
         <f t="shared" si="37"/>
-        <v>1503.5</v>
+        <v>1580.67</v>
       </c>
       <c r="AR83" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCD</v>
+        <v>ABCD</v>
       </c>
       <c r="AS83" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Paraguay</v>
+        <v>Australia</v>
       </c>
       <c r="AT83" s="130" t="str">
         <f>"Ⓓ "&amp;AE83</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓓ Australia</v>
       </c>
     </row>
     <row r="84" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56904,7 +57164,7 @@
       <c r="I84" s="69"/>
       <c r="J84" s="99" t="str">
         <f>VLOOKUP(4,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓒ Scotland</v>
+        <v>Ⓙ Austria</v>
       </c>
       <c r="K84" s="100">
         <f t="shared" si="47"/>
@@ -56916,19 +57176,19 @@
       </c>
       <c r="M84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="100">
         <f>VLOOKUP(4,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" s="100" t="str">
         <f>VLOOKUP(4,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(4,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 3</v>
+        <v>2 - 3</v>
       </c>
       <c r="P84" s="101">
         <f t="shared" si="48"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R84" s="123">
         <f>DATE(2026,12,3)+TIME(4,0,0)+gmt_delta</f>
@@ -56936,15 +57196,15 @@
       </c>
       <c r="S84" s="127" t="str">
         <f>IF(OR(BM10="",BM11=""),"",IF(BM10&gt;BM11,BL10,IF(BM10&lt;BM11,BL11,IF(OR(BN10="",BN11=""),"draw",IF(BN10&gt;BN11,BL10,IF(BN10&lt;BN11,BL11,IF(OR(BO10="",BO11=""),"draw",IF(BO10&gt;BO11,BL10,IF(BO10&lt;BO11,BL11,"draw")))))))))</f>
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="T84" s="127" t="str" cm="1">
         <f t="array" ref="T84">IF(OR(S84="",S84="draw"),INDEX(T,86,lang),S84)</f>
-        <v>Austria</v>
+        <v>Germany</v>
       </c>
       <c r="AD84" s="123">
         <f t="shared" si="38"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE84" s="124" t="str">
         <f>J35</f>
@@ -56956,7 +57216,7 @@
       </c>
       <c r="AG84" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH84" s="123">
         <f t="shared" si="40"/>
@@ -56964,11 +57224,11 @@
       </c>
       <c r="AI84" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ84" s="123">
         <f t="shared" si="42"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK84" s="123" t="s">
         <v>3185</v>
@@ -56983,11 +57243,11 @@
       </c>
       <c r="AN84" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP84" s="123">
         <f>AN84/AN92*10000+AM84/AM92*1000+AI84/AI92*100+IF(AQ84=0,ROW(),AQ84)/2000000</f>
-        <v>468.57219506142854</v>
+        <v>2138.0960045852376</v>
       </c>
       <c r="AQ84" s="126">
         <f t="shared" si="37"/>
@@ -56995,7 +57255,7 @@
       </c>
       <c r="AR84" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCD</v>
+        <v>ABCD</v>
       </c>
       <c r="AS84" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57018,11 +57278,11 @@
       <c r="I85" s="69"/>
       <c r="J85" s="99" t="str">
         <f>VLOOKUP(5,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓙ Austria</v>
+        <v>Ⓒ Scotland</v>
       </c>
       <c r="K85" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,3,FALSE)</f>
@@ -57034,11 +57294,11 @@
       </c>
       <c r="N85" s="100">
         <f>VLOOKUP(5,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" s="100" t="str">
         <f>VLOOKUP(5,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(5,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>3 - 3</v>
       </c>
       <c r="P85" s="101">
         <f t="shared" si="48"/>
@@ -57050,15 +57310,15 @@
       </c>
       <c r="S85" s="127" t="str">
         <f>IF(OR(BM14="",BM15=""),"",IF(BM14&gt;BM15,BL14,IF(BM14&lt;BM15,BL15,IF(OR(BN14="",BN15=""),"draw",IF(BN14&gt;BN15,BL14,IF(BN14&lt;BN15,BL15,IF(OR(BO14="",BO15=""),"draw",IF(BO14&gt;BO15,BL14,IF(BO14&lt;BO15,BL15,"draw")))))))))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="T85" s="127" t="str" cm="1">
         <f t="array" ref="T85">IF(OR(S85="",S85="draw"),INDEX(T,87,lang),S85)</f>
-        <v>Jordan</v>
+        <v>France</v>
       </c>
       <c r="AD85" s="123">
         <f t="shared" si="38"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE85" s="124" t="str">
         <f>J41</f>
@@ -57070,7 +57330,7 @@
       </c>
       <c r="AG85" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH85" s="123">
         <f t="shared" si="40"/>
@@ -57078,11 +57338,11 @@
       </c>
       <c r="AI85" s="123">
         <f t="shared" si="41"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ85" s="123">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK85" s="123" t="s">
         <v>3186</v>
@@ -57097,11 +57357,11 @@
       </c>
       <c r="AN85" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP85" s="123">
         <f>AN85/AN92*10000+AM85/AM92*1000+AI85/AI92*100+IF(AQ85=0,ROW(),AQ85)/2000000</f>
-        <v>2278.096068310238</v>
+        <v>3961.9055921197619</v>
       </c>
       <c r="AQ85" s="126">
         <f t="shared" si="37"/>
@@ -57109,11 +57369,11 @@
       </c>
       <c r="AR85" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDF</v>
+        <v>ABCD</v>
       </c>
       <c r="AS85" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Japan</v>
+        <v/>
       </c>
       <c r="AT85" s="130" t="str">
         <f>"Ⓕ "&amp;AE85</f>
@@ -57132,31 +57392,31 @@
       <c r="I86" s="69"/>
       <c r="J86" s="99" t="str">
         <f>VLOOKUP(6,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓕ Japan</v>
+        <v>Ⓐ Korea Republic</v>
       </c>
       <c r="K86" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="100">
         <f>VLOOKUP(6,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O86" s="100" t="str">
         <f>VLOOKUP(6,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(6,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 3</v>
+        <v>4 - 5</v>
       </c>
       <c r="P86" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R86" s="123">
         <f>DATE(2026,12,4)+TIME(8,0,0)+gmt_delta</f>
@@ -57164,19 +57424,19 @@
       </c>
       <c r="S86" s="127" t="str">
         <f>IF(OR(BM26="",BM27=""),"",IF(BM26&gt;BM27,BL26,IF(BM26&lt;BM27,BL27,IF(OR(BN26="",BN27=""),"draw",IF(BN26&gt;BN27,BL26,IF(BN26&lt;BN27,BL27,IF(OR(BO26="",BO27=""),"draw",IF(BO26&gt;BO27,BL26,IF(BO26&lt;BO27,BL27,"draw")))))))))</f>
-        <v/>
+        <v>Croatia</v>
       </c>
       <c r="T86" s="127" t="str" cm="1">
         <f t="array" ref="T86">IF(OR(S86="",S86="draw"),INDEX(T,88,lang),S86)</f>
-        <v>DR Congo</v>
+        <v>Croatia</v>
       </c>
       <c r="AD86" s="123">
         <f t="shared" si="38"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE86" s="124" t="str">
         <f>J47</f>
-        <v>Iran</v>
+        <v>New Zealand</v>
       </c>
       <c r="AF86" s="123">
         <f t="shared" si="39"/>
@@ -57184,7 +57444,7 @@
       </c>
       <c r="AG86" s="123">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH86" s="123">
         <f t="shared" si="40"/>
@@ -57192,11 +57452,11 @@
       </c>
       <c r="AI86" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ86" s="123">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK86" s="123" t="s">
         <v>3187</v>
@@ -57211,27 +57471,27 @@
       </c>
       <c r="AN86" s="123">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP86" s="123">
         <f>AN86/AN92*10000+AM86/AM92*1000+AI86/AI92*100+IF(AQ86=0,ROW(),AQ86)/2000000</f>
-        <v>2238.0960457452379</v>
+        <v>3919.0482598326189</v>
       </c>
       <c r="AQ86" s="126">
         <f t="shared" si="37"/>
-        <v>1615.3</v>
+        <v>1281.57</v>
       </c>
       <c r="AR86" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFG</v>
+        <v>ABCD</v>
       </c>
       <c r="AS86" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Iran</v>
+        <v/>
       </c>
       <c r="AT86" s="130" t="str">
         <f>"Ⓖ "&amp;AE86</f>
-        <v>Ⓖ Iran</v>
+        <v>Ⓖ New Zealand</v>
       </c>
     </row>
     <row r="87" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57246,31 +57506,31 @@
       <c r="I87" s="69"/>
       <c r="J87" s="99" t="str">
         <f>VLOOKUP(7,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓓ Paraguay</v>
+        <v>Ⓓ Australia</v>
       </c>
       <c r="K87" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" s="100">
         <f>VLOOKUP(7,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" s="100" t="str">
         <f>VLOOKUP(7,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(7,$AD$80:$AN$91,7,FALSE)</f>
-        <v>1 - 2</v>
+        <v>1 - 3</v>
       </c>
       <c r="P87" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R87" s="123">
         <f>DATE(2026,12,4)+TIME(4,0,0)+gmt_delta</f>
@@ -57278,23 +57538,23 @@
       </c>
       <c r="S87" s="127" t="str">
         <f>IF(OR(BM30="",BM31=""),"",IF(BM30&gt;BM31,BL30,IF(BM30&lt;BM31,BL31,IF(OR(BN30="",BN31=""),"draw",IF(BN30&gt;BN31,BL30,IF(BN30&lt;BN31,BL31,IF(OR(BO30="",BO31=""),"draw",IF(BO30&gt;BO31,BL30,IF(BO30&lt;BO31,BL31,"draw")))))))))</f>
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="T87" s="127" t="str" cm="1">
         <f t="array" ref="T87">IF(OR(S87="",S87="draw"),INDEX(T,89,lang),S87)</f>
-        <v>Uzbekistan</v>
+        <v>Spain</v>
       </c>
       <c r="AD87" s="123">
         <f t="shared" si="38"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE87" s="124" t="str">
         <f>J53</f>
-        <v>Saudi Arabia</v>
+        <v>Cape Verde</v>
       </c>
       <c r="AF87" s="123">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG87" s="123">
         <f t="shared" si="49"/>
@@ -57306,46 +57566,46 @@
       </c>
       <c r="AI87" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ87" s="123">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AK87" s="123" t="s">
         <v>3188</v>
       </c>
       <c r="AL87" s="123">
         <f t="shared" si="43"/>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AM87" s="123">
         <f t="shared" si="44"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN87" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP87" s="123">
         <f>AN87/AN92*10000+AM87/AM92*1000+AI87/AI92*100+IF(AQ87=0,ROW(),AQ87)/2000000</f>
-        <v>285.71499642928575</v>
+        <v>5028.5721116364284</v>
       </c>
       <c r="AQ87" s="126">
         <f t="shared" si="37"/>
-        <v>1421.43</v>
+        <v>1366.13</v>
       </c>
       <c r="AR87" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFG</v>
+        <v>ABCDH</v>
       </c>
       <c r="AS87" s="129" t="str">
         <f t="shared" si="46"/>
-        <v/>
+        <v>Cape Verde</v>
       </c>
       <c r="AT87" s="130" t="str">
         <f>"Ⓗ "&amp;AE87</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
     </row>
     <row r="88" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57360,31 +57620,31 @@
       <c r="I88" s="69"/>
       <c r="J88" s="99" t="str">
         <f>VLOOKUP(8,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓖ Iran</v>
+        <v>Ⓗ Cape Verde</v>
       </c>
       <c r="K88" s="100">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,3,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,4,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="100">
         <f>VLOOKUP(8,$AD$80:$AN$91,5,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O88" s="100" t="str">
         <f>VLOOKUP(8,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(8,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 1</v>
+        <v>2 - 7</v>
       </c>
       <c r="P88" s="101">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R88" s="123">
         <f>DATE(2026,12,5)+TIME(4,0,0)+gmt_delta</f>
@@ -57392,11 +57652,11 @@
       </c>
       <c r="S88" s="127" t="str">
         <f>IF(OR(BM18="",BM19=""),"",IF(BM18&gt;BM19,BL18,IF(BM18&lt;BM19,BL19,IF(OR(BN18="",BN19=""),"draw",IF(BN18&gt;BN19,BL18,IF(BN18&lt;BN19,BL19,IF(OR(BO18="",BO19=""),"draw",IF(BO18&gt;BO19,BL18,IF(BO18&lt;BO19,BL19,"draw")))))))))</f>
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="T88" s="127" t="str" cm="1">
         <f t="array" ref="T88">IF(OR(S88="",S88="draw"),INDEX(T,90,lang),S88)</f>
-        <v>Colombia</v>
+        <v>Canada</v>
       </c>
       <c r="AD88" s="123">
         <f t="shared" si="38"/>
@@ -57412,7 +57672,7 @@
       </c>
       <c r="AG88" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH88" s="123">
         <f t="shared" si="40"/>
@@ -57420,11 +57680,11 @@
       </c>
       <c r="AI88" s="123">
         <f t="shared" si="41"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ88" s="123">
         <f t="shared" si="42"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK88" s="123" t="s">
         <v>3189</v>
@@ -57439,11 +57699,11 @@
       </c>
       <c r="AN88" s="123">
         <f t="shared" si="45"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP88" s="123">
         <f>AN88/AN92*10000+AM88/AM92*1000+AI88/AI92*100+IF(AQ88=0,ROW(),AQ88)/2000000</f>
-        <v>5937.1436326128569</v>
+        <v>7609.5245849938083</v>
       </c>
       <c r="AQ88" s="126">
         <f t="shared" si="37"/>
@@ -57451,7 +57711,7 @@
       </c>
       <c r="AR88" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFGI</v>
+        <v>ABCDHI</v>
       </c>
       <c r="AS88" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57474,11 +57734,11 @@
       <c r="I89" s="69"/>
       <c r="J89" s="102" t="str">
         <f>VLOOKUP(9,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓐ Korea Republic</v>
+        <v>Ⓕ Japan</v>
       </c>
       <c r="K89" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,3,FALSE)</f>
@@ -57486,19 +57746,19 @@
       </c>
       <c r="M89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N89" s="103">
         <f>VLOOKUP(9,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O89" s="103" t="str">
         <f>VLOOKUP(9,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(9,$AD$80:$AN$91,7,FALSE)</f>
-        <v>3 - 5</v>
+        <v>4 - 5</v>
       </c>
       <c r="P89" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R89" s="123">
         <f>DATE(2026,12,5)+TIME(8,0,0)+gmt_delta</f>
@@ -57506,15 +57766,15 @@
       </c>
       <c r="S89" s="127" t="str">
         <f>IF(OR(BM22="",BM23=""),"",IF(BM22&gt;BM23,BL22,IF(BM22&lt;BM23,BL23,IF(OR(BN22="",BN23=""),"draw",IF(BN22&gt;BN23,BL22,IF(BN22&lt;BN23,BL23,IF(OR(BO22="",BO23=""),"draw",IF(BO22&gt;BO23,BL22,IF(BO22&lt;BO23,BL23,"draw")))))))))</f>
-        <v/>
+        <v>Netherlands</v>
       </c>
       <c r="T89" s="127" t="str" cm="1">
         <f t="array" ref="T89">IF(OR(S89="",S89="draw"),INDEX(T,91,lang),S89)</f>
-        <v>Panama</v>
+        <v>Netherlands</v>
       </c>
       <c r="AD89" s="123">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE89" s="124" t="str">
         <f>J65</f>
@@ -57526,7 +57786,7 @@
       </c>
       <c r="AG89" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH89" s="123">
         <f t="shared" si="40"/>
@@ -57534,11 +57794,11 @@
       </c>
       <c r="AI89" s="123">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ89" s="123">
         <f t="shared" si="42"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK89" s="123" t="s">
         <v>3190</v>
@@ -57553,11 +57813,11 @@
       </c>
       <c r="AN89" s="123">
         <f t="shared" si="45"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP89" s="123">
         <f>AN89/AN92*10000+AM89/AM92*1000+AI89/AI92*100+IF(AQ89=0,ROW(),AQ89)/2000000</f>
-        <v>5591.4293681535719</v>
+        <v>7266.6674633916664</v>
       </c>
       <c r="AQ89" s="126">
         <f t="shared" si="37"/>
@@ -57565,7 +57825,7 @@
       </c>
       <c r="AR89" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFGIJ</v>
+        <v>ABCDHIJ</v>
       </c>
       <c r="AS89" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57588,11 +57848,11 @@
       <c r="I90" s="69"/>
       <c r="J90" s="102" t="str">
         <f>VLOOKUP(10,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓔ Ivory Coast</v>
+        <v>Ⓖ New Zealand</v>
       </c>
       <c r="K90" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,3,FALSE)</f>
@@ -57600,19 +57860,19 @@
       </c>
       <c r="M90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N90" s="103">
         <f>VLOOKUP(10,$AD$80:$AN$91,5,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O90" s="103" t="str">
         <f>VLOOKUP(10,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(10,$AD$80:$AN$91,7,FALSE)</f>
-        <v>2 - 4</v>
+        <v>1 - 2</v>
       </c>
       <c r="P90" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R90" s="123">
         <f>DATE(2026,12,6)+TIME(4,0,0)+gmt_delta</f>
@@ -57620,11 +57880,11 @@
       </c>
       <c r="S90" s="127" t="str">
         <f>IF(OR(BM34="",BM35=""),"",IF(BM34&gt;BM35,BL34,IF(BM34&lt;BM35,BL35,IF(OR(BN34="",BN35=""),"draw",IF(BN34&gt;BN35,BL34,IF(BN34&lt;BN35,BL35,IF(OR(BO34="",BO35=""),"draw",IF(BO34&gt;BO35,BL34,IF(BO34&lt;BO35,BL35,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T90" s="127" cm="1">
+        <v>United States</v>
+      </c>
+      <c r="T90" s="127" t="str" cm="1">
         <f t="array" ref="T90">IF(OR(S90="",S90="draw"),INDEX(T,92,lang),S90)</f>
-        <v>0</v>
+        <v>United States</v>
       </c>
       <c r="AD90" s="123">
         <f t="shared" si="38"/>
@@ -57640,7 +57900,7 @@
       </c>
       <c r="AG90" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="123">
         <f t="shared" si="40"/>
@@ -57648,11 +57908,11 @@
       </c>
       <c r="AI90" s="123">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ90" s="123">
         <f t="shared" si="42"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK90" s="123" t="s">
         <v>3191</v>
@@ -57667,11 +57927,11 @@
       </c>
       <c r="AN90" s="123">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP90" s="123">
         <f>AN90/AN92*10000+AM90/AM92*1000+AI90/AI92*100+IF(AQ90=0,ROW(),AQ90)/2000000</f>
-        <v>7.391749999999999E-4</v>
+        <v>1695.2388344130952</v>
       </c>
       <c r="AQ90" s="126">
         <f t="shared" si="37"/>
@@ -57679,7 +57939,7 @@
       </c>
       <c r="AR90" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFGIJ</v>
+        <v>ABCDHIJ</v>
       </c>
       <c r="AS90" s="129" t="str">
         <f t="shared" si="46"/>
@@ -57702,11 +57962,11 @@
       <c r="I91" s="69"/>
       <c r="J91" s="102" t="str">
         <f>VLOOKUP(11,$AD$80:$AT$91,17,FALSE)</f>
-        <v>Ⓗ Saudi Arabia</v>
+        <v>Ⓔ Ivory Coast</v>
       </c>
       <c r="K91" s="103">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,3,FALSE)</f>
@@ -57714,7 +57974,7 @@
       </c>
       <c r="M91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" s="103">
         <f>VLOOKUP(11,$AD$80:$AN$91,5,FALSE)</f>
@@ -57722,11 +57982,11 @@
       </c>
       <c r="O91" s="103" t="str">
         <f>VLOOKUP(11,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(11,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 3</v>
+        <v>3 - 5</v>
       </c>
       <c r="P91" s="104">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="123">
         <f>DATE(2026,12,6)+TIME(8,0,0)+gmt_delta</f>
@@ -57734,11 +57994,11 @@
       </c>
       <c r="S91" s="127" t="str">
         <f>IF(OR(BM38="",BM39=""),"",IF(BM38&gt;BM39,BL38,IF(BM38&lt;BM39,BL39,IF(OR(BN38="",BN39=""),"draw",IF(BN38&gt;BN39,BL38,IF(BN38&lt;BN39,BL39,IF(OR(BO38="",BO39=""),"draw",IF(BO38&gt;BO39,BL38,IF(BO38&lt;BO39,BL39,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T91" s="127" cm="1">
+        <v>Belgium</v>
+      </c>
+      <c r="T91" s="127" t="str" cm="1">
         <f t="array" ref="T91">IF(OR(S91="",S91="draw"),INDEX(T,93,lang),S91)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
       <c r="AD91" s="123">
         <f t="shared" si="38"/>
@@ -57746,7 +58006,7 @@
       </c>
       <c r="AE91" s="124" t="str">
         <f>J77</f>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="AF91" s="123">
         <f t="shared" si="39"/>
@@ -57754,7 +58014,7 @@
       </c>
       <c r="AG91" s="123">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,4,FALSE)</f>
@@ -57766,42 +58026,42 @@
       </c>
       <c r="AJ91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,6,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK91" s="123" t="s">
         <v>3192</v>
       </c>
       <c r="AL91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,8,FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM91" s="123">
         <f t="shared" si="44"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN91" s="123">
         <f>VLOOKUP($AE91,$AE$8:$AQ$78,10,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP91" s="123">
         <f>AN91/AN92*10000+AM91/AM92*1000+AI91/AI92*100+IF(AQ91=0,ROW(),AQ91)/2000000</f>
-        <v>5917.1437156778566</v>
+        <v>7423.810196964524</v>
       </c>
       <c r="AQ91" s="126">
         <f t="shared" si="37"/>
-        <v>1717.07</v>
+        <v>1346.31</v>
       </c>
       <c r="AR91" s="125" t="str">
         <f t="shared" si="50"/>
-        <v>BCDFGIJL</v>
+        <v>ABCDHIJL</v>
       </c>
       <c r="AS91" s="129" t="str">
         <f t="shared" si="46"/>
-        <v>Croatia</v>
+        <v>Ghana</v>
       </c>
       <c r="AT91" s="130" t="str">
         <f>"Ⓛ "&amp;AE91</f>
-        <v>Ⓛ Croatia</v>
+        <v>Ⓛ Ghana</v>
       </c>
     </row>
     <row r="92" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57820,7 +58080,7 @@
       </c>
       <c r="K92" s="106">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,3,FALSE)</f>
@@ -57828,7 +58088,7 @@
       </c>
       <c r="M92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,4,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="106">
         <f>VLOOKUP(12,$AD$80:$AN$91,5,FALSE)</f>
@@ -57836,11 +58096,11 @@
       </c>
       <c r="O92" s="106" t="str">
         <f>VLOOKUP(12,$AD$80:$AN$91,6,FALSE) &amp; " - " &amp; VLOOKUP(12,$AD$80:$AN$91,7,FALSE)</f>
-        <v>0 - 5</v>
+        <v>2 - 7</v>
       </c>
       <c r="P92" s="107">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF92" s="123">
         <f>MAX(AF80:AF91)+1</f>
@@ -57856,11 +58116,11 @@
       </c>
       <c r="AI92" s="123">
         <f>MAX(AI80:AI91)+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ92" s="123">
         <f>MAX(AJ80:AJ91)+1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL92" s="123">
         <f>MIN(AL80:AL91)</f>
@@ -57876,7 +58136,7 @@
       </c>
       <c r="AS92" s="126" t="b">
         <f>SUM(K9:K78)=144</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:46" x14ac:dyDescent="0.25">
@@ -57904,11 +58164,11 @@
       </c>
       <c r="S95" s="127" t="str">
         <f>IF(OR(BT12="",BT13=""),"",IF(BT12&gt;BT13,BS12,IF(BT12&lt;BT13,BS13,IF(OR(BU12="",BU13=""),"draw",IF(BU12&gt;BU13,BS12,IF(BU12&lt;BU13,BS13,IF(OR(BV12="",BV13=""),"draw",IF(BV12&gt;BV13,BS12,IF(BV12&lt;BV13,BS13,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T95" s="127" cm="1">
+        <v>France</v>
+      </c>
+      <c r="T95" s="127" t="str" cm="1">
         <f t="array" ref="T95">IF(OR(S95="",S95="draw"),INDEX(T,94,lang),S95)</f>
-        <v>0</v>
+        <v>France</v>
       </c>
     </row>
     <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57918,11 +58178,11 @@
       </c>
       <c r="S96" s="127" t="str">
         <f>IF(OR(BT20="",BT21=""),"",IF(BT20&gt;BT21,BS20,IF(BT20&lt;BT21,BS21,IF(OR(BU20="",BU21=""),"draw",IF(BU20&gt;BU21,BS20,IF(BU20&lt;BU21,BS21,IF(OR(BV20="",BV21=""),"draw",IF(BV20&gt;BV21,BS20,IF(BV20&lt;BV21,BS21,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T96" s="127" cm="1">
+        <v>Canada</v>
+      </c>
+      <c r="T96" s="127" t="str" cm="1">
         <f t="array" ref="T96">IF(OR(S96="",S96="draw"),INDEX(T,95,lang),S96)</f>
-        <v>0</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="97" spans="18:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57932,11 +58192,11 @@
       </c>
       <c r="S97" s="127" t="str">
         <f>IF(OR(BT28="",BT29=""),"",IF(BT28&gt;BT29,BS28,IF(BT28&lt;BT29,BS29,IF(OR(BU28="",BU29=""),"draw",IF(BU28&gt;BU29,BS28,IF(BU28&lt;BU29,BS29,IF(OR(BV28="",BV29=""),"draw",IF(BV28&gt;BV29,BS28,IF(BV28&lt;BV29,BS29,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T97" s="127" cm="1">
+        <v>Spain</v>
+      </c>
+      <c r="T97" s="127" t="str" cm="1">
         <f t="array" ref="T97">IF(OR(S97="",S97="draw"),INDEX(T,96,lang),S97)</f>
-        <v>0</v>
+        <v>Spain</v>
       </c>
     </row>
     <row r="98" spans="18:29" x14ac:dyDescent="0.25">
@@ -57946,11 +58206,11 @@
       </c>
       <c r="S98" s="127" t="str">
         <f>IF(OR(BT36="",BT37=""),"",IF(BT36&gt;BT37,BS36,IF(BT36&lt;BT37,BS37,IF(OR(BU36="",BU37=""),"draw",IF(BU36&gt;BU37,BS36,IF(BU36&lt;BU37,BS37,IF(OR(BV36="",BV37=""),"draw",IF(BV36&gt;BV37,BS36,IF(BV36&lt;BV37,BS37,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T98" s="127" cm="1">
+        <v>Belgium</v>
+      </c>
+      <c r="T98" s="127" t="str" cm="1">
         <f t="array" ref="T98">IF(OR(S98="",S98="draw"),INDEX(T,97,lang),S98)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
     </row>
     <row r="102" spans="18:29" x14ac:dyDescent="0.25">
@@ -57960,23 +58220,23 @@
       </c>
       <c r="S102" s="127" t="str">
         <f>IF(OR(CA16="",CA17=""),"",IF(CA16&gt;CA17,BZ16,IF(CA16&lt;CA17,BZ17,IF(OR(CB16="",CB17=""),"draw",IF(CB16&gt;CB17,BZ16,IF(CB16&lt;CB17,BZ17,IF(OR(CC16="",CC17=""),"draw",IF(CC16&gt;CC17,BZ16,IF(CC16&lt;CC17,BZ17,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T102" s="127" cm="1">
+        <v>France</v>
+      </c>
+      <c r="T102" s="127" t="str" cm="1">
         <f t="array" ref="T102">IF(OR(S102="",S102="draw"),INDEX(T,98,lang),S102)</f>
-        <v>0</v>
+        <v>France</v>
       </c>
       <c r="U102" s="123" t="str">
         <f>IF(OR(CA16="",CA17=""),"",IF(CA16&lt;CA17,BZ16,IF(CA16&gt;CA17,BZ17,IF(OR(CB16="",CB17=""),"draw",IF(CB16&lt;CB17,BZ16,IF(CB16&gt;CB17,BZ17,IF(OR(CC16="",CC17=""),"draw",IF(CC16&lt;CC17,BZ16,IF(CC16&gt;CC17,BZ17,"draw")))))))))</f>
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="X102" s="123" t="str">
         <f>IF(OR(CM16="",CM17=""),"",IF(CM16&lt;CM17,CL16,IF(CM16&gt;CM17,CL17,IF(OR(CN16="",CN17=""),"draw",IF(CN16&lt;CN17,CL16,IF(CN16&gt;CN17,CL17,IF(OR(CO16="",CO17=""),"draw",IF(CO16&lt;CO17,CL16,IF(CO16&gt;CO17,CL17,"draw")))))))))</f>
         <v/>
       </c>
-      <c r="AC102" s="127" cm="1">
+      <c r="AC102" s="127" t="str" cm="1">
         <f t="array" ref="AC102">IF(OR(U102="",U102="draw"),INDEX(T,100,lang),U102)</f>
-        <v>0</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="103" spans="18:29" x14ac:dyDescent="0.25">
@@ -57986,23 +58246,23 @@
       </c>
       <c r="S103" s="127" t="str">
         <f>IF(OR(CA32="",CA33=""),"",IF(CA32&gt;CA33,BZ32,IF(CA32&lt;CA33,BZ33,IF(OR(CB32="",CB33=""),"draw",IF(CB32&gt;CB33,BZ32,IF(CB32&lt;CB33,BZ33,IF(OR(CC32="",CC33=""),"draw",IF(CC32&gt;CC33,BZ32,IF(CC32&lt;CC33,BZ33,"draw")))))))))</f>
-        <v/>
-      </c>
-      <c r="T103" s="127" cm="1">
+        <v>Spain</v>
+      </c>
+      <c r="T103" s="127" t="str" cm="1">
         <f t="array" ref="T103">IF(OR(S103="",S103="draw"),INDEX(T,99,lang),S103)</f>
-        <v>0</v>
+        <v>Spain</v>
       </c>
       <c r="U103" s="123" t="str">
         <f>IF(OR(CA32="",CA33=""),"",IF(CA32&lt;CA33,BZ32,IF(CA32&gt;CA33,BZ33,IF(OR(CB32="",CB33=""),"draw",IF(CB32&lt;CB33,BZ32,IF(CB32&gt;CB33,BZ33,IF(OR(CC32="",CC33=""),"draw",IF(CC32&lt;CC33,BZ32,IF(CC32&gt;CC33,BZ33,"draw")))))))))</f>
-        <v/>
+        <v>Belgium</v>
       </c>
       <c r="X103" s="123" t="str">
         <f>IF(OR(CM32="",CM33=""),"",IF(CM32&lt;CM33,CL32,IF(CM32&gt;CM33,CL33,IF(OR(CN32="",CN33=""),"draw",IF(CN32&lt;CN33,CL32,IF(CN32&gt;CN33,CL33,IF(OR(CO32="",CO33=""),"draw",IF(CO32&lt;CO33,CL32,IF(CO32&gt;CO33,CL33,"draw")))))))))</f>
         <v/>
       </c>
-      <c r="AC103" s="127" cm="1">
+      <c r="AC103" s="127" t="str" cm="1">
         <f t="array" ref="AC103">IF(OR(U103="",U103="draw"),INDEX(T,101,lang),U103)</f>
-        <v>0</v>
+        <v>Belgium</v>
       </c>
     </row>
     <row r="107" spans="18:29" x14ac:dyDescent="0.25">
@@ -58022,11 +58282,11 @@
       </c>
       <c r="S111" s="127" t="str">
         <f>IF(OR(CH23="",CH24=""),"",IF(CH23&gt;CH24,CG23,IF(CH23&lt;CH24,CG24,IF(OR(CI23="",CI24=""),"",IF(CI23&gt;CI24,CG23,IF(CI23&lt;CI24,CG24,IF(OR(CJ23="",CJ24=""),"",IF(CJ23&gt;CJ24,CG23,IF(CJ23&lt;CJ24,CG24,"")))))))))</f>
-        <v/>
+        <v>France</v>
       </c>
       <c r="T111" s="127" t="str">
         <f>S111</f>
-        <v/>
+        <v>France</v>
       </c>
     </row>
   </sheetData>
@@ -59119,19 +59379,19 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="109">
         <f>MATCH(C3,C6:C500,0)</f>
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="C3" s="121" t="str">
         <f>'2026 World Cup'!AR91</f>
-        <v>BCDFGIJL</v>
+        <v>ABCDHIJL</v>
       </c>
       <c r="D3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,2,FALSE)</f>
-        <v>3C</v>
+        <v>3H</v>
       </c>
       <c r="E3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,3,FALSE)</f>
-        <v>3G</v>
+        <v>3J</v>
       </c>
       <c r="F3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,4,FALSE)</f>
@@ -59139,15 +59399,15 @@
       </c>
       <c r="G3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,5,FALSE)</f>
-        <v>3D</v>
+        <v>3C</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,6,FALSE)</f>
-        <v>3J</v>
+        <v>3A</v>
       </c>
       <c r="I3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,7,FALSE)</f>
-        <v>3F</v>
+        <v>3D</v>
       </c>
       <c r="J3" s="121" t="str">
         <f>VLOOKUP($C3,$C$6:$K$500,8,FALSE)</f>
@@ -75043,167 +75303,8 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010090E39FCCE5B25D41843728463D8702CD" ma:contentTypeVersion="3" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="f526c9bbb9da171fc3aa15898664257d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dacec4a-16e0-4c23-af47-b0328532aa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f692aa5e1eb72d1d7d7719d109e8ca1" ns2:_="">
-    <xsd:import namespace="3dacec4a-16e0-4c23-af47-b0328532aa0c"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3dacec4a-16e0-4c23-af47-b0328532aa0c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Innholdstype"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Tittel"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF111CA8-B7DF-4BB6-BA58-B6B64E66D0ED}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE5795B-96C8-47EE-A841-211BADDD3AC6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67F88573-3515-4800-8A45-0C5DD11CD377}"/>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{463b6811-b0a4-4b2a-b932-72c4c970c5d2}" enabled="0" method="" siteId="{463b6811-b0a4-4b2a-b932-72c4c970c5d2}" removed="1"/>
+</clbl:labelList>
 </file>